--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,72 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Brazilian Serie A</t>
+  </si>
+  <si>
+    <t>Finnish Veikkausliiga</t>
+  </si>
+  <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>Cruzeiro MG</t>
+  </si>
+  <si>
+    <t>HJK Helsinki</t>
+  </si>
+  <si>
+    <t>KuPS</t>
+  </si>
+  <si>
+    <t>MB Rouissat</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Sao Paulo</t>
+  </si>
+  <si>
+    <t>VPS</t>
+  </si>
+  <si>
+    <t>AC Oulu</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>Olympique Akbou</t>
+  </si>
+  <si>
+    <t>ES Setif</t>
+  </si>
+  <si>
+    <t>2026-10-06 01:52:54</t>
   </si>
 </sst>
 </file>
@@ -585,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +894,1458 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2">
+        <v>1.91</v>
+      </c>
+      <c r="G2">
+        <v>1.98</v>
+      </c>
+      <c r="H2">
+        <v>4.4</v>
+      </c>
+      <c r="I2">
+        <v>4.8</v>
+      </c>
+      <c r="J2">
+        <v>3.65</v>
+      </c>
+      <c r="K2">
+        <v>3.85</v>
+      </c>
+      <c r="L2">
+        <v>1.42</v>
+      </c>
+      <c r="M2">
+        <v>1.05</v>
+      </c>
+      <c r="N2">
+        <v>3.55</v>
+      </c>
+      <c r="O2">
+        <v>1.35</v>
+      </c>
+      <c r="P2">
+        <v>1.89</v>
+      </c>
+      <c r="Q2">
+        <v>2.04</v>
+      </c>
+      <c r="R2">
+        <v>1.33</v>
+      </c>
+      <c r="S2">
+        <v>3.55</v>
+      </c>
+      <c r="T2">
+        <v>1.81</v>
+      </c>
+      <c r="U2">
+        <v>1.9</v>
+      </c>
+      <c r="V2">
+        <v>1.26</v>
+      </c>
+      <c r="W2">
+        <v>2.02</v>
+      </c>
+      <c r="X2">
+        <v>950</v>
+      </c>
+      <c r="Y2">
+        <v>950</v>
+      </c>
+      <c r="Z2">
+        <v>38</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>9</v>
+      </c>
+      <c r="AC2">
+        <v>8.4</v>
+      </c>
+      <c r="AD2">
+        <v>20</v>
+      </c>
+      <c r="AE2">
+        <v>80</v>
+      </c>
+      <c r="AF2">
+        <v>21</v>
+      </c>
+      <c r="AG2">
+        <v>11.5</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>85</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>48</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>38</v>
+      </c>
+      <c r="AO2">
+        <v>80</v>
+      </c>
+      <c r="AP2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ2">
+        <v>9.6</v>
+      </c>
+      <c r="AR2">
+        <v>2.24</v>
+      </c>
+      <c r="AS2">
+        <v>2.38</v>
+      </c>
+      <c r="AT2">
+        <v>7.8</v>
+      </c>
+      <c r="AU2">
+        <v>7.4</v>
+      </c>
+      <c r="AV2">
+        <v>11</v>
+      </c>
+      <c r="AW2">
+        <v>2.32</v>
+      </c>
+      <c r="AX2">
+        <v>7.8</v>
+      </c>
+      <c r="AY2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>16.5</v>
+      </c>
+      <c r="BA2">
+        <v>2.32</v>
+      </c>
+      <c r="BB2">
+        <v>17.5</v>
+      </c>
+      <c r="BC2">
+        <v>17</v>
+      </c>
+      <c r="BD2">
+        <v>2.26</v>
+      </c>
+      <c r="BE2">
+        <v>2.38</v>
+      </c>
+      <c r="BF2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG2">
+        <v>2.32</v>
+      </c>
+      <c r="BH2">
+        <v>10.5</v>
+      </c>
+      <c r="BI2">
+        <v>2.18</v>
+      </c>
+      <c r="BJ2">
+        <v>12</v>
+      </c>
+      <c r="BK2">
+        <v>7.6</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>2.16</v>
+      </c>
+      <c r="BN2">
+        <v>4.9</v>
+      </c>
+      <c r="BO2">
+        <v>3.85</v>
+      </c>
+      <c r="BP2">
+        <v>19</v>
+      </c>
+      <c r="BQ2">
+        <v>9.6</v>
+      </c>
+      <c r="BR2">
+        <v>40</v>
+      </c>
+      <c r="BS2">
+        <v>2.04</v>
+      </c>
+      <c r="BT2">
+        <v>9</v>
+      </c>
+      <c r="BU2">
+        <v>6.6</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>2.08</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>2.1</v>
+      </c>
+      <c r="BZ2">
+        <v>36</v>
+      </c>
+      <c r="CA2">
+        <v>4.7</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3">
+        <v>1.52</v>
+      </c>
+      <c r="G3">
+        <v>1.81</v>
+      </c>
+      <c r="H3">
+        <v>5.2</v>
+      </c>
+      <c r="I3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J3">
+        <v>3.7</v>
+      </c>
+      <c r="K3">
+        <v>7</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1.96</v>
+      </c>
+      <c r="Q3">
+        <v>1.63</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="BZ3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4">
+        <v>1.59</v>
+      </c>
+      <c r="G4">
+        <v>1.69</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>6.8</v>
+      </c>
+      <c r="J4">
+        <v>4</v>
+      </c>
+      <c r="K4">
+        <v>4.4</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>1.81</v>
+      </c>
+      <c r="Q4">
+        <v>1.76</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5">
+        <v>1.1</v>
+      </c>
+      <c r="G5">
+        <v>600</v>
+      </c>
+      <c r="H5">
+        <v>1.1</v>
+      </c>
+      <c r="I5">
+        <v>870</v>
+      </c>
+      <c r="J5">
+        <v>1.1</v>
+      </c>
+      <c r="K5">
+        <v>950</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.07</v>
+      </c>
+      <c r="Q5">
+        <v>1.01</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6">
+        <v>1.1</v>
+      </c>
+      <c r="G6">
+        <v>600</v>
+      </c>
+      <c r="H6">
+        <v>1.1</v>
+      </c>
+      <c r="I6">
+        <v>870</v>
+      </c>
+      <c r="J6">
+        <v>1.1</v>
+      </c>
+      <c r="K6">
+        <v>950</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.07</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>1.1</v>
+      </c>
+      <c r="G7">
+        <v>600</v>
+      </c>
+      <c r="H7">
+        <v>1.1</v>
+      </c>
+      <c r="I7">
+        <v>870</v>
+      </c>
+      <c r="J7">
+        <v>1.1</v>
+      </c>
+      <c r="K7">
+        <v>950</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.07</v>
+      </c>
+      <c r="Q7">
+        <v>1.01</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
@@ -319,7 +319,7 @@
     <t>ES Setif</t>
   </si>
   <si>
-    <t>2026-10-06 01:52:54</t>
+    <t>2026-10-06 04:04:29</t>
   </si>
 </sst>
 </file>
@@ -913,16 +913,16 @@
         <v>95</v>
       </c>
       <c r="F2">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G2">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2">
         <v>3.65</v>
@@ -931,130 +931,130 @@
         <v>3.85</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q2">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="U2">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="V2">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X2">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="Y2">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
         <v>38</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2">
         <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AE2">
         <v>80</v>
       </c>
       <c r="AF2">
+        <v>12</v>
+      </c>
+      <c r="AG2">
+        <v>11</v>
+      </c>
+      <c r="AH2">
         <v>21</v>
-      </c>
-      <c r="AG2">
-        <v>11.5</v>
-      </c>
-      <c r="AH2">
-        <v>1000</v>
       </c>
       <c r="AI2">
         <v>85</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN2">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="AO2">
         <v>80</v>
       </c>
       <c r="AP2">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AR2">
-        <v>2.24</v>
+        <v>8</v>
       </c>
       <c r="AS2">
-        <v>2.38</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT2">
         <v>7.8</v>
       </c>
       <c r="AU2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AW2">
-        <v>2.32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX2">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AY2">
+        <v>9.4</v>
+      </c>
+      <c r="AZ2">
+        <v>17</v>
+      </c>
+      <c r="BA2">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AZ2">
-        <v>16.5</v>
-      </c>
-      <c r="BA2">
-        <v>2.32</v>
       </c>
       <c r="BB2">
         <v>17.5</v>
@@ -1063,25 +1063,25 @@
         <v>17</v>
       </c>
       <c r="BD2">
-        <v>2.26</v>
+        <v>8.4</v>
       </c>
       <c r="BE2">
-        <v>2.38</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BG2">
-        <v>2.32</v>
+        <v>9.4</v>
       </c>
       <c r="BH2">
+        <v>3.3</v>
+      </c>
+      <c r="BI2">
+        <v>3.05</v>
+      </c>
+      <c r="BJ2">
         <v>10.5</v>
-      </c>
-      <c r="BI2">
-        <v>2.18</v>
-      </c>
-      <c r="BJ2">
-        <v>12</v>
       </c>
       <c r="BK2">
         <v>7.6</v>
@@ -1090,49 +1090,49 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>2.16</v>
+        <v>13.5</v>
       </c>
       <c r="BN2">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BO2">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BR2">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>2.04</v>
+        <v>10</v>
       </c>
       <c r="BT2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BU2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>2.08</v>
+        <v>11</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>2.1</v>
+        <v>11.5</v>
       </c>
       <c r="BZ2">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="CA2">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="s">
         <v>101</v>
@@ -1155,22 +1155,22 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="G3">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="H3">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="I3">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1397,7 +1397,7 @@
         <v>97</v>
       </c>
       <c r="F4">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="G4">
         <v>1.69</v>
@@ -1406,7 +1406,7 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1427,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q4">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="R4">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
@@ -319,7 +319,7 @@
     <t>ES Setif</t>
   </si>
   <si>
-    <t>2026-10-06 04:04:29</t>
+    <t>2026-10-06 06:16:18</t>
   </si>
 </sst>
 </file>
@@ -925,10 +925,10 @@
         <v>4.7</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -937,7 +937,7 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O2">
         <v>1.36</v>
@@ -1051,7 +1051,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA2">
         <v>9.199999999999999</v>
@@ -1403,16 +1403,16 @@
         <v>1.69</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1427,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q4">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R4">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
@@ -319,7 +319,7 @@
     <t>ES Setif</t>
   </si>
   <si>
-    <t>2026-10-06 06:16:18</t>
+    <t>2026-10-06 08:27:28</t>
   </si>
 </sst>
 </file>
@@ -913,226 +913,226 @@
         <v>95</v>
       </c>
       <c r="F2">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="I2">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="J2">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="L2">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="R2">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T2">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="U2">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="V2">
         <v>1.27</v>
       </c>
       <c r="W2">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y2">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AD2">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
+        <v>970</v>
+      </c>
+      <c r="AG2">
+        <v>970</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>970</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>9</v>
+      </c>
+      <c r="AQ2">
+        <v>9.6</v>
+      </c>
+      <c r="AR2">
+        <v>1.49</v>
+      </c>
+      <c r="AS2">
+        <v>1.49</v>
+      </c>
+      <c r="AT2">
+        <v>6.4</v>
+      </c>
+      <c r="AU2">
+        <v>6.2</v>
+      </c>
+      <c r="AV2">
+        <v>11</v>
+      </c>
+      <c r="AW2">
+        <v>1.49</v>
+      </c>
+      <c r="AX2">
+        <v>7.8</v>
+      </c>
+      <c r="AY2">
+        <v>7.4</v>
+      </c>
+      <c r="AZ2">
         <v>12</v>
       </c>
-      <c r="AG2">
-        <v>11</v>
-      </c>
-      <c r="AH2">
-        <v>21</v>
-      </c>
-      <c r="AI2">
-        <v>85</v>
-      </c>
-      <c r="AJ2">
-        <v>24</v>
-      </c>
-      <c r="AK2">
-        <v>23</v>
-      </c>
-      <c r="AL2">
-        <v>44</v>
-      </c>
-      <c r="AM2">
-        <v>140</v>
-      </c>
-      <c r="AN2">
-        <v>15</v>
-      </c>
-      <c r="AO2">
-        <v>80</v>
-      </c>
-      <c r="AP2">
-        <v>11.5</v>
-      </c>
-      <c r="AQ2">
-        <v>12.5</v>
-      </c>
-      <c r="AR2">
-        <v>8</v>
-      </c>
-      <c r="AS2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT2">
-        <v>7.8</v>
-      </c>
-      <c r="AU2">
-        <v>7.6</v>
-      </c>
-      <c r="AV2">
-        <v>15</v>
-      </c>
-      <c r="AW2">
+      <c r="BA2">
+        <v>1.49</v>
+      </c>
+      <c r="BB2">
+        <v>1.49</v>
+      </c>
+      <c r="BC2">
+        <v>1.52</v>
+      </c>
+      <c r="BD2">
+        <v>1.49</v>
+      </c>
+      <c r="BE2">
+        <v>1.49</v>
+      </c>
+      <c r="BF2">
         <v>9.199999999999999</v>
       </c>
-      <c r="AX2">
-        <v>10.5</v>
-      </c>
-      <c r="AY2">
-        <v>9.4</v>
-      </c>
-      <c r="AZ2">
-        <v>17.5</v>
-      </c>
-      <c r="BA2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB2">
-        <v>17.5</v>
-      </c>
-      <c r="BC2">
-        <v>17</v>
-      </c>
-      <c r="BD2">
-        <v>8.4</v>
-      </c>
-      <c r="BE2">
-        <v>10</v>
-      </c>
-      <c r="BF2">
-        <v>12</v>
-      </c>
       <c r="BG2">
-        <v>9.4</v>
+        <v>1.49</v>
       </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>3.05</v>
+        <v>1.23</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>7.6</v>
+        <v>1.87</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4.1</v>
+        <v>1.39</v>
       </c>
       <c r="BP2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>10.5</v>
+        <v>1.87</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>7</v>
+        <v>1.87</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>101</v>
@@ -1155,22 +1155,22 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G3">
         <v>1.69</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="I3">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1185,10 +1185,10 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>1.96</v>
+        <v>1.07</v>
       </c>
       <c r="Q3">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1397,22 +1397,22 @@
         <v>97</v>
       </c>
       <c r="F4">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G4">
         <v>1.69</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I4">
         <v>6.8</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1427,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.92</v>
+        <v>1.07</v>
       </c>
       <c r="Q4">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="R4">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
@@ -319,7 +319,7 @@
     <t>ES Setif</t>
   </si>
   <si>
-    <t>2026-10-06 08:27:28</t>
+    <t>2026-10-06 10:38:39</t>
   </si>
 </sst>
 </file>
@@ -913,226 +913,226 @@
         <v>95</v>
       </c>
       <c r="F2">
+        <v>1.91</v>
+      </c>
+      <c r="G2">
+        <v>1.99</v>
+      </c>
+      <c r="H2">
+        <v>4.3</v>
+      </c>
+      <c r="I2">
+        <v>4.7</v>
+      </c>
+      <c r="J2">
+        <v>3.6</v>
+      </c>
+      <c r="K2">
+        <v>3.85</v>
+      </c>
+      <c r="L2">
+        <v>1.44</v>
+      </c>
+      <c r="M2">
+        <v>1.08</v>
+      </c>
+      <c r="N2">
+        <v>3.55</v>
+      </c>
+      <c r="O2">
+        <v>1.36</v>
+      </c>
+      <c r="P2">
         <v>1.87</v>
       </c>
-      <c r="G2">
+      <c r="Q2">
         <v>2.06</v>
       </c>
-      <c r="H2">
-        <v>3.85</v>
-      </c>
-      <c r="I2">
-        <v>5.5</v>
-      </c>
-      <c r="J2">
-        <v>3.25</v>
-      </c>
-      <c r="K2">
-        <v>4.5</v>
-      </c>
-      <c r="L2">
-        <v>1.42</v>
-      </c>
-      <c r="M2">
-        <v>1.07</v>
-      </c>
-      <c r="N2">
-        <v>3.25</v>
-      </c>
-      <c r="O2">
-        <v>1.32</v>
-      </c>
-      <c r="P2">
-        <v>1.78</v>
-      </c>
-      <c r="Q2">
-        <v>1.93</v>
-      </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="U2">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="V2">
         <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X2">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y2">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB2">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AC2">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF2">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN2">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP2">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
+        <v>12.5</v>
+      </c>
+      <c r="AR2">
+        <v>8.4</v>
+      </c>
+      <c r="AS2">
+        <v>10</v>
+      </c>
+      <c r="AT2">
+        <v>7.8</v>
+      </c>
+      <c r="AU2">
+        <v>7.4</v>
+      </c>
+      <c r="AV2">
+        <v>15.5</v>
+      </c>
+      <c r="AW2">
         <v>9.6</v>
       </c>
-      <c r="AR2">
-        <v>1.49</v>
-      </c>
-      <c r="AS2">
-        <v>1.49</v>
-      </c>
-      <c r="AT2">
-        <v>6.4</v>
-      </c>
-      <c r="AU2">
-        <v>6.2</v>
-      </c>
-      <c r="AV2">
-        <v>11</v>
-      </c>
-      <c r="AW2">
-        <v>1.49</v>
-      </c>
       <c r="AX2">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AY2">
+        <v>9.6</v>
+      </c>
+      <c r="AZ2">
+        <v>17.5</v>
+      </c>
+      <c r="BA2">
+        <v>9.6</v>
+      </c>
+      <c r="BB2">
         <v>7.4</v>
       </c>
-      <c r="AZ2">
-        <v>12</v>
-      </c>
-      <c r="BA2">
-        <v>1.49</v>
-      </c>
-      <c r="BB2">
-        <v>1.49</v>
-      </c>
       <c r="BC2">
-        <v>1.52</v>
+        <v>17</v>
       </c>
       <c r="BD2">
-        <v>1.49</v>
+        <v>8.6</v>
       </c>
       <c r="BE2">
-        <v>1.49</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BG2">
-        <v>1.49</v>
+        <v>9.6</v>
       </c>
       <c r="BH2">
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.23</v>
+        <v>1.99</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK2">
-        <v>1.87</v>
+        <v>7.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO2">
-        <v>1.39</v>
+        <v>3.75</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ2">
-        <v>1.87</v>
+        <v>9.6</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU2">
-        <v>1.87</v>
+        <v>5.9</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="CB2" t="s">
         <v>101</v>
@@ -1185,10 +1185,10 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>1.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q3">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>3.95</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1427,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.07</v>
+        <v>1.92</v>
       </c>
       <c r="Q4">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="R4">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="111">
   <si>
     <t>League</t>
   </si>
@@ -262,9 +262,18 @@
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
+    <t>Jordanian Premier League</t>
+  </si>
+  <si>
+    <t>Romanian Liga II</t>
+  </si>
+  <si>
     <t>Algerian Ligue 1</t>
   </si>
   <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>2026-10-08</t>
   </si>
   <si>
@@ -289,6 +298,12 @@
     <t>HJK Helsinki</t>
   </si>
   <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Politehnica Timisoara</t>
+  </si>
+  <si>
     <t>KuPS</t>
   </si>
   <si>
@@ -298,6 +313,9 @@
     <t>JS Saoura</t>
   </si>
   <si>
+    <t>Independiente Juniors</t>
+  </si>
+  <si>
     <t>MC Oran</t>
   </si>
   <si>
@@ -307,6 +325,12 @@
     <t>VPS</t>
   </si>
   <si>
+    <t>Al Buqaa</t>
+  </si>
+  <si>
+    <t>CSA Steaua Bucuresti</t>
+  </si>
+  <si>
     <t>AC Oulu</t>
   </si>
   <si>
@@ -316,10 +340,13 @@
     <t>Olympique Akbou</t>
   </si>
   <si>
+    <t>Club Nueve de Octubre</t>
+  </si>
+  <si>
     <t>ES Setif</t>
   </si>
   <si>
-    <t>2026-10-06 10:38:39</t>
+    <t>2026-10-06 12:50:18</t>
   </si>
 </sst>
 </file>
@@ -651,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -901,19 +928,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F2">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G2">
         <v>1.99</v>
@@ -958,7 +985,7 @@
         <v>1.9</v>
       </c>
       <c r="U2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V2">
         <v>1.27</v>
@@ -1009,13 +1036,13 @@
         <v>23</v>
       </c>
       <c r="AL2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM2">
         <v>140</v>
       </c>
       <c r="AN2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO2">
         <v>80</v>
@@ -1027,7 +1054,7 @@
         <v>12.5</v>
       </c>
       <c r="AR2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS2">
         <v>10</v>
@@ -1042,7 +1069,7 @@
         <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX2">
         <v>10</v>
@@ -1054,16 +1081,16 @@
         <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC2">
         <v>17</v>
       </c>
       <c r="BD2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE2">
         <v>10</v>
@@ -1072,16 +1099,16 @@
         <v>12.5</v>
       </c>
       <c r="BG2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BI2">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="BJ2">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
         <v>7.6</v>
@@ -1090,7 +1117,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BN2">
         <v>5.3</v>
@@ -1108,7 +1135,7 @@
         <v>44</v>
       </c>
       <c r="BS2">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="BT2">
         <v>9.6</v>
@@ -1120,22 +1147,22 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="BZ2">
         <v>38</v>
       </c>
       <c r="CA2">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CB2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1143,46 +1170,46 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G3">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H3">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="I3">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="K3">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P3">
         <v>2.2</v>
@@ -1191,452 +1218,452 @@
         <v>1.71</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG3">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BH3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BI3">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BO3">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BP3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BR3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BV3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F4">
-        <v>1.63</v>
+        <v>1.1</v>
       </c>
       <c r="G4">
-        <v>1.69</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="I4">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>3.95</v>
+        <v>1.1</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P4">
-        <v>1.92</v>
+        <v>1.08</v>
       </c>
       <c r="Q4">
-        <v>1.94</v>
+        <v>1.02</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F5">
         <v>1.1</v>
@@ -1651,252 +1678,252 @@
         <v>870</v>
       </c>
       <c r="J5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K5">
         <v>950</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>1.63</v>
       </c>
       <c r="G6">
-        <v>600</v>
+        <v>1.69</v>
       </c>
       <c r="H6">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="I6">
-        <v>870</v>
+        <v>6.8</v>
       </c>
       <c r="J6">
-        <v>1.1</v>
+        <v>3.95</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1911,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.07</v>
+        <v>1.92</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2103,24 +2130,24 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F7">
         <v>1.1</v>
@@ -2345,7 +2372,733 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>101</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8">
+        <v>1.1</v>
+      </c>
+      <c r="G8">
+        <v>600</v>
+      </c>
+      <c r="H8">
+        <v>1.1</v>
+      </c>
+      <c r="I8">
+        <v>870</v>
+      </c>
+      <c r="J8">
+        <v>1.1</v>
+      </c>
+      <c r="K8">
+        <v>950</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.07</v>
+      </c>
+      <c r="Q8">
+        <v>1.01</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9">
+        <v>1.1</v>
+      </c>
+      <c r="G9">
+        <v>600</v>
+      </c>
+      <c r="H9">
+        <v>1.1</v>
+      </c>
+      <c r="I9">
+        <v>870</v>
+      </c>
+      <c r="J9">
+        <v>1.1</v>
+      </c>
+      <c r="K9">
+        <v>950</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.04</v>
+      </c>
+      <c r="Q9">
+        <v>1.01</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10">
+        <v>1.1</v>
+      </c>
+      <c r="G10">
+        <v>600</v>
+      </c>
+      <c r="H10">
+        <v>1.1</v>
+      </c>
+      <c r="I10">
+        <v>870</v>
+      </c>
+      <c r="J10">
+        <v>1.1</v>
+      </c>
+      <c r="K10">
+        <v>950</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>1.07</v>
+      </c>
+      <c r="Q10">
+        <v>1.01</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="126">
   <si>
     <t>League</t>
   </si>
@@ -268,12 +268,18 @@
     <t>Romanian Liga II</t>
   </si>
   <si>
+    <t>Moroccan Botola Pro 1</t>
+  </si>
+  <si>
     <t>Algerian Ligue 1</t>
   </si>
   <si>
     <t>Ecuadorian Serie B</t>
   </si>
   <si>
+    <t>Romanian Liga I</t>
+  </si>
+  <si>
     <t>2026-10-08</t>
   </si>
   <si>
@@ -289,9 +295,18 @@
     <t>17:00:00</t>
   </si>
   <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
     <t>Cruzeiro MG</t>
   </si>
   <si>
@@ -307,6 +322,9 @@
     <t>KuPS</t>
   </si>
   <si>
+    <t>Union de Touarga</t>
+  </si>
+  <si>
     <t>MB Rouissat</t>
   </si>
   <si>
@@ -316,9 +334,21 @@
     <t>Independiente Juniors</t>
   </si>
   <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Club R Zemamra</t>
+  </si>
+  <si>
+    <t>FAR Rabat</t>
+  </si>
+  <si>
     <t>MC Oran</t>
   </si>
   <si>
+    <t>MAS Maghrib A Fes</t>
+  </si>
+  <si>
     <t>Sao Paulo</t>
   </si>
   <si>
@@ -334,6 +364,9 @@
     <t>AC Oulu</t>
   </si>
   <si>
+    <t>RSB Berkane</t>
+  </si>
+  <si>
     <t>USM Alger</t>
   </si>
   <si>
@@ -343,10 +376,22 @@
     <t>Club Nueve de Octubre</t>
   </si>
   <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>HUSA Agadir</t>
+  </si>
+  <si>
+    <t>Widad Temara</t>
+  </si>
+  <si>
     <t>ES Setif</t>
   </si>
   <si>
-    <t>2026-10-06 12:50:18</t>
+    <t>Raja Casablanca</t>
+  </si>
+  <si>
+    <t>2026-10-06 15:02:08</t>
   </si>
 </sst>
 </file>
@@ -678,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -928,16 +973,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F2">
         <v>1.92</v>
@@ -1042,7 +1087,7 @@
         <v>140</v>
       </c>
       <c r="AN2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO2">
         <v>80</v>
@@ -1078,16 +1123,16 @@
         <v>9.6</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA2">
         <v>9.800000000000001</v>
       </c>
       <c r="BB2">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="BC2">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BD2">
         <v>8.800000000000001</v>
@@ -1102,13 +1147,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BH2">
-        <v>16</v>
+        <v>3.3</v>
       </c>
       <c r="BI2">
-        <v>2.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK2">
         <v>7.6</v>
@@ -1117,52 +1162,52 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="BN2">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BO2">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2">
         <v>9.6</v>
       </c>
       <c r="BR2">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BS2">
-        <v>1.92</v>
+        <v>10</v>
       </c>
       <c r="BT2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW2">
-        <v>1.95</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY2">
-        <v>1.96</v>
+        <v>12</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="CA2">
-        <v>1.91</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1170,16 +1215,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F3">
         <v>1.61</v>
@@ -1206,22 +1251,22 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O3">
         <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q3">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R3">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S3">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="T3">
         <v>1.73</v>
@@ -1296,10 +1341,10 @@
         <v>14</v>
       </c>
       <c r="AR3">
-        <v>28</v>
+        <v>3.05</v>
       </c>
       <c r="AS3">
-        <v>85</v>
+        <v>3.2</v>
       </c>
       <c r="AT3">
         <v>7.6</v>
@@ -1311,7 +1356,7 @@
         <v>14</v>
       </c>
       <c r="AW3">
-        <v>42</v>
+        <v>3.1</v>
       </c>
       <c r="AX3">
         <v>8.199999999999999</v>
@@ -1323,7 +1368,7 @@
         <v>12.5</v>
       </c>
       <c r="BA3">
-        <v>42</v>
+        <v>3.1</v>
       </c>
       <c r="BB3">
         <v>12.5</v>
@@ -1335,13 +1380,13 @@
         <v>18.5</v>
       </c>
       <c r="BE3">
-        <v>55</v>
+        <v>3.2</v>
       </c>
       <c r="BF3">
         <v>6</v>
       </c>
       <c r="BG3">
-        <v>46</v>
+        <v>3.2</v>
       </c>
       <c r="BH3">
         <v>5</v>
@@ -1353,13 +1398,13 @@
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>6.2</v>
+        <v>2.18</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BN3">
         <v>5.9</v>
@@ -1371,40 +1416,40 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>7.2</v>
+        <v>2.16</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>6.8</v>
+        <v>2.14</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="CB3" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1412,16 +1457,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F4">
         <v>1.1</v>
@@ -1448,34 +1493,34 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="O4">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P4">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Q4">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="R4">
         <v>1.08</v>
       </c>
       <c r="S4">
+        <v>1.35</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
         <v>1.02</v>
       </c>
-      <c r="T4">
-        <v>1.01</v>
-      </c>
-      <c r="U4">
-        <v>1.01</v>
-      </c>
-      <c r="V4">
-        <v>1.01</v>
-      </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1532,52 +1577,52 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4">
         <v>1.01</v>
@@ -1646,7 +1691,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1654,16 +1699,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F5">
         <v>1.1</v>
@@ -1888,7 +1933,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1896,28 +1941,28 @@
         <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F6">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G6">
         <v>1.69</v>
       </c>
       <c r="H6">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I6">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J6">
         <v>3.95</v>
@@ -1926,211 +1971,211 @@
         <v>4.3</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P6">
+        <v>1.93</v>
+      </c>
+      <c r="Q6">
+        <v>1.96</v>
+      </c>
+      <c r="R6">
+        <v>1.32</v>
+      </c>
+      <c r="S6">
+        <v>3.15</v>
+      </c>
+      <c r="T6">
+        <v>1.96</v>
+      </c>
+      <c r="U6">
         <v>1.92</v>
       </c>
-      <c r="Q6">
-        <v>1.94</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="CB6" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2138,483 +2183,483 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F7">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="G7">
-        <v>600</v>
+        <v>4.9</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>2.12</v>
       </c>
       <c r="I7">
-        <v>870</v>
+        <v>3.1</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>2.66</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P7">
-        <v>1.07</v>
+        <v>1.42</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F8">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="G8">
-        <v>600</v>
+        <v>4.3</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>2.12</v>
       </c>
       <c r="I8">
-        <v>870</v>
+        <v>2.68</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>2.46</v>
       </c>
       <c r="K8">
         <v>950</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P8">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2622,258 +2667,258 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F9">
-        <v>1.1</v>
+        <v>2.02</v>
       </c>
       <c r="G9">
-        <v>600</v>
+        <v>2.3</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="I9">
         <v>870</v>
       </c>
       <c r="J9">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P9">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="CB9" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F10">
         <v>1.1</v>
@@ -2894,211 +2939,1421 @@
         <v>950</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P10">
+        <v>1.06</v>
+      </c>
+      <c r="Q10">
+        <v>1.01</v>
+      </c>
+      <c r="R10">
+        <v>1.06</v>
+      </c>
+      <c r="S10">
+        <v>1.01</v>
+      </c>
+      <c r="T10">
+        <v>1.01</v>
+      </c>
+      <c r="U10">
+        <v>1.01</v>
+      </c>
+      <c r="V10">
+        <v>1.01</v>
+      </c>
+      <c r="W10">
+        <v>1.01</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>1000</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>1000</v>
+      </c>
+      <c r="AC10">
+        <v>1000</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>1000</v>
+      </c>
+      <c r="AG10">
+        <v>1000</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>1000</v>
+      </c>
+      <c r="AK10">
+        <v>1000</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>1000</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10">
+        <v>1.01</v>
+      </c>
+      <c r="AR10">
+        <v>1.01</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>1.01</v>
+      </c>
+      <c r="AU10">
+        <v>1.01</v>
+      </c>
+      <c r="AV10">
+        <v>1.01</v>
+      </c>
+      <c r="AW10">
+        <v>1.01</v>
+      </c>
+      <c r="AX10">
+        <v>1.01</v>
+      </c>
+      <c r="AY10">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10">
+        <v>1.01</v>
+      </c>
+      <c r="BA10">
+        <v>1.01</v>
+      </c>
+      <c r="BB10">
+        <v>1.01</v>
+      </c>
+      <c r="BC10">
+        <v>1.01</v>
+      </c>
+      <c r="BD10">
+        <v>1.01</v>
+      </c>
+      <c r="BE10">
+        <v>1.01</v>
+      </c>
+      <c r="BF10">
+        <v>1.01</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>1.01</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.01</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.01</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.01</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>1.01</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.01</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11">
+        <v>2.36</v>
+      </c>
+      <c r="G11">
+        <v>2.56</v>
+      </c>
+      <c r="H11">
+        <v>2.98</v>
+      </c>
+      <c r="I11">
+        <v>3.3</v>
+      </c>
+      <c r="J11">
+        <v>3.45</v>
+      </c>
+      <c r="K11">
+        <v>3.65</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.06</v>
+      </c>
+      <c r="N11">
+        <v>4</v>
+      </c>
+      <c r="O11">
+        <v>1.27</v>
+      </c>
+      <c r="P11">
+        <v>2.04</v>
+      </c>
+      <c r="Q11">
+        <v>1.79</v>
+      </c>
+      <c r="R11">
+        <v>1.41</v>
+      </c>
+      <c r="S11">
+        <v>3</v>
+      </c>
+      <c r="T11">
+        <v>1.66</v>
+      </c>
+      <c r="U11">
+        <v>2.24</v>
+      </c>
+      <c r="V11">
+        <v>1.44</v>
+      </c>
+      <c r="W11">
+        <v>1.64</v>
+      </c>
+      <c r="X11">
+        <v>21</v>
+      </c>
+      <c r="Y11">
+        <v>14.5</v>
+      </c>
+      <c r="Z11">
+        <v>24</v>
+      </c>
+      <c r="AA11">
+        <v>55</v>
+      </c>
+      <c r="AB11">
+        <v>12.5</v>
+      </c>
+      <c r="AC11">
+        <v>9</v>
+      </c>
+      <c r="AD11">
+        <v>14.5</v>
+      </c>
+      <c r="AE11">
+        <v>36</v>
+      </c>
+      <c r="AF11">
+        <v>17.5</v>
+      </c>
+      <c r="AG11">
+        <v>12.5</v>
+      </c>
+      <c r="AH11">
+        <v>17</v>
+      </c>
+      <c r="AI11">
+        <v>42</v>
+      </c>
+      <c r="AJ11">
+        <v>36</v>
+      </c>
+      <c r="AK11">
+        <v>26</v>
+      </c>
+      <c r="AL11">
+        <v>40</v>
+      </c>
+      <c r="AM11">
+        <v>100</v>
+      </c>
+      <c r="AN11">
+        <v>18.5</v>
+      </c>
+      <c r="AO11">
+        <v>28</v>
+      </c>
+      <c r="AP11">
+        <v>14</v>
+      </c>
+      <c r="AQ11">
+        <v>11.5</v>
+      </c>
+      <c r="AR11">
+        <v>18.5</v>
+      </c>
+      <c r="AS11">
+        <v>34</v>
+      </c>
+      <c r="AT11">
+        <v>10</v>
+      </c>
+      <c r="AU11">
+        <v>7.2</v>
+      </c>
+      <c r="AV11">
+        <v>11.5</v>
+      </c>
+      <c r="AW11">
+        <v>23</v>
+      </c>
+      <c r="AX11">
+        <v>14</v>
+      </c>
+      <c r="AY11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11">
+        <v>13.5</v>
+      </c>
+      <c r="BA11">
+        <v>28</v>
+      </c>
+      <c r="BB11">
+        <v>7</v>
+      </c>
+      <c r="BC11">
+        <v>21</v>
+      </c>
+      <c r="BD11">
+        <v>25</v>
+      </c>
+      <c r="BE11">
+        <v>7.8</v>
+      </c>
+      <c r="BF11">
+        <v>14.5</v>
+      </c>
+      <c r="BG11">
+        <v>18.5</v>
+      </c>
+      <c r="BH11">
+        <v>4.2</v>
+      </c>
+      <c r="BI11">
+        <v>2.84</v>
+      </c>
+      <c r="BJ11">
+        <v>13</v>
+      </c>
+      <c r="BK11">
+        <v>5.6</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>21</v>
+      </c>
+      <c r="BN11">
+        <v>7.8</v>
+      </c>
+      <c r="BO11">
+        <v>3.6</v>
+      </c>
+      <c r="BP11">
+        <v>25</v>
+      </c>
+      <c r="BQ11">
+        <v>10.5</v>
+      </c>
+      <c r="BR11">
+        <v>40</v>
+      </c>
+      <c r="BS11">
+        <v>16.5</v>
+      </c>
+      <c r="BT11">
+        <v>9</v>
+      </c>
+      <c r="BU11">
+        <v>4.1</v>
+      </c>
+      <c r="BV11">
+        <v>34</v>
+      </c>
+      <c r="BW11">
+        <v>14</v>
+      </c>
+      <c r="BX11">
+        <v>48</v>
+      </c>
+      <c r="BY11">
+        <v>19</v>
+      </c>
+      <c r="BZ11">
+        <v>34</v>
+      </c>
+      <c r="CA11">
+        <v>13.5</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" t="s">
+        <v>121</v>
+      </c>
+      <c r="F12">
+        <v>1.1</v>
+      </c>
+      <c r="G12">
+        <v>1000</v>
+      </c>
+      <c r="H12">
+        <v>1.1</v>
+      </c>
+      <c r="I12">
+        <v>1000</v>
+      </c>
+      <c r="J12">
+        <v>1.1</v>
+      </c>
+      <c r="K12">
+        <v>950</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
         <v>1.07</v>
       </c>
-      <c r="Q10">
-        <v>1.01</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <v>0</v>
-      </c>
-      <c r="AH10">
-        <v>0</v>
-      </c>
-      <c r="AI10">
-        <v>0</v>
-      </c>
-      <c r="AJ10">
-        <v>0</v>
-      </c>
-      <c r="AK10">
-        <v>0</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>0</v>
-      </c>
-      <c r="AO10">
-        <v>0</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>0</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>0</v>
-      </c>
-      <c r="BC10">
-        <v>0</v>
-      </c>
-      <c r="BD10">
-        <v>0</v>
-      </c>
-      <c r="BE10">
-        <v>0</v>
-      </c>
-      <c r="BF10">
-        <v>0</v>
-      </c>
-      <c r="BG10">
-        <v>0</v>
-      </c>
-      <c r="BH10">
-        <v>0</v>
-      </c>
-      <c r="BI10">
-        <v>0</v>
-      </c>
-      <c r="BJ10">
-        <v>0</v>
-      </c>
-      <c r="BK10">
-        <v>0</v>
-      </c>
-      <c r="BL10">
-        <v>0</v>
-      </c>
-      <c r="BM10">
-        <v>0</v>
-      </c>
-      <c r="BN10">
-        <v>0</v>
-      </c>
-      <c r="BO10">
-        <v>0</v>
-      </c>
-      <c r="BP10">
-        <v>0</v>
-      </c>
-      <c r="BQ10">
-        <v>0</v>
-      </c>
-      <c r="BR10">
-        <v>0</v>
-      </c>
-      <c r="BS10">
-        <v>0</v>
-      </c>
-      <c r="BT10">
-        <v>0</v>
-      </c>
-      <c r="BU10">
-        <v>0</v>
-      </c>
-      <c r="BV10">
-        <v>0</v>
-      </c>
-      <c r="BW10">
-        <v>0</v>
-      </c>
-      <c r="BX10">
-        <v>0</v>
-      </c>
-      <c r="BY10">
-        <v>0</v>
-      </c>
-      <c r="BZ10">
-        <v>0</v>
-      </c>
-      <c r="CA10">
-        <v>0</v>
-      </c>
-      <c r="CB10" t="s">
+      <c r="Q12">
+        <v>1.01</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13">
+        <v>1.1</v>
+      </c>
+      <c r="G13">
+        <v>1.4</v>
+      </c>
+      <c r="H13">
+        <v>1.1</v>
+      </c>
+      <c r="I13">
+        <v>1000</v>
+      </c>
+      <c r="J13">
+        <v>1.1</v>
+      </c>
+      <c r="K13">
+        <v>950</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1.07</v>
+      </c>
+      <c r="Q13">
+        <v>1.01</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14">
+        <v>1.1</v>
+      </c>
+      <c r="G14">
+        <v>600</v>
+      </c>
+      <c r="H14">
+        <v>1.1</v>
+      </c>
+      <c r="I14">
+        <v>870</v>
+      </c>
+      <c r="J14">
+        <v>1.1</v>
+      </c>
+      <c r="K14">
+        <v>950</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1.07</v>
+      </c>
+      <c r="Q14">
+        <v>1.01</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" t="s">
         <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>124</v>
+      </c>
+      <c r="F15">
+        <v>1.1</v>
+      </c>
+      <c r="G15">
+        <v>1000</v>
+      </c>
+      <c r="H15">
+        <v>1.1</v>
+      </c>
+      <c r="I15">
+        <v>1000</v>
+      </c>
+      <c r="J15">
+        <v>1.1</v>
+      </c>
+      <c r="K15">
+        <v>950</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1.07</v>
+      </c>
+      <c r="Q15">
+        <v>1.01</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="135">
   <si>
     <t>League</t>
   </si>
@@ -280,6 +280,12 @@
     <t>Romanian Liga I</t>
   </si>
   <si>
+    <t>Peruvian Primera Division</t>
+  </si>
+  <si>
+    <t>Irish Premier Division</t>
+  </si>
+  <si>
     <t>2026-10-08</t>
   </si>
   <si>
@@ -307,6 +313,9 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
     <t>Cruzeiro MG</t>
   </si>
   <si>
@@ -325,15 +334,15 @@
     <t>Union de Touarga</t>
   </si>
   <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>Independiente Juniors</t>
+  </si>
+  <si>
     <t>MB Rouissat</t>
   </si>
   <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>Independiente Juniors</t>
-  </si>
-  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
@@ -343,12 +352,21 @@
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Cesar Vallejo Moquegua</t>
+  </si>
+  <si>
     <t>MC Oran</t>
   </si>
   <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
     <t>MAS Maghrib A Fes</t>
   </si>
   <si>
+    <t>Atletico Grau</t>
+  </si>
+  <si>
     <t>Sao Paulo</t>
   </si>
   <si>
@@ -367,15 +385,15 @@
     <t>RSB Berkane</t>
   </si>
   <si>
+    <t>Olympique Akbou</t>
+  </si>
+  <si>
+    <t>Club Nueve de Octubre</t>
+  </si>
+  <si>
     <t>USM Alger</t>
   </si>
   <si>
-    <t>Olympique Akbou</t>
-  </si>
-  <si>
-    <t>Club Nueve de Octubre</t>
-  </si>
-  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
@@ -385,13 +403,22 @@
     <t>Widad Temara</t>
   </si>
   <si>
+    <t>Cienciano</t>
+  </si>
+  <si>
     <t>ES Setif</t>
   </si>
   <si>
+    <t>Drogheda</t>
+  </si>
+  <si>
     <t>Raja Casablanca</t>
   </si>
   <si>
-    <t>2026-10-06 15:02:08</t>
+    <t>CD Los Chankas</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:13:21</t>
   </si>
 </sst>
 </file>
@@ -723,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -973,28 +1000,28 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F2">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G2">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>4.3</v>
       </c>
       <c r="I2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J2">
         <v>3.6</v>
@@ -1021,10 +1048,10 @@
         <v>2.06</v>
       </c>
       <c r="R2">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T2">
         <v>1.9</v>
@@ -1042,25 +1069,25 @@
         <v>14</v>
       </c>
       <c r="Y2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z2">
         <v>36</v>
       </c>
       <c r="AA2">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AB2">
         <v>8.6</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE2">
-        <v>75</v>
+        <v>550</v>
       </c>
       <c r="AF2">
         <v>11.5</v>
@@ -1072,7 +1099,7 @@
         <v>21</v>
       </c>
       <c r="AI2">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
         <v>24</v>
@@ -1084,40 +1111,40 @@
         <v>48</v>
       </c>
       <c r="AM2">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
         <v>15</v>
       </c>
       <c r="AO2">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
         <v>12.5</v>
       </c>
       <c r="AR2">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="AS2">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AT2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU2">
         <v>7.4</v>
       </c>
       <c r="AV2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW2">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="AX2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY2">
         <v>9.6</v>
@@ -1126,7 +1153,7 @@
         <v>17</v>
       </c>
       <c r="BA2">
-        <v>9.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="BB2">
         <v>17.5</v>
@@ -1135,16 +1162,16 @@
         <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BF2">
         <v>12.5</v>
       </c>
       <c r="BG2">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BH2">
         <v>3.3</v>
@@ -1207,7 +1234,7 @@
         <v>10</v>
       </c>
       <c r="CB2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1215,19 +1242,19 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G3">
         <v>1.68</v>
@@ -1242,7 +1269,7 @@
         <v>4.3</v>
       </c>
       <c r="K3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L3">
         <v>1.31</v>
@@ -1251,10 +1278,10 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="O3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P3">
         <v>2.22</v>
@@ -1263,10 +1290,10 @@
         <v>1.72</v>
       </c>
       <c r="R3">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S3">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="T3">
         <v>1.73</v>
@@ -1359,7 +1386,7 @@
         <v>3.1</v>
       </c>
       <c r="AX3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY3">
         <v>7.8</v>
@@ -1371,10 +1398,10 @@
         <v>3.1</v>
       </c>
       <c r="BB3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD3">
         <v>18.5</v>
@@ -1449,7 +1476,7 @@
         <v>2.42</v>
       </c>
       <c r="CB3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1457,22 +1484,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F4">
         <v>1.1</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H4">
         <v>1.1</v>
@@ -1481,7 +1508,7 @@
         <v>1000</v>
       </c>
       <c r="J4">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1493,16 +1520,16 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O4">
         <v>1.33</v>
       </c>
       <c r="P4">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Q4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R4">
         <v>1.08</v>
@@ -1691,7 +1718,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1699,16 +1726,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F5">
         <v>1.1</v>
@@ -1933,7 +1960,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1941,22 +1968,22 @@
         <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F6">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G6">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H6">
         <v>5.9</v>
@@ -1965,7 +1992,7 @@
         <v>6.4</v>
       </c>
       <c r="J6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K6">
         <v>4.3</v>
@@ -1977,7 +2004,7 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="O6">
         <v>1.28</v>
@@ -1989,10 +2016,10 @@
         <v>1.96</v>
       </c>
       <c r="R6">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S6">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="T6">
         <v>1.96</v>
@@ -2004,115 +2031,115 @@
         <v>1.18</v>
       </c>
       <c r="W6">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="X6">
-        <v>50</v>
+        <v>15.5</v>
       </c>
       <c r="Y6">
+        <v>19.5</v>
+      </c>
+      <c r="Z6">
+        <v>55</v>
+      </c>
+      <c r="AA6">
+        <v>210</v>
+      </c>
+      <c r="AB6">
+        <v>8.4</v>
+      </c>
+      <c r="AC6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD6">
+        <v>24</v>
+      </c>
+      <c r="AE6">
+        <v>110</v>
+      </c>
+      <c r="AF6">
+        <v>9.6</v>
+      </c>
+      <c r="AG6">
+        <v>10.5</v>
+      </c>
+      <c r="AH6">
         <v>23</v>
       </c>
-      <c r="Z6">
-        <v>60</v>
-      </c>
-      <c r="AA6">
-        <v>1000</v>
-      </c>
-      <c r="AB6">
+      <c r="AI6">
+        <v>100</v>
+      </c>
+      <c r="AJ6">
+        <v>16.5</v>
+      </c>
+      <c r="AK6">
+        <v>18.5</v>
+      </c>
+      <c r="AL6">
+        <v>46</v>
+      </c>
+      <c r="AM6">
+        <v>160</v>
+      </c>
+      <c r="AN6">
+        <v>10</v>
+      </c>
+      <c r="AO6">
+        <v>140</v>
+      </c>
+      <c r="AP6">
+        <v>13</v>
+      </c>
+      <c r="AQ6">
+        <v>16.5</v>
+      </c>
+      <c r="AR6">
+        <v>10.5</v>
+      </c>
+      <c r="AS6">
+        <v>12.5</v>
+      </c>
+      <c r="AT6">
+        <v>7.4</v>
+      </c>
+      <c r="AU6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV6">
+        <v>20</v>
+      </c>
+      <c r="AW6">
+        <v>11.5</v>
+      </c>
+      <c r="AX6">
+        <v>8.6</v>
+      </c>
+      <c r="AY6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ6">
+        <v>19.5</v>
+      </c>
+      <c r="BA6">
+        <v>11.5</v>
+      </c>
+      <c r="BB6">
+        <v>14</v>
+      </c>
+      <c r="BC6">
+        <v>16</v>
+      </c>
+      <c r="BD6">
         <v>9.800000000000001</v>
       </c>
-      <c r="AC6">
+      <c r="BE6">
         <v>12</v>
       </c>
-      <c r="AD6">
-        <v>29</v>
-      </c>
-      <c r="AE6">
-        <v>1000</v>
-      </c>
-      <c r="AF6">
-        <v>11</v>
-      </c>
-      <c r="AG6">
-        <v>13</v>
-      </c>
-      <c r="AH6">
-        <v>28</v>
-      </c>
-      <c r="AI6">
-        <v>1000</v>
-      </c>
-      <c r="AJ6">
-        <v>20</v>
-      </c>
-      <c r="AK6">
-        <v>25</v>
-      </c>
-      <c r="AL6">
-        <v>48</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>11.5</v>
-      </c>
-      <c r="AO6">
-        <v>1000</v>
-      </c>
-      <c r="AP6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ6">
-        <v>14.5</v>
-      </c>
-      <c r="AR6">
-        <v>3.2</v>
-      </c>
-      <c r="AS6">
-        <v>3.45</v>
-      </c>
-      <c r="AT6">
-        <v>6.2</v>
-      </c>
-      <c r="AU6">
-        <v>7.6</v>
-      </c>
-      <c r="AV6">
-        <v>15</v>
-      </c>
-      <c r="AW6">
-        <v>3.45</v>
-      </c>
-      <c r="AX6">
-        <v>7.4</v>
-      </c>
-      <c r="AY6">
-        <v>8</v>
-      </c>
-      <c r="AZ6">
-        <v>14</v>
-      </c>
-      <c r="BA6">
-        <v>3.45</v>
-      </c>
-      <c r="BB6">
-        <v>12.5</v>
-      </c>
-      <c r="BC6">
-        <v>14</v>
-      </c>
-      <c r="BD6">
-        <v>3.2</v>
-      </c>
-      <c r="BE6">
-        <v>3.45</v>
-      </c>
       <c r="BF6">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BG6">
-        <v>3.45</v>
+        <v>12</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2175,7 +2202,7 @@
         <v>2.34</v>
       </c>
       <c r="CB6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2183,34 +2210,34 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H7">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I7">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="J7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="K7">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
         <v>1.49</v>
@@ -2219,22 +2246,22 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="O7">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P7">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="Q7">
         <v>2.42</v>
       </c>
       <c r="R7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S7">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2243,10 +2270,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W7">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2417,7 +2444,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2425,267 +2452,267 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F8">
-        <v>3.2</v>
+        <v>1.93</v>
       </c>
       <c r="G8">
-        <v>4.3</v>
+        <v>2.12</v>
       </c>
       <c r="H8">
-        <v>2.12</v>
+        <v>4.8</v>
       </c>
       <c r="I8">
-        <v>2.68</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L8">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2.18</v>
+        <v>2.54</v>
       </c>
       <c r="O8">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="P8">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="Q8">
         <v>2.58</v>
       </c>
       <c r="R8">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="S8">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V8">
+        <v>1.2</v>
+      </c>
+      <c r="W8">
+        <v>1.89</v>
+      </c>
+      <c r="X8">
+        <v>11</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC8">
+        <v>9.4</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>11</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>85</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8">
+        <v>10</v>
+      </c>
+      <c r="AR8">
+        <v>1.03</v>
+      </c>
+      <c r="AS8">
+        <v>1.03</v>
+      </c>
+      <c r="AT8">
+        <v>1.03</v>
+      </c>
+      <c r="AU8">
+        <v>1.03</v>
+      </c>
+      <c r="AV8">
+        <v>1.03</v>
+      </c>
+      <c r="AW8">
+        <v>1.03</v>
+      </c>
+      <c r="AX8">
+        <v>1.03</v>
+      </c>
+      <c r="AY8">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8">
+        <v>1.03</v>
+      </c>
+      <c r="BA8">
+        <v>1.03</v>
+      </c>
+      <c r="BB8">
+        <v>1.03</v>
+      </c>
+      <c r="BC8">
+        <v>1.03</v>
+      </c>
+      <c r="BD8">
+        <v>1.03</v>
+      </c>
+      <c r="BE8">
+        <v>1.03</v>
+      </c>
+      <c r="BF8">
+        <v>17.5</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.26</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.48</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.48</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
         <v>1.6</v>
       </c>
-      <c r="W8">
-        <v>1.3</v>
-      </c>
-      <c r="X8">
-        <v>12</v>
-      </c>
-      <c r="Y8">
-        <v>1000</v>
-      </c>
-      <c r="Z8">
-        <v>1000</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
-        <v>1000</v>
-      </c>
-      <c r="AC8">
-        <v>1000</v>
-      </c>
-      <c r="AD8">
-        <v>1000</v>
-      </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
-        <v>1000</v>
-      </c>
-      <c r="AG8">
-        <v>1000</v>
-      </c>
-      <c r="AH8">
-        <v>1000</v>
-      </c>
-      <c r="AI8">
-        <v>1000</v>
-      </c>
-      <c r="AJ8">
-        <v>1000</v>
-      </c>
-      <c r="AK8">
-        <v>1000</v>
-      </c>
-      <c r="AL8">
-        <v>1000</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>1000</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>1.01</v>
-      </c>
-      <c r="AQ8">
-        <v>1.01</v>
-      </c>
-      <c r="AR8">
-        <v>1.01</v>
-      </c>
-      <c r="AS8">
-        <v>1.01</v>
-      </c>
-      <c r="AT8">
-        <v>1.01</v>
-      </c>
-      <c r="AU8">
-        <v>1.01</v>
-      </c>
-      <c r="AV8">
-        <v>1.01</v>
-      </c>
-      <c r="AW8">
-        <v>1.01</v>
-      </c>
-      <c r="AX8">
-        <v>1.01</v>
-      </c>
-      <c r="AY8">
-        <v>1.01</v>
-      </c>
-      <c r="AZ8">
-        <v>1.01</v>
-      </c>
-      <c r="BA8">
-        <v>1.01</v>
-      </c>
-      <c r="BB8">
-        <v>1.01</v>
-      </c>
-      <c r="BC8">
-        <v>1.01</v>
-      </c>
-      <c r="BD8">
-        <v>1.01</v>
-      </c>
-      <c r="BE8">
-        <v>1.01</v>
-      </c>
-      <c r="BF8">
-        <v>1.01</v>
-      </c>
-      <c r="BG8">
-        <v>1.01</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
-        <v>1.01</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.01</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
-      <c r="BO8">
-        <v>1.01</v>
-      </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="CB8" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F9">
-        <v>2.02</v>
+        <v>1.1</v>
       </c>
       <c r="G9">
-        <v>2.3</v>
+        <v>600</v>
       </c>
       <c r="H9">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="I9">
         <v>870</v>
@@ -2694,7 +2721,7 @@
         <v>1.12</v>
       </c>
       <c r="K9">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2703,22 +2730,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.58</v>
+        <v>1.09</v>
       </c>
       <c r="O9">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="P9">
-        <v>1.53</v>
+        <v>1.09</v>
       </c>
       <c r="Q9">
-        <v>2.56</v>
+        <v>1.62</v>
       </c>
       <c r="R9">
         <v>1.08</v>
       </c>
       <c r="S9">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2727,10 +2754,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2787,52 +2814,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2844,141 +2871,141 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F10">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="G10">
-        <v>600</v>
+        <v>4.4</v>
       </c>
       <c r="H10">
-        <v>1.1</v>
+        <v>2.18</v>
       </c>
       <c r="I10">
-        <v>870</v>
+        <v>2.68</v>
       </c>
       <c r="J10">
-        <v>1.1</v>
+        <v>2.56</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M10">
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.07</v>
+        <v>2.18</v>
       </c>
       <c r="O10">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="P10">
-        <v>1.06</v>
+        <v>1.46</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="R10">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="S10">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z10">
         <v>1000</v>
@@ -2990,7 +3017,7 @@
         <v>1000</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD10">
         <v>1000</v>
@@ -3029,52 +3056,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3086,7 +3113,7 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
@@ -3122,7 +3149,7 @@
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV10">
         <v>1000</v>
@@ -3143,7 +3170,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3151,31 +3178,31 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F11">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="G11">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="H11">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="I11">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="J11">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K11">
         <v>3.65</v>
@@ -3196,55 +3223,55 @@
         <v>2.04</v>
       </c>
       <c r="Q11">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="R11">
         <v>1.41</v>
       </c>
       <c r="S11">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T11">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U11">
         <v>2.24</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W11">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="X11">
         <v>21</v>
       </c>
       <c r="Y11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z11">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB11">
         <v>12.5</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF11">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AG11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH11">
         <v>17</v>
@@ -3265,10 +3292,10 @@
         <v>100</v>
       </c>
       <c r="AN11">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AO11">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP11">
         <v>14</v>
@@ -3280,7 +3307,7 @@
         <v>18.5</v>
       </c>
       <c r="AS11">
-        <v>34</v>
+        <v>7.2</v>
       </c>
       <c r="AT11">
         <v>10</v>
@@ -3295,34 +3322,34 @@
         <v>23</v>
       </c>
       <c r="AX11">
+        <v>14.5</v>
+      </c>
+      <c r="AY11">
+        <v>10</v>
+      </c>
+      <c r="AZ11">
         <v>14</v>
-      </c>
-      <c r="AY11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ11">
-        <v>13.5</v>
       </c>
       <c r="BA11">
         <v>28</v>
       </c>
       <c r="BB11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC11">
         <v>21</v>
       </c>
       <c r="BD11">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BE11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF11">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BG11">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH11">
         <v>4.2</v>
@@ -3334,13 +3361,13 @@
         <v>13</v>
       </c>
       <c r="BK11">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
         <v>7.8</v>
@@ -3352,13 +3379,13 @@
         <v>25</v>
       </c>
       <c r="BQ11">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
         <v>40</v>
       </c>
       <c r="BS11">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
         <v>9</v>
@@ -3370,22 +3397,22 @@
         <v>34</v>
       </c>
       <c r="BW11">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
         <v>48</v>
       </c>
       <c r="BY11">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
         <v>34</v>
       </c>
       <c r="CA11">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3393,241 +3420,241 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F12">
-        <v>1.1</v>
+        <v>2.54</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H12">
-        <v>1.1</v>
+        <v>2.74</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="J12">
-        <v>1.1</v>
+        <v>2.46</v>
       </c>
       <c r="K12">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P12">
-        <v>1.07</v>
+        <v>1.48</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="CB12" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3635,725 +3662,1451 @@
         <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F13">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="G13">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="H13">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J13">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="K13">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P13">
-        <v>1.07</v>
+        <v>1.78</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F14">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="G14">
-        <v>600</v>
+        <v>3.9</v>
       </c>
       <c r="H14">
-        <v>1.1</v>
+        <v>2.12</v>
       </c>
       <c r="I14">
-        <v>870</v>
+        <v>2.38</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P14">
-        <v>1.07</v>
+        <v>1.95</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F15">
+        <v>1.91</v>
+      </c>
+      <c r="G15">
+        <v>2.34</v>
+      </c>
+      <c r="H15">
+        <v>3.85</v>
+      </c>
+      <c r="I15">
+        <v>6.4</v>
+      </c>
+      <c r="J15">
+        <v>2.86</v>
+      </c>
+      <c r="K15">
+        <v>3.25</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>2.36</v>
+      </c>
+      <c r="O15">
+        <v>1.6</v>
+      </c>
+      <c r="P15">
+        <v>1.37</v>
+      </c>
+      <c r="Q15">
+        <v>2.28</v>
+      </c>
+      <c r="R15">
+        <v>1.08</v>
+      </c>
+      <c r="S15">
+        <v>2.28</v>
+      </c>
+      <c r="T15">
+        <v>1.01</v>
+      </c>
+      <c r="U15">
+        <v>1.01</v>
+      </c>
+      <c r="V15">
+        <v>1.19</v>
+      </c>
+      <c r="W15">
+        <v>1.74</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15">
+        <v>1.01</v>
+      </c>
+      <c r="AR15">
+        <v>1.01</v>
+      </c>
+      <c r="AS15">
+        <v>1.01</v>
+      </c>
+      <c r="AT15">
+        <v>1.01</v>
+      </c>
+      <c r="AU15">
+        <v>1.01</v>
+      </c>
+      <c r="AV15">
+        <v>1.01</v>
+      </c>
+      <c r="AW15">
+        <v>1.01</v>
+      </c>
+      <c r="AX15">
+        <v>1.01</v>
+      </c>
+      <c r="AY15">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15">
+        <v>1.01</v>
+      </c>
+      <c r="BA15">
+        <v>1.01</v>
+      </c>
+      <c r="BB15">
+        <v>1.01</v>
+      </c>
+      <c r="BC15">
+        <v>1.01</v>
+      </c>
+      <c r="BD15">
+        <v>1.01</v>
+      </c>
+      <c r="BE15">
+        <v>1.01</v>
+      </c>
+      <c r="BF15">
+        <v>1.01</v>
+      </c>
+      <c r="BG15">
+        <v>1.01</v>
+      </c>
+      <c r="BH15">
+        <v>2.94</v>
+      </c>
+      <c r="BI15">
+        <v>2.06</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.01</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.01</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F16">
+        <v>1.38</v>
+      </c>
+      <c r="G16">
+        <v>1.44</v>
+      </c>
+      <c r="H16">
+        <v>7.2</v>
+      </c>
+      <c r="I16">
+        <v>11</v>
+      </c>
+      <c r="J16">
+        <v>4.9</v>
+      </c>
+      <c r="K16">
+        <v>5.7</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1.07</v>
+      </c>
+      <c r="Q16">
+        <v>1.63</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
         <v>84</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17">
+        <v>1.1</v>
+      </c>
+      <c r="G17">
+        <v>1000</v>
+      </c>
+      <c r="H17">
+        <v>1.1</v>
+      </c>
+      <c r="I17">
+        <v>1000</v>
+      </c>
+      <c r="J17">
+        <v>1.1</v>
+      </c>
+      <c r="K17">
+        <v>950</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>1.36</v>
+      </c>
+      <c r="O17">
+        <v>1.01</v>
+      </c>
+      <c r="P17">
+        <v>1.36</v>
+      </c>
+      <c r="Q17">
+        <v>2.32</v>
+      </c>
+      <c r="R17">
+        <v>1.05</v>
+      </c>
+      <c r="S17">
+        <v>2.48</v>
+      </c>
+      <c r="T17">
+        <v>1.01</v>
+      </c>
+      <c r="U17">
+        <v>1.01</v>
+      </c>
+      <c r="V17">
+        <v>1.4</v>
+      </c>
+      <c r="W17">
+        <v>1.33</v>
+      </c>
+      <c r="X17">
+        <v>1000</v>
+      </c>
+      <c r="Y17">
+        <v>1000</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>1000</v>
+      </c>
+      <c r="AC17">
+        <v>1000</v>
+      </c>
+      <c r="AD17">
+        <v>1000</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>1000</v>
+      </c>
+      <c r="AG17">
+        <v>1000</v>
+      </c>
+      <c r="AH17">
+        <v>1000</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17">
+        <v>1.01</v>
+      </c>
+      <c r="AR17">
+        <v>1.01</v>
+      </c>
+      <c r="AS17">
+        <v>1.01</v>
+      </c>
+      <c r="AT17">
+        <v>1.01</v>
+      </c>
+      <c r="AU17">
+        <v>1.01</v>
+      </c>
+      <c r="AV17">
+        <v>1.01</v>
+      </c>
+      <c r="AW17">
+        <v>1.01</v>
+      </c>
+      <c r="AX17">
+        <v>1.01</v>
+      </c>
+      <c r="AY17">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17">
+        <v>1.01</v>
+      </c>
+      <c r="BA17">
+        <v>1.01</v>
+      </c>
+      <c r="BB17">
+        <v>1.01</v>
+      </c>
+      <c r="BC17">
+        <v>1.01</v>
+      </c>
+      <c r="BD17">
+        <v>1.01</v>
+      </c>
+      <c r="BE17">
+        <v>1.01</v>
+      </c>
+      <c r="BF17">
+        <v>1.01</v>
+      </c>
+      <c r="BG17">
+        <v>1.01</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.01</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.01</v>
+      </c>
+      <c r="BN17">
+        <v>1000</v>
+      </c>
+      <c r="BO17">
+        <v>1.01</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>1.01</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.01</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>1.01</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.01</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
         <v>88</v>
       </c>
-      <c r="C15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" t="s">
-        <v>124</v>
-      </c>
-      <c r="F15">
-        <v>1.1</v>
-      </c>
-      <c r="G15">
-        <v>1000</v>
-      </c>
-      <c r="H15">
-        <v>1.1</v>
-      </c>
-      <c r="I15">
-        <v>1000</v>
-      </c>
-      <c r="J15">
-        <v>1.1</v>
-      </c>
-      <c r="K15">
-        <v>950</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>1.07</v>
-      </c>
-      <c r="Q15">
-        <v>1.01</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <v>0</v>
-      </c>
-      <c r="AJ15">
-        <v>0</v>
-      </c>
-      <c r="AK15">
-        <v>0</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>0</v>
-      </c>
-      <c r="AO15">
-        <v>0</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>0</v>
-      </c>
-      <c r="BC15">
-        <v>0</v>
-      </c>
-      <c r="BD15">
-        <v>0</v>
-      </c>
-      <c r="BE15">
-        <v>0</v>
-      </c>
-      <c r="BF15">
-        <v>0</v>
-      </c>
-      <c r="BG15">
-        <v>0</v>
-      </c>
-      <c r="BH15">
-        <v>0</v>
-      </c>
-      <c r="BI15">
-        <v>0</v>
-      </c>
-      <c r="BJ15">
-        <v>0</v>
-      </c>
-      <c r="BK15">
-        <v>0</v>
-      </c>
-      <c r="BL15">
-        <v>0</v>
-      </c>
-      <c r="BM15">
-        <v>0</v>
-      </c>
-      <c r="BN15">
-        <v>0</v>
-      </c>
-      <c r="BO15">
-        <v>0</v>
-      </c>
-      <c r="BP15">
-        <v>0</v>
-      </c>
-      <c r="BQ15">
-        <v>0</v>
-      </c>
-      <c r="BR15">
-        <v>0</v>
-      </c>
-      <c r="BS15">
-        <v>0</v>
-      </c>
-      <c r="BT15">
-        <v>0</v>
-      </c>
-      <c r="BU15">
-        <v>0</v>
-      </c>
-      <c r="BV15">
-        <v>0</v>
-      </c>
-      <c r="BW15">
-        <v>0</v>
-      </c>
-      <c r="BX15">
-        <v>0</v>
-      </c>
-      <c r="BY15">
-        <v>0</v>
-      </c>
-      <c r="BZ15">
-        <v>0</v>
-      </c>
-      <c r="CA15">
-        <v>0</v>
-      </c>
-      <c r="CB15" t="s">
-        <v>125</v>
+      <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" t="s">
+        <v>133</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.04</v>
+      </c>
+      <c r="Q18">
+        <v>1.01</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
@@ -418,7 +418,7 @@
     <t>CD Los Chankas</t>
   </si>
   <si>
-    <t>2026-10-06 17:13:21</t>
+    <t>2026-10-06 19:24:56</t>
   </si>
 </sst>
 </file>
@@ -1012,10 +1012,10 @@
         <v>117</v>
       </c>
       <c r="F2">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H2">
         <v>4.3</v>
@@ -1024,10 +1024,10 @@
         <v>4.6</v>
       </c>
       <c r="J2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -1036,82 +1036,82 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="V2">
         <v>1.27</v>
       </c>
       <c r="W2">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA2">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC2">
         <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE2">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ2">
         <v>24</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN2">
         <v>15</v>
@@ -1120,10 +1120,10 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR2">
         <v>22</v>
@@ -1132,16 +1132,16 @@
         <v>60</v>
       </c>
       <c r="AT2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
@@ -1150,13 +1150,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA2">
         <v>46</v>
       </c>
       <c r="BB2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC2">
         <v>18.5</v>
@@ -1165,7 +1165,7 @@
         <v>29</v>
       </c>
       <c r="BE2">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BF2">
         <v>12.5</v>
@@ -1535,7 +1535,7 @@
         <v>1.08</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1992,7 +1992,7 @@
         <v>6.4</v>
       </c>
       <c r="J6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K6">
         <v>4.3</v>
@@ -2010,7 +2010,7 @@
         <v>1.28</v>
       </c>
       <c r="P6">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q6">
         <v>1.96</v>
@@ -2040,7 +2040,7 @@
         <v>19.5</v>
       </c>
       <c r="Z6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA6">
         <v>210</v>
@@ -2222,7 +2222,7 @@
         <v>122</v>
       </c>
       <c r="F7">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="G7">
         <v>4.8</v>
@@ -2237,7 +2237,7 @@
         <v>2.68</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="L7">
         <v>1.49</v>
@@ -2246,22 +2246,22 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>2.32</v>
+        <v>2.68</v>
       </c>
       <c r="O7">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="P7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q7">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="S7">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2464,16 +2464,16 @@
         <v>123</v>
       </c>
       <c r="F8">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="G8">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H8">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J8">
         <v>3.1</v>
@@ -2488,22 +2488,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="O8">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P8">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q8">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="R8">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="S8">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="T8">
         <v>2.24</v>
@@ -2515,10 +2515,10 @@
         <v>1.2</v>
       </c>
       <c r="W8">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="X8">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
         <v>1000</v>
@@ -2530,7 +2530,7 @@
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
         <v>9.4</v>
@@ -2542,7 +2542,7 @@
         <v>1000</v>
       </c>
       <c r="AF8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG8">
         <v>1000</v>
@@ -2584,7 +2584,7 @@
         <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AU8">
         <v>1.03</v>
@@ -2629,7 +2629,7 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="BP8">
         <v>1000</v>
@@ -2754,10 +2754,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2948,25 +2948,25 @@
         <v>125</v>
       </c>
       <c r="F10">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G10">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="H10">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="I10">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J10">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="K10">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L10">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="M10">
         <v>1.01</v>
@@ -2975,13 +2975,13 @@
         <v>2.18</v>
       </c>
       <c r="O10">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="P10">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="Q10">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="R10">
         <v>1.12</v>
@@ -2990,22 +2990,22 @@
         <v>4</v>
       </c>
       <c r="T10">
-        <v>2.08</v>
+        <v>1.02</v>
       </c>
       <c r="U10">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
         <v>1.6</v>
       </c>
       <c r="W10">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X10">
         <v>12</v>
       </c>
       <c r="Y10">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
         <v>1000</v>
@@ -3017,7 +3017,7 @@
         <v>1000</v>
       </c>
       <c r="AC10">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
         <v>1000</v>
@@ -3113,7 +3113,7 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
@@ -3149,7 +3149,7 @@
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
         <v>1000</v>
@@ -3190,25 +3190,25 @@
         <v>126</v>
       </c>
       <c r="F11">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G11">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H11">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I11">
         <v>3.15</v>
       </c>
       <c r="J11">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K11">
         <v>3.65</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M11">
         <v>1.06</v>
@@ -3223,13 +3223,13 @@
         <v>2.04</v>
       </c>
       <c r="Q11">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="R11">
         <v>1.41</v>
       </c>
       <c r="S11">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T11">
         <v>1.67</v>
@@ -3238,10 +3238,10 @@
         <v>2.24</v>
       </c>
       <c r="V11">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W11">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X11">
         <v>21</v>
@@ -3268,7 +3268,7 @@
         <v>34</v>
       </c>
       <c r="AF11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG11">
         <v>12</v>
@@ -3307,7 +3307,7 @@
         <v>18.5</v>
       </c>
       <c r="AS11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT11">
         <v>10</v>
@@ -3319,7 +3319,7 @@
         <v>11.5</v>
       </c>
       <c r="AW11">
-        <v>23</v>
+        <v>6.8</v>
       </c>
       <c r="AX11">
         <v>14.5</v>
@@ -3331,10 +3331,10 @@
         <v>14</v>
       </c>
       <c r="BA11">
-        <v>28</v>
+        <v>7.2</v>
       </c>
       <c r="BB11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC11">
         <v>21</v>
@@ -3343,7 +3343,7 @@
         <v>30</v>
       </c>
       <c r="BE11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF11">
         <v>16</v>
@@ -3361,13 +3361,13 @@
         <v>13</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BN11">
         <v>7.8</v>
@@ -3379,13 +3379,13 @@
         <v>25</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BR11">
         <v>40</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BT11">
         <v>9</v>
@@ -3397,19 +3397,19 @@
         <v>34</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BX11">
         <v>48</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BZ11">
         <v>34</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="CB11" t="s">
         <v>134</v>
@@ -3432,58 +3432,58 @@
         <v>127</v>
       </c>
       <c r="F12">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="G12">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H12">
         <v>2.74</v>
       </c>
       <c r="I12">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J12">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="K12">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="M12">
         <v>1.08</v>
       </c>
       <c r="N12">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O12">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="P12">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
       </c>
       <c r="R12">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="S12">
-        <v>4.4</v>
+        <v>2.72</v>
       </c>
       <c r="T12">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3501,7 +3501,7 @@
         <v>1000</v>
       </c>
       <c r="AC12">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
         <v>1000</v>
@@ -3540,118 +3540,118 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
         <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
         <v>134</v>
@@ -3674,7 +3674,7 @@
         <v>128</v>
       </c>
       <c r="F13">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G13">
         <v>1.6</v>
@@ -3686,7 +3686,7 @@
         <v>11.5</v>
       </c>
       <c r="J13">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="K13">
         <v>4.7</v>
@@ -3698,13 +3698,13 @@
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="O13">
         <v>1.34</v>
       </c>
       <c r="P13">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Q13">
         <v>1.9</v>
@@ -3716,16 +3716,16 @@
         <v>2.58</v>
       </c>
       <c r="T13">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U13">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="V13">
         <v>1.09</v>
       </c>
       <c r="W13">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X13">
         <v>13</v>
@@ -3836,22 +3836,22 @@
         <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>2.38</v>
+        <v>1.29</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BN13">
         <v>1000</v>
@@ -3863,37 +3863,37 @@
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="CB13" t="s">
         <v>134</v>
@@ -3964,7 +3964,7 @@
         <v>2.14</v>
       </c>
       <c r="V14">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W14">
         <v>1.34</v>
@@ -4158,22 +4158,22 @@
         <v>130</v>
       </c>
       <c r="F15">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="G15">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="H15">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="I15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J15">
-        <v>2.86</v>
+        <v>2.68</v>
       </c>
       <c r="K15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4209,7 +4209,7 @@
         <v>1.19</v>
       </c>
       <c r="W15">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4224,10 +4224,10 @@
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD15">
         <v>1000</v>
@@ -4266,52 +4266,52 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
         <v>1.01</v>
@@ -4323,61 +4323,61 @@
         <v>2.94</v>
       </c>
       <c r="BI15">
+        <v>2.08</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
         <v>2.06</v>
       </c>
-      <c r="BJ15">
-        <v>1000</v>
-      </c>
-      <c r="BK15">
-        <v>1.01</v>
-      </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="CB15" t="s">
         <v>134</v>
@@ -4400,7 +4400,7 @@
         <v>131</v>
       </c>
       <c r="F16">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G16">
         <v>1.44</v>
@@ -4409,10 +4409,10 @@
         <v>7.2</v>
       </c>
       <c r="I16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K16">
         <v>5.7</v>
@@ -4642,22 +4642,22 @@
         <v>132</v>
       </c>
       <c r="F17">
-        <v>1.1</v>
+        <v>2.58</v>
       </c>
       <c r="G17">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H17">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="I17">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J17">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="K17">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4666,34 +4666,34 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.36</v>
+        <v>2.16</v>
       </c>
       <c r="O17">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="P17">
         <v>1.36</v>
       </c>
       <c r="Q17">
-        <v>2.32</v>
+        <v>2.58</v>
       </c>
       <c r="R17">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="S17">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W17">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4750,52 +4750,52 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17">
         <v>1.01</v>
@@ -4804,64 +4804,64 @@
         <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="CB17" t="s">
         <v>134</v>
@@ -4884,226 +4884,226 @@
         <v>133</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P18">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
         <v>134</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
@@ -418,7 +418,7 @@
     <t>CD Los Chankas</t>
   </si>
   <si>
-    <t>2026-10-06 19:24:56</t>
+    <t>2026-10-06 21:37:21</t>
   </si>
 </sst>
 </file>
@@ -1012,31 +1012,31 @@
         <v>117</v>
       </c>
       <c r="F2">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="G2">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I2">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J2">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
         <v>1.44</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O2">
         <v>1.34</v>
@@ -1054,7 +1054,7 @@
         <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U2">
         <v>2.12</v>
@@ -1063,7 +1063,7 @@
         <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="X2">
         <v>14.5</v>
@@ -1075,70 +1075,70 @@
         <v>38</v>
       </c>
       <c r="AA2">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2">
         <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE2">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI2">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
         <v>24</v>
       </c>
       <c r="AK2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL2">
         <v>46</v>
       </c>
       <c r="AM2">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AS2">
         <v>60</v>
       </c>
       <c r="AT2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU2">
         <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW2">
         <v>40</v>
@@ -1147,31 +1147,31 @@
         <v>10.5</v>
       </c>
       <c r="AY2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA2">
         <v>46</v>
       </c>
       <c r="BB2">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BC2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF2">
         <v>12.5</v>
       </c>
       <c r="BG2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH2">
         <v>3.3</v>
@@ -1278,13 +1278,13 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O3">
         <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q3">
         <v>1.72</v>
@@ -1499,13 +1499,13 @@
         <v>1.1</v>
       </c>
       <c r="G4">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H4">
         <v>1.1</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J4">
         <v>1.12</v>
@@ -1529,25 +1529,25 @@
         <v>1.13</v>
       </c>
       <c r="Q4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R4">
         <v>1.08</v>
       </c>
       <c r="S4">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W4">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1992,7 +1992,7 @@
         <v>6.4</v>
       </c>
       <c r="J6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K6">
         <v>4.3</v>
@@ -2231,7 +2231,7 @@
         <v>2.16</v>
       </c>
       <c r="I7">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J7">
         <v>2.68</v>
@@ -2270,7 +2270,7 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W7">
         <v>1.27</v>
@@ -2464,13 +2464,13 @@
         <v>123</v>
       </c>
       <c r="F8">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="G8">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I8">
         <v>6.2</v>
@@ -2506,7 +2506,7 @@
         <v>1.01</v>
       </c>
       <c r="T8">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U8">
         <v>1.7</v>
@@ -2575,52 +2575,52 @@
         <v>1.03</v>
       </c>
       <c r="AQ8">
+        <v>1.03</v>
+      </c>
+      <c r="AR8">
+        <v>1.03</v>
+      </c>
+      <c r="AS8">
+        <v>1.03</v>
+      </c>
+      <c r="AT8">
+        <v>1.03</v>
+      </c>
+      <c r="AU8">
+        <v>1.03</v>
+      </c>
+      <c r="AV8">
+        <v>1.03</v>
+      </c>
+      <c r="AW8">
+        <v>1.03</v>
+      </c>
+      <c r="AX8">
+        <v>1.03</v>
+      </c>
+      <c r="AY8">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8">
+        <v>1.03</v>
+      </c>
+      <c r="BA8">
+        <v>1.03</v>
+      </c>
+      <c r="BB8">
+        <v>1.03</v>
+      </c>
+      <c r="BC8">
+        <v>1.03</v>
+      </c>
+      <c r="BD8">
+        <v>1.03</v>
+      </c>
+      <c r="BE8">
+        <v>1.03</v>
+      </c>
+      <c r="BF8">
         <v>10</v>
-      </c>
-      <c r="AR8">
-        <v>1.03</v>
-      </c>
-      <c r="AS8">
-        <v>1.03</v>
-      </c>
-      <c r="AT8">
-        <v>5.4</v>
-      </c>
-      <c r="AU8">
-        <v>1.03</v>
-      </c>
-      <c r="AV8">
-        <v>1.03</v>
-      </c>
-      <c r="AW8">
-        <v>1.03</v>
-      </c>
-      <c r="AX8">
-        <v>1.03</v>
-      </c>
-      <c r="AY8">
-        <v>1.03</v>
-      </c>
-      <c r="AZ8">
-        <v>1.03</v>
-      </c>
-      <c r="BA8">
-        <v>1.03</v>
-      </c>
-      <c r="BB8">
-        <v>1.03</v>
-      </c>
-      <c r="BC8">
-        <v>1.03</v>
-      </c>
-      <c r="BD8">
-        <v>1.03</v>
-      </c>
-      <c r="BE8">
-        <v>1.03</v>
-      </c>
-      <c r="BF8">
-        <v>17.5</v>
       </c>
       <c r="BG8">
         <v>1.01</v>
@@ -2709,13 +2709,13 @@
         <v>1.1</v>
       </c>
       <c r="G9">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H9">
         <v>1.1</v>
       </c>
       <c r="I9">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J9">
         <v>1.12</v>
@@ -2730,7 +2730,7 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O9">
         <v>1.02</v>
@@ -2748,16 +2748,16 @@
         <v>1.62</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
         <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3193,7 +3193,7 @@
         <v>2.52</v>
       </c>
       <c r="G11">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H11">
         <v>2.88</v>
@@ -3677,19 +3677,19 @@
         <v>1.46</v>
       </c>
       <c r="G13">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H13">
         <v>8</v>
       </c>
       <c r="I13">
-        <v>11.5</v>
+        <v>140</v>
       </c>
       <c r="J13">
         <v>3.9</v>
       </c>
       <c r="K13">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3701,7 +3701,7 @@
         <v>2.64</v>
       </c>
       <c r="O13">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P13">
         <v>1.65</v>
@@ -3722,7 +3722,7 @@
         <v>1.6</v>
       </c>
       <c r="V13">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="W13">
         <v>2.62</v>
@@ -3782,58 +3782,58 @@
         <v>330</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4400,22 +4400,22 @@
         <v>131</v>
       </c>
       <c r="F16">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="G16">
         <v>1.44</v>
       </c>
       <c r="H16">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="I16">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J16">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4884,31 +4884,31 @@
         <v>133</v>
       </c>
       <c r="F18">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="G18">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="H18">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I18">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K18">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O18">
         <v>1.29</v>
@@ -4920,22 +4920,22 @@
         <v>1.74</v>
       </c>
       <c r="R18">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S18">
         <v>2.5</v>
       </c>
       <c r="T18">
-        <v>1.02</v>
+        <v>1.84</v>
       </c>
       <c r="U18">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="V18">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W18">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5004,10 +5004,10 @@
         <v>1.03</v>
       </c>
       <c r="AT18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
         <v>1.03</v>
@@ -5016,10 +5016,10 @@
         <v>1.03</v>
       </c>
       <c r="AX18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
         <v>1.03</v>
@@ -5028,7 +5028,7 @@
         <v>1.03</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
         <v>1.03</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="141">
   <si>
     <t>League</t>
   </si>
@@ -259,6 +259,9 @@
     <t>Brazilian Serie A</t>
   </si>
   <si>
+    <t>Qatari Stars League</t>
+  </si>
+  <si>
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
@@ -271,12 +274,12 @@
     <t>Moroccan Botola Pro 1</t>
   </si>
   <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>Algerian Ligue 1</t>
   </si>
   <si>
-    <t>Ecuadorian Serie B</t>
-  </si>
-  <si>
     <t>Romanian Liga I</t>
   </si>
   <si>
@@ -292,6 +295,9 @@
     <t>00:30:00</t>
   </si>
   <si>
+    <t>14:45:00</t>
+  </si>
+  <si>
     <t>15:00:00</t>
   </si>
   <si>
@@ -319,6 +325,9 @@
     <t>Cruzeiro MG</t>
   </si>
   <si>
+    <t>Al Shamal</t>
+  </si>
+  <si>
     <t>HJK Helsinki</t>
   </si>
   <si>
@@ -334,15 +343,18 @@
     <t>Union de Touarga</t>
   </si>
   <si>
+    <t>Al-Wakra</t>
+  </si>
+  <si>
+    <t>Independiente Juniors</t>
+  </si>
+  <si>
+    <t>MB Rouissat</t>
+  </si>
+  <si>
     <t>JS Saoura</t>
   </si>
   <si>
-    <t>Independiente Juniors</t>
-  </si>
-  <si>
-    <t>MB Rouissat</t>
-  </si>
-  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
@@ -370,6 +382,9 @@
     <t>Sao Paulo</t>
   </si>
   <si>
+    <t>Al-Duhail SC</t>
+  </si>
+  <si>
     <t>VPS</t>
   </si>
   <si>
@@ -385,15 +400,18 @@
     <t>RSB Berkane</t>
   </si>
   <si>
+    <t>Al Gharafa</t>
+  </si>
+  <si>
+    <t>Club Nueve de Octubre</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
     <t>Olympique Akbou</t>
   </si>
   <si>
-    <t>Club Nueve de Octubre</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
@@ -418,7 +436,7 @@
     <t>CD Los Chankas</t>
   </si>
   <si>
-    <t>2026-10-06 21:37:21</t>
+    <t>2026-10-06 23:49:07</t>
   </si>
 </sst>
 </file>
@@ -750,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1000,34 +1018,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F2">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G2">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="H2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2">
         <v>3.7</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -1042,7 +1060,7 @@
         <v>1.34</v>
       </c>
       <c r="P2">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q2">
         <v>2.02</v>
@@ -1051,25 +1069,25 @@
         <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U2">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V2">
         <v>1.27</v>
       </c>
       <c r="W2">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z2">
         <v>38</v>
@@ -1078,7 +1096,7 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC2">
         <v>8.199999999999999</v>
@@ -1087,7 +1105,7 @@
         <v>17.5</v>
       </c>
       <c r="AE2">
-        <v>520</v>
+        <v>95</v>
       </c>
       <c r="AF2">
         <v>11.5</v>
@@ -1096,7 +1114,7 @@
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI2">
         <v>1000</v>
@@ -1126,46 +1144,46 @@
         <v>14</v>
       </c>
       <c r="AR2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS2">
         <v>60</v>
       </c>
       <c r="AT2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU2">
         <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW2">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BA2">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BB2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC2">
         <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE2">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="BF2">
         <v>12.5</v>
@@ -1195,7 +1213,7 @@
         <v>4.5</v>
       </c>
       <c r="BO2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
         <v>14.5</v>
@@ -1234,7 +1252,7 @@
         <v>10</v>
       </c>
       <c r="CB2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1242,241 +1260,241 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F3">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="G3">
-        <v>1.68</v>
+        <v>1000</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="I3">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J3">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="K3">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L3">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>1.07</v>
       </c>
       <c r="O3">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="P3">
-        <v>2.28</v>
+        <v>1.07</v>
       </c>
       <c r="Q3">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="R3">
-        <v>1.45</v>
+        <v>1.07</v>
       </c>
       <c r="S3">
-        <v>2.66</v>
+        <v>1.19</v>
       </c>
       <c r="T3">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
         <v>1000</v>
       </c>
       <c r="Y3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1484,241 +1502,241 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F4">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="G4">
-        <v>990</v>
+        <v>1.68</v>
       </c>
       <c r="H4">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="I4">
-        <v>990</v>
+        <v>6.2</v>
       </c>
       <c r="J4">
-        <v>1.12</v>
+        <v>4.3</v>
       </c>
       <c r="K4">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>1.13</v>
+        <v>4.1</v>
       </c>
       <c r="O4">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="P4">
-        <v>1.13</v>
+        <v>2.22</v>
       </c>
       <c r="Q4">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="R4">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="S4">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="T4">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="U4">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V4">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="W4">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="X4">
         <v>1000</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA4">
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM4">
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AR4">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW4">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ4">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BE4">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="CB4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1726,28 +1744,28 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F5">
         <v>1.1</v>
       </c>
       <c r="G5">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H5">
         <v>1.1</v>
       </c>
       <c r="I5">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J5">
         <v>1.12</v>
@@ -1762,35 +1780,35 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="O5">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P5">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="Q5">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="R5">
+        <v>1.08</v>
+      </c>
+      <c r="S5">
+        <v>2.96</v>
+      </c>
+      <c r="T5">
+        <v>1.11</v>
+      </c>
+      <c r="U5">
+        <v>1.11</v>
+      </c>
+      <c r="V5">
+        <v>1.04</v>
+      </c>
+      <c r="W5">
         <v>1.05</v>
       </c>
-      <c r="S5">
-        <v>1.01</v>
-      </c>
-      <c r="T5">
-        <v>1.01</v>
-      </c>
-      <c r="U5">
-        <v>1.01</v>
-      </c>
-      <c r="V5">
-        <v>1.01</v>
-      </c>
-      <c r="W5">
-        <v>1.01</v>
-      </c>
       <c r="X5">
         <v>1000</v>
       </c>
@@ -1846,52 +1864,52 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5">
         <v>1.01</v>
@@ -1960,491 +1978,491 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F6">
-        <v>1.65</v>
+        <v>1.1</v>
       </c>
       <c r="G6">
-        <v>1.71</v>
+        <v>600</v>
       </c>
       <c r="H6">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="I6">
-        <v>6.4</v>
+        <v>870</v>
       </c>
       <c r="J6">
-        <v>3.9</v>
+        <v>1.12</v>
       </c>
       <c r="K6">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L6">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="O6">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="Q6">
-        <v>1.96</v>
+        <v>1.02</v>
       </c>
       <c r="R6">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="S6">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="T6">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6">
+        <v>1.01</v>
+      </c>
+      <c r="AR6">
+        <v>1.01</v>
+      </c>
+      <c r="AS6">
+        <v>1.01</v>
+      </c>
+      <c r="AT6">
+        <v>1.01</v>
+      </c>
+      <c r="AU6">
+        <v>1.01</v>
+      </c>
+      <c r="AV6">
+        <v>1.01</v>
+      </c>
+      <c r="AW6">
+        <v>1.01</v>
+      </c>
+      <c r="AX6">
+        <v>1.01</v>
+      </c>
+      <c r="AY6">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6">
+        <v>1.01</v>
+      </c>
+      <c r="BA6">
+        <v>1.01</v>
+      </c>
+      <c r="BB6">
+        <v>1.01</v>
+      </c>
+      <c r="BC6">
+        <v>1.01</v>
+      </c>
+      <c r="BD6">
+        <v>1.01</v>
+      </c>
+      <c r="BE6">
+        <v>1.01</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.01</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.01</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.01</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
         <v>140</v>
-      </c>
-      <c r="AP6">
-        <v>13</v>
-      </c>
-      <c r="AQ6">
-        <v>16.5</v>
-      </c>
-      <c r="AR6">
-        <v>10.5</v>
-      </c>
-      <c r="AS6">
-        <v>12.5</v>
-      </c>
-      <c r="AT6">
-        <v>7.4</v>
-      </c>
-      <c r="AU6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV6">
-        <v>20</v>
-      </c>
-      <c r="AW6">
-        <v>11.5</v>
-      </c>
-      <c r="AX6">
-        <v>8.6</v>
-      </c>
-      <c r="AY6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ6">
-        <v>19.5</v>
-      </c>
-      <c r="BA6">
-        <v>11.5</v>
-      </c>
-      <c r="BB6">
-        <v>14</v>
-      </c>
-      <c r="BC6">
-        <v>16</v>
-      </c>
-      <c r="BD6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE6">
-        <v>12</v>
-      </c>
-      <c r="BF6">
-        <v>9</v>
-      </c>
-      <c r="BG6">
-        <v>12</v>
-      </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
-      <c r="BI6">
-        <v>2.92</v>
-      </c>
-      <c r="BJ6">
-        <v>1000</v>
-      </c>
-      <c r="BK6">
-        <v>2.34</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>2.34</v>
-      </c>
-      <c r="BN6">
-        <v>1000</v>
-      </c>
-      <c r="BO6">
-        <v>1.57</v>
-      </c>
-      <c r="BP6">
-        <v>1000</v>
-      </c>
-      <c r="BQ6">
-        <v>2.12</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>2.34</v>
-      </c>
-      <c r="BT6">
-        <v>1000</v>
-      </c>
-      <c r="BU6">
-        <v>2.08</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>2.34</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>2.34</v>
-      </c>
-      <c r="BZ6">
-        <v>1000</v>
-      </c>
-      <c r="CA6">
-        <v>2.34</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F7">
-        <v>2.96</v>
+        <v>1.65</v>
       </c>
       <c r="G7">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="H7">
-        <v>2.16</v>
+        <v>5.9</v>
       </c>
       <c r="I7">
+        <v>6.4</v>
+      </c>
+      <c r="J7">
+        <v>3.9</v>
+      </c>
+      <c r="K7">
+        <v>4.3</v>
+      </c>
+      <c r="L7">
+        <v>1.36</v>
+      </c>
+      <c r="M7">
+        <v>1.06</v>
+      </c>
+      <c r="N7">
+        <v>3.45</v>
+      </c>
+      <c r="O7">
+        <v>1.29</v>
+      </c>
+      <c r="P7">
+        <v>1.94</v>
+      </c>
+      <c r="Q7">
+        <v>1.96</v>
+      </c>
+      <c r="R7">
+        <v>1.32</v>
+      </c>
+      <c r="S7">
+        <v>3.5</v>
+      </c>
+      <c r="T7">
+        <v>1.96</v>
+      </c>
+      <c r="U7">
+        <v>1.92</v>
+      </c>
+      <c r="V7">
+        <v>1.18</v>
+      </c>
+      <c r="W7">
+        <v>2.42</v>
+      </c>
+      <c r="X7">
+        <v>15.5</v>
+      </c>
+      <c r="Y7">
+        <v>19.5</v>
+      </c>
+      <c r="Z7">
+        <v>60</v>
+      </c>
+      <c r="AA7">
+        <v>210</v>
+      </c>
+      <c r="AB7">
+        <v>8.4</v>
+      </c>
+      <c r="AC7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD7">
+        <v>24</v>
+      </c>
+      <c r="AE7">
+        <v>110</v>
+      </c>
+      <c r="AF7">
+        <v>9.6</v>
+      </c>
+      <c r="AG7">
+        <v>10.5</v>
+      </c>
+      <c r="AH7">
+        <v>23</v>
+      </c>
+      <c r="AI7">
+        <v>100</v>
+      </c>
+      <c r="AJ7">
+        <v>16.5</v>
+      </c>
+      <c r="AK7">
+        <v>18.5</v>
+      </c>
+      <c r="AL7">
+        <v>48</v>
+      </c>
+      <c r="AM7">
+        <v>160</v>
+      </c>
+      <c r="AN7">
+        <v>10.5</v>
+      </c>
+      <c r="AO7">
+        <v>140</v>
+      </c>
+      <c r="AP7">
+        <v>13</v>
+      </c>
+      <c r="AQ7">
+        <v>16.5</v>
+      </c>
+      <c r="AR7">
+        <v>10</v>
+      </c>
+      <c r="AS7">
+        <v>11.5</v>
+      </c>
+      <c r="AT7">
+        <v>7.4</v>
+      </c>
+      <c r="AU7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV7">
+        <v>20</v>
+      </c>
+      <c r="AW7">
+        <v>11</v>
+      </c>
+      <c r="AX7">
+        <v>8.6</v>
+      </c>
+      <c r="AY7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ7">
+        <v>19.5</v>
+      </c>
+      <c r="BA7">
+        <v>11</v>
+      </c>
+      <c r="BB7">
+        <v>14</v>
+      </c>
+      <c r="BC7">
+        <v>16</v>
+      </c>
+      <c r="BD7">
+        <v>9.4</v>
+      </c>
+      <c r="BE7">
+        <v>11.5</v>
+      </c>
+      <c r="BF7">
+        <v>9</v>
+      </c>
+      <c r="BG7">
+        <v>11.5</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
         <v>2.92</v>
       </c>
-      <c r="J7">
-        <v>2.68</v>
-      </c>
-      <c r="K7">
-        <v>5.1</v>
-      </c>
-      <c r="L7">
-        <v>1.49</v>
-      </c>
-      <c r="M7">
-        <v>1.01</v>
-      </c>
-      <c r="N7">
-        <v>2.68</v>
-      </c>
-      <c r="O7">
-        <v>1.02</v>
-      </c>
-      <c r="P7">
-        <v>1.48</v>
-      </c>
-      <c r="Q7">
-        <v>2.3</v>
-      </c>
-      <c r="R7">
-        <v>1.14</v>
-      </c>
-      <c r="S7">
-        <v>3.2</v>
-      </c>
-      <c r="T7">
-        <v>1.01</v>
-      </c>
-      <c r="U7">
-        <v>1.01</v>
-      </c>
-      <c r="V7">
-        <v>1.52</v>
-      </c>
-      <c r="W7">
-        <v>1.27</v>
-      </c>
-      <c r="X7">
-        <v>1000</v>
-      </c>
-      <c r="Y7">
-        <v>1000</v>
-      </c>
-      <c r="Z7">
-        <v>1000</v>
-      </c>
-      <c r="AA7">
-        <v>1000</v>
-      </c>
-      <c r="AB7">
-        <v>1000</v>
-      </c>
-      <c r="AC7">
-        <v>1000</v>
-      </c>
-      <c r="AD7">
-        <v>1000</v>
-      </c>
-      <c r="AE7">
-        <v>1000</v>
-      </c>
-      <c r="AF7">
-        <v>1000</v>
-      </c>
-      <c r="AG7">
-        <v>1000</v>
-      </c>
-      <c r="AH7">
-        <v>1000</v>
-      </c>
-      <c r="AI7">
-        <v>1000</v>
-      </c>
-      <c r="AJ7">
-        <v>1000</v>
-      </c>
-      <c r="AK7">
-        <v>1000</v>
-      </c>
-      <c r="AL7">
-        <v>1000</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
-      <c r="AN7">
-        <v>1000</v>
-      </c>
-      <c r="AO7">
-        <v>1000</v>
-      </c>
-      <c r="AP7">
-        <v>1.03</v>
-      </c>
-      <c r="AQ7">
-        <v>1.03</v>
-      </c>
-      <c r="AR7">
-        <v>1.03</v>
-      </c>
-      <c r="AS7">
-        <v>1.03</v>
-      </c>
-      <c r="AT7">
-        <v>1.03</v>
-      </c>
-      <c r="AU7">
-        <v>1.03</v>
-      </c>
-      <c r="AV7">
-        <v>1.03</v>
-      </c>
-      <c r="AW7">
-        <v>1.03</v>
-      </c>
-      <c r="AX7">
-        <v>1.03</v>
-      </c>
-      <c r="AY7">
-        <v>1.03</v>
-      </c>
-      <c r="AZ7">
-        <v>1.03</v>
-      </c>
-      <c r="BA7">
-        <v>1.03</v>
-      </c>
-      <c r="BB7">
-        <v>1.03</v>
-      </c>
-      <c r="BC7">
-        <v>1.03</v>
-      </c>
-      <c r="BD7">
-        <v>1.03</v>
-      </c>
-      <c r="BE7">
-        <v>1.03</v>
-      </c>
-      <c r="BF7">
-        <v>1.01</v>
-      </c>
-      <c r="BG7">
-        <v>1.01</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.01</v>
-      </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="CB7" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2452,70 +2470,70 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F8">
-        <v>1.89</v>
+        <v>3.1</v>
       </c>
       <c r="G8">
-        <v>2.08</v>
+        <v>4.9</v>
       </c>
       <c r="H8">
-        <v>4.9</v>
+        <v>2.16</v>
       </c>
       <c r="I8">
-        <v>6.2</v>
+        <v>2.92</v>
       </c>
       <c r="J8">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="K8">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="O8">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="P8">
         <v>1.48</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="R8">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="S8">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="T8">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="W8">
-        <v>1.94</v>
+        <v>1.26</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2533,7 +2551,7 @@
         <v>1000</v>
       </c>
       <c r="AC8">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
         <v>1000</v>
@@ -2542,7 +2560,7 @@
         <v>1000</v>
       </c>
       <c r="AF8">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
         <v>1000</v>
@@ -2560,7 +2578,7 @@
         <v>1000</v>
       </c>
       <c r="AL8">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
         <v>1000</v>
@@ -2620,7 +2638,7 @@
         <v>1.03</v>
       </c>
       <c r="BF8">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
         <v>1.01</v>
@@ -2629,99 +2647,99 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F9">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="G9">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="I9">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J9">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2730,34 +2748,34 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="O9">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="P9">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Q9">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="R9">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="S9">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2814,52 +2832,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2928,81 +2946,81 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F10">
-        <v>3.2</v>
+        <v>1.52</v>
       </c>
       <c r="G10">
-        <v>4.8</v>
+        <v>990</v>
       </c>
       <c r="H10">
-        <v>2.14</v>
+        <v>1.12</v>
       </c>
       <c r="I10">
-        <v>2.7</v>
+        <v>990</v>
       </c>
       <c r="J10">
-        <v>2.42</v>
+        <v>1.12</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>3.1</v>
       </c>
       <c r="L10">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="O10">
-        <v>1.45</v>
+        <v>1.02</v>
       </c>
       <c r="P10">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="Q10">
-        <v>2.42</v>
+        <v>1.62</v>
       </c>
       <c r="R10">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="S10">
-        <v>4</v>
+        <v>1.62</v>
       </c>
       <c r="T10">
+        <v>1.11</v>
+      </c>
+      <c r="U10">
+        <v>1.11</v>
+      </c>
+      <c r="V10">
         <v>1.02</v>
       </c>
-      <c r="U10">
-        <v>1.01</v>
-      </c>
-      <c r="V10">
-        <v>1.6</v>
-      </c>
       <c r="W10">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
         <v>1000</v>
@@ -3170,7 +3188,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3178,312 +3196,312 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F11">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="G11">
-        <v>2.66</v>
+        <v>4.8</v>
       </c>
       <c r="H11">
-        <v>2.88</v>
+        <v>2.14</v>
       </c>
       <c r="I11">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="J11">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="K11">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L11">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="M11">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
+        <v>2.18</v>
+      </c>
+      <c r="O11">
+        <v>1.45</v>
+      </c>
+      <c r="P11">
+        <v>1.39</v>
+      </c>
+      <c r="Q11">
+        <v>2.42</v>
+      </c>
+      <c r="R11">
+        <v>1.12</v>
+      </c>
+      <c r="S11">
         <v>4</v>
       </c>
-      <c r="O11">
-        <v>1.27</v>
-      </c>
-      <c r="P11">
-        <v>2.04</v>
-      </c>
-      <c r="Q11">
-        <v>1.8</v>
-      </c>
-      <c r="R11">
-        <v>1.41</v>
-      </c>
-      <c r="S11">
-        <v>3</v>
-      </c>
       <c r="T11">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>2.24</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W11">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="X11">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Y11">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
         <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F12">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="G12">
-        <v>3.35</v>
+        <v>2.08</v>
       </c>
       <c r="H12">
-        <v>2.74</v>
+        <v>4.8</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="J12">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="L12">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
+        <v>1.12</v>
+      </c>
+      <c r="N12">
+        <v>2.42</v>
+      </c>
+      <c r="O12">
+        <v>1.53</v>
+      </c>
+      <c r="P12">
+        <v>1.5</v>
+      </c>
+      <c r="Q12">
+        <v>2.46</v>
+      </c>
+      <c r="R12">
         <v>1.08</v>
       </c>
-      <c r="N12">
-        <v>2.6</v>
-      </c>
-      <c r="O12">
-        <v>1.49</v>
-      </c>
-      <c r="P12">
-        <v>1.57</v>
-      </c>
-      <c r="Q12">
-        <v>2.2</v>
-      </c>
-      <c r="R12">
-        <v>1.12</v>
-      </c>
       <c r="S12">
-        <v>2.72</v>
+        <v>1.05</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="W12">
-        <v>1.42</v>
+        <v>1.94</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3501,7 +3519,7 @@
         <v>1000</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD12">
         <v>1000</v>
@@ -3510,7 +3528,7 @@
         <v>1000</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG12">
         <v>1000</v>
@@ -3528,7 +3546,7 @@
         <v>1000</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM12">
         <v>1000</v>
@@ -3543,7 +3561,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
         <v>1.03</v>
@@ -3552,10 +3570,10 @@
         <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
         <v>1.03</v>
@@ -3564,10 +3582,10 @@
         <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
         <v>1.03</v>
@@ -3588,7 +3606,7 @@
         <v>1.03</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG12">
         <v>1.01</v>
@@ -3597,485 +3615,485 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.56</v>
+        <v>3.4</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="CB12" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F13">
-        <v>1.46</v>
+        <v>2.52</v>
       </c>
       <c r="G13">
-        <v>1.62</v>
+        <v>2.66</v>
       </c>
       <c r="H13">
-        <v>8</v>
+        <v>2.88</v>
       </c>
       <c r="I13">
+        <v>3.15</v>
+      </c>
+      <c r="J13">
+        <v>3.45</v>
+      </c>
+      <c r="K13">
+        <v>3.65</v>
+      </c>
+      <c r="L13">
+        <v>1.02</v>
+      </c>
+      <c r="M13">
+        <v>1.06</v>
+      </c>
+      <c r="N13">
+        <v>4</v>
+      </c>
+      <c r="O13">
+        <v>1.27</v>
+      </c>
+      <c r="P13">
+        <v>2.04</v>
+      </c>
+      <c r="Q13">
+        <v>1.8</v>
+      </c>
+      <c r="R13">
+        <v>1.41</v>
+      </c>
+      <c r="S13">
+        <v>3</v>
+      </c>
+      <c r="T13">
+        <v>1.67</v>
+      </c>
+      <c r="U13">
+        <v>2.24</v>
+      </c>
+      <c r="V13">
+        <v>1.48</v>
+      </c>
+      <c r="W13">
+        <v>1.6</v>
+      </c>
+      <c r="X13">
+        <v>21</v>
+      </c>
+      <c r="Y13">
+        <v>14</v>
+      </c>
+      <c r="Z13">
+        <v>22</v>
+      </c>
+      <c r="AA13">
+        <v>60</v>
+      </c>
+      <c r="AB13">
+        <v>12.5</v>
+      </c>
+      <c r="AC13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD13">
+        <v>13.5</v>
+      </c>
+      <c r="AE13">
+        <v>34</v>
+      </c>
+      <c r="AF13">
+        <v>21</v>
+      </c>
+      <c r="AG13">
+        <v>12</v>
+      </c>
+      <c r="AH13">
+        <v>17</v>
+      </c>
+      <c r="AI13">
+        <v>42</v>
+      </c>
+      <c r="AJ13">
+        <v>36</v>
+      </c>
+      <c r="AK13">
+        <v>26</v>
+      </c>
+      <c r="AL13">
+        <v>40</v>
+      </c>
+      <c r="AM13">
+        <v>100</v>
+      </c>
+      <c r="AN13">
+        <v>22</v>
+      </c>
+      <c r="AO13">
+        <v>26</v>
+      </c>
+      <c r="AP13">
+        <v>14</v>
+      </c>
+      <c r="AQ13">
+        <v>11.5</v>
+      </c>
+      <c r="AR13">
+        <v>18.5</v>
+      </c>
+      <c r="AS13">
+        <v>7.4</v>
+      </c>
+      <c r="AT13">
+        <v>10</v>
+      </c>
+      <c r="AU13">
+        <v>7.2</v>
+      </c>
+      <c r="AV13">
+        <v>11.5</v>
+      </c>
+      <c r="AW13">
+        <v>6.8</v>
+      </c>
+      <c r="AX13">
+        <v>14.5</v>
+      </c>
+      <c r="AY13">
+        <v>10</v>
+      </c>
+      <c r="AZ13">
+        <v>14</v>
+      </c>
+      <c r="BA13">
+        <v>7.2</v>
+      </c>
+      <c r="BB13">
+        <v>27</v>
+      </c>
+      <c r="BC13">
+        <v>21</v>
+      </c>
+      <c r="BD13">
+        <v>30</v>
+      </c>
+      <c r="BE13">
+        <v>7.8</v>
+      </c>
+      <c r="BF13">
+        <v>16</v>
+      </c>
+      <c r="BG13">
+        <v>18</v>
+      </c>
+      <c r="BH13">
+        <v>4.2</v>
+      </c>
+      <c r="BI13">
+        <v>2.84</v>
+      </c>
+      <c r="BJ13">
+        <v>13</v>
+      </c>
+      <c r="BK13">
+        <v>2.64</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>3.3</v>
+      </c>
+      <c r="BN13">
+        <v>7.8</v>
+      </c>
+      <c r="BO13">
+        <v>3.6</v>
+      </c>
+      <c r="BP13">
+        <v>25</v>
+      </c>
+      <c r="BQ13">
+        <v>2.94</v>
+      </c>
+      <c r="BR13">
+        <v>40</v>
+      </c>
+      <c r="BS13">
+        <v>3.05</v>
+      </c>
+      <c r="BT13">
+        <v>9</v>
+      </c>
+      <c r="BU13">
+        <v>4.1</v>
+      </c>
+      <c r="BV13">
+        <v>34</v>
+      </c>
+      <c r="BW13">
+        <v>3</v>
+      </c>
+      <c r="BX13">
+        <v>48</v>
+      </c>
+      <c r="BY13">
+        <v>3.1</v>
+      </c>
+      <c r="BZ13">
+        <v>34</v>
+      </c>
+      <c r="CA13">
+        <v>3</v>
+      </c>
+      <c r="CB13" t="s">
         <v>140</v>
-      </c>
-      <c r="J13">
-        <v>3.9</v>
-      </c>
-      <c r="K13">
-        <v>5.3</v>
-      </c>
-      <c r="L13">
-        <v>1.01</v>
-      </c>
-      <c r="M13">
-        <v>1.05</v>
-      </c>
-      <c r="N13">
-        <v>2.64</v>
-      </c>
-      <c r="O13">
-        <v>1.33</v>
-      </c>
-      <c r="P13">
-        <v>1.65</v>
-      </c>
-      <c r="Q13">
-        <v>1.9</v>
-      </c>
-      <c r="R13">
-        <v>1.18</v>
-      </c>
-      <c r="S13">
-        <v>2.58</v>
-      </c>
-      <c r="T13">
-        <v>2.22</v>
-      </c>
-      <c r="U13">
-        <v>1.6</v>
-      </c>
-      <c r="V13">
-        <v>1.06</v>
-      </c>
-      <c r="W13">
-        <v>2.62</v>
-      </c>
-      <c r="X13">
-        <v>13</v>
-      </c>
-      <c r="Y13">
-        <v>23</v>
-      </c>
-      <c r="Z13">
-        <v>85</v>
-      </c>
-      <c r="AA13">
-        <v>380</v>
-      </c>
-      <c r="AB13">
-        <v>6.8</v>
-      </c>
-      <c r="AC13">
-        <v>10</v>
-      </c>
-      <c r="AD13">
-        <v>42</v>
-      </c>
-      <c r="AE13">
-        <v>190</v>
-      </c>
-      <c r="AF13">
-        <v>8.6</v>
-      </c>
-      <c r="AG13">
-        <v>11</v>
-      </c>
-      <c r="AH13">
-        <v>30</v>
-      </c>
-      <c r="AI13">
-        <v>180</v>
-      </c>
-      <c r="AJ13">
-        <v>15</v>
-      </c>
-      <c r="AK13">
-        <v>20</v>
-      </c>
-      <c r="AL13">
-        <v>60</v>
-      </c>
-      <c r="AM13">
-        <v>250</v>
-      </c>
-      <c r="AN13">
-        <v>11.5</v>
-      </c>
-      <c r="AO13">
-        <v>330</v>
-      </c>
-      <c r="AP13">
-        <v>5.1</v>
-      </c>
-      <c r="AQ13">
-        <v>6.2</v>
-      </c>
-      <c r="AR13">
-        <v>7.8</v>
-      </c>
-      <c r="AS13">
-        <v>8.4</v>
-      </c>
-      <c r="AT13">
-        <v>3.8</v>
-      </c>
-      <c r="AU13">
-        <v>4.6</v>
-      </c>
-      <c r="AV13">
-        <v>7</v>
-      </c>
-      <c r="AW13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX13">
-        <v>4.3</v>
-      </c>
-      <c r="AY13">
-        <v>4.8</v>
-      </c>
-      <c r="AZ13">
-        <v>6.6</v>
-      </c>
-      <c r="BA13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB13">
-        <v>5.4</v>
-      </c>
-      <c r="BC13">
-        <v>6</v>
-      </c>
-      <c r="BD13">
-        <v>7.4</v>
-      </c>
-      <c r="BE13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF13">
-        <v>4.9</v>
-      </c>
-      <c r="BG13">
-        <v>8.4</v>
-      </c>
-      <c r="BH13">
-        <v>1000</v>
-      </c>
-      <c r="BI13">
-        <v>1.29</v>
-      </c>
-      <c r="BJ13">
-        <v>1000</v>
-      </c>
-      <c r="BK13">
-        <v>1.29</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>1.29</v>
-      </c>
-      <c r="BN13">
-        <v>1000</v>
-      </c>
-      <c r="BO13">
-        <v>1.01</v>
-      </c>
-      <c r="BP13">
-        <v>1000</v>
-      </c>
-      <c r="BQ13">
-        <v>1.29</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>1.29</v>
-      </c>
-      <c r="BT13">
-        <v>1000</v>
-      </c>
-      <c r="BU13">
-        <v>1.29</v>
-      </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>1.29</v>
-      </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
-        <v>1.29</v>
-      </c>
-      <c r="BZ13">
-        <v>1000</v>
-      </c>
-      <c r="CA13">
-        <v>1.29</v>
-      </c>
-      <c r="CB13" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F14">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="G14">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="H14">
-        <v>2.12</v>
+        <v>2.74</v>
       </c>
       <c r="I14">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="K14">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M14">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N14">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="O14">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="P14">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="Q14">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="R14">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="S14">
-        <v>3.15</v>
+        <v>2.72</v>
       </c>
       <c r="T14">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="U14">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="X14">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AS14">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW14">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14">
         <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4087,58 +4105,58 @@
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="CB14" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4146,241 +4164,241 @@
         <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F15">
-        <v>2.02</v>
+        <v>1.46</v>
       </c>
       <c r="G15">
-        <v>2.22</v>
+        <v>1.61</v>
       </c>
       <c r="H15">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="I15">
+        <v>990</v>
+      </c>
+      <c r="J15">
+        <v>3.95</v>
+      </c>
+      <c r="K15">
+        <v>5.3</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.05</v>
+      </c>
+      <c r="N15">
+        <v>2.64</v>
+      </c>
+      <c r="O15">
+        <v>1.33</v>
+      </c>
+      <c r="P15">
+        <v>1.65</v>
+      </c>
+      <c r="Q15">
+        <v>1.9</v>
+      </c>
+      <c r="R15">
+        <v>1.18</v>
+      </c>
+      <c r="S15">
+        <v>2.58</v>
+      </c>
+      <c r="T15">
+        <v>1.11</v>
+      </c>
+      <c r="U15">
+        <v>1.11</v>
+      </c>
+      <c r="V15">
+        <v>1.06</v>
+      </c>
+      <c r="W15">
+        <v>2.64</v>
+      </c>
+      <c r="X15">
+        <v>13</v>
+      </c>
+      <c r="Y15">
+        <v>23</v>
+      </c>
+      <c r="Z15">
+        <v>85</v>
+      </c>
+      <c r="AA15">
+        <v>380</v>
+      </c>
+      <c r="AB15">
+        <v>6.8</v>
+      </c>
+      <c r="AC15">
+        <v>10</v>
+      </c>
+      <c r="AD15">
+        <v>42</v>
+      </c>
+      <c r="AE15">
+        <v>190</v>
+      </c>
+      <c r="AF15">
+        <v>8.6</v>
+      </c>
+      <c r="AG15">
+        <v>11</v>
+      </c>
+      <c r="AH15">
+        <v>30</v>
+      </c>
+      <c r="AI15">
+        <v>180</v>
+      </c>
+      <c r="AJ15">
+        <v>15</v>
+      </c>
+      <c r="AK15">
+        <v>20</v>
+      </c>
+      <c r="AL15">
+        <v>60</v>
+      </c>
+      <c r="AM15">
+        <v>250</v>
+      </c>
+      <c r="AN15">
+        <v>11.5</v>
+      </c>
+      <c r="AO15">
+        <v>330</v>
+      </c>
+      <c r="AP15">
+        <v>5.1</v>
+      </c>
+      <c r="AQ15">
+        <v>6.2</v>
+      </c>
+      <c r="AR15">
+        <v>7.8</v>
+      </c>
+      <c r="AS15">
+        <v>8.4</v>
+      </c>
+      <c r="AT15">
+        <v>3.8</v>
+      </c>
+      <c r="AU15">
+        <v>4.6</v>
+      </c>
+      <c r="AV15">
+        <v>7</v>
+      </c>
+      <c r="AW15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX15">
+        <v>4.3</v>
+      </c>
+      <c r="AY15">
+        <v>4.8</v>
+      </c>
+      <c r="AZ15">
         <v>6.6</v>
       </c>
-      <c r="J15">
-        <v>2.68</v>
-      </c>
-      <c r="K15">
-        <v>3.3</v>
-      </c>
-      <c r="L15">
-        <v>1.01</v>
-      </c>
-      <c r="M15">
-        <v>1.01</v>
-      </c>
-      <c r="N15">
-        <v>2.36</v>
-      </c>
-      <c r="O15">
-        <v>1.6</v>
-      </c>
-      <c r="P15">
-        <v>1.37</v>
-      </c>
-      <c r="Q15">
-        <v>2.28</v>
-      </c>
-      <c r="R15">
-        <v>1.08</v>
-      </c>
-      <c r="S15">
-        <v>2.28</v>
-      </c>
-      <c r="T15">
-        <v>1.01</v>
-      </c>
-      <c r="U15">
-        <v>1.01</v>
-      </c>
-      <c r="V15">
-        <v>1.19</v>
-      </c>
-      <c r="W15">
-        <v>1.81</v>
-      </c>
-      <c r="X15">
-        <v>1000</v>
-      </c>
-      <c r="Y15">
-        <v>1000</v>
-      </c>
-      <c r="Z15">
-        <v>1000</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>8</v>
-      </c>
-      <c r="AC15">
-        <v>11.5</v>
-      </c>
-      <c r="AD15">
-        <v>1000</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>1000</v>
-      </c>
-      <c r="AG15">
-        <v>1000</v>
-      </c>
-      <c r="AH15">
-        <v>1000</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>1000</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
-      <c r="AP15">
-        <v>1.03</v>
-      </c>
-      <c r="AQ15">
-        <v>1.03</v>
-      </c>
-      <c r="AR15">
-        <v>1.03</v>
-      </c>
-      <c r="AS15">
-        <v>1.03</v>
-      </c>
-      <c r="AT15">
-        <v>1.03</v>
-      </c>
-      <c r="AU15">
-        <v>1.03</v>
-      </c>
-      <c r="AV15">
-        <v>1.03</v>
-      </c>
-      <c r="AW15">
-        <v>1.03</v>
-      </c>
-      <c r="AX15">
-        <v>1.03</v>
-      </c>
-      <c r="AY15">
-        <v>1.03</v>
-      </c>
-      <c r="AZ15">
-        <v>1.03</v>
-      </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH15">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>2.08</v>
+        <v>1.29</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>2.06</v>
+        <v>1.29</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>2.06</v>
+        <v>1.29</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>2.06</v>
+        <v>1.29</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>2.06</v>
+        <v>1.29</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>2.06</v>
+        <v>1.29</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>2.06</v>
+        <v>1.29</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>2.06</v>
+        <v>1.29</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>2.06</v>
+        <v>1.29</v>
       </c>
       <c r="CB15" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4388,276 +4406,276 @@
         <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F16">
-        <v>1.42</v>
+        <v>3.3</v>
       </c>
       <c r="G16">
-        <v>1.44</v>
+        <v>3.9</v>
       </c>
       <c r="H16">
+        <v>2.12</v>
+      </c>
+      <c r="I16">
+        <v>2.38</v>
+      </c>
+      <c r="J16">
+        <v>3.4</v>
+      </c>
+      <c r="K16">
+        <v>3.95</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.06</v>
+      </c>
+      <c r="N16">
+        <v>3.75</v>
+      </c>
+      <c r="O16">
+        <v>1.29</v>
+      </c>
+      <c r="P16">
+        <v>1.95</v>
+      </c>
+      <c r="Q16">
+        <v>1.85</v>
+      </c>
+      <c r="R16">
+        <v>1.36</v>
+      </c>
+      <c r="S16">
+        <v>3.15</v>
+      </c>
+      <c r="T16">
+        <v>1.71</v>
+      </c>
+      <c r="U16">
+        <v>2.14</v>
+      </c>
+      <c r="V16">
+        <v>1.72</v>
+      </c>
+      <c r="W16">
+        <v>1.34</v>
+      </c>
+      <c r="X16">
+        <v>18</v>
+      </c>
+      <c r="Y16">
+        <v>12</v>
+      </c>
+      <c r="Z16">
+        <v>17</v>
+      </c>
+      <c r="AA16">
+        <v>34</v>
+      </c>
+      <c r="AB16">
+        <v>16.5</v>
+      </c>
+      <c r="AC16">
+        <v>9.6</v>
+      </c>
+      <c r="AD16">
+        <v>13</v>
+      </c>
+      <c r="AE16">
+        <v>27</v>
+      </c>
+      <c r="AF16">
+        <v>30</v>
+      </c>
+      <c r="AG16">
+        <v>17.5</v>
+      </c>
+      <c r="AH16">
+        <v>20</v>
+      </c>
+      <c r="AI16">
+        <v>42</v>
+      </c>
+      <c r="AJ16">
+        <v>75</v>
+      </c>
+      <c r="AK16">
+        <v>48</v>
+      </c>
+      <c r="AL16">
+        <v>60</v>
+      </c>
+      <c r="AM16">
+        <v>100</v>
+      </c>
+      <c r="AN16">
+        <v>46</v>
+      </c>
+      <c r="AO16">
+        <v>19.5</v>
+      </c>
+      <c r="AP16">
+        <v>11.5</v>
+      </c>
+      <c r="AQ16">
         <v>8</v>
       </c>
-      <c r="I16">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J16">
-        <v>5</v>
-      </c>
-      <c r="K16">
-        <v>5.4</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>1.07</v>
-      </c>
-      <c r="Q16">
-        <v>1.63</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-      <c r="AO16">
-        <v>0</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
       <c r="AR16">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F17">
-        <v>2.58</v>
+        <v>1.97</v>
       </c>
       <c r="G17">
-        <v>3.05</v>
+        <v>2.22</v>
       </c>
       <c r="H17">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="I17">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="J17">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="K17">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4666,34 +4684,34 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="O17">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="P17">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q17">
-        <v>2.58</v>
+        <v>2.28</v>
       </c>
       <c r="R17">
         <v>1.08</v>
       </c>
       <c r="S17">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="T17">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="U17">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="V17">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="W17">
-        <v>1.49</v>
+        <v>1.81</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4804,309 +4822,793 @@
         <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BI17">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="CB17" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
         <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F18">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="G18">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="H18">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J18">
+        <v>4.9</v>
+      </c>
+      <c r="K18">
+        <v>5.3</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.07</v>
+      </c>
+      <c r="Q18">
+        <v>1.63</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" t="s">
+        <v>138</v>
+      </c>
+      <c r="F19">
+        <v>2.68</v>
+      </c>
+      <c r="G19">
+        <v>3.05</v>
+      </c>
+      <c r="H19">
+        <v>2.9</v>
+      </c>
+      <c r="I19">
         <v>3.35</v>
       </c>
-      <c r="K18">
-        <v>950</v>
-      </c>
-      <c r="L18">
-        <v>1.01</v>
-      </c>
-      <c r="M18">
+      <c r="J19">
+        <v>2.7</v>
+      </c>
+      <c r="K19">
+        <v>3.55</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.12</v>
+      </c>
+      <c r="N19">
+        <v>2.16</v>
+      </c>
+      <c r="O19">
+        <v>1.48</v>
+      </c>
+      <c r="P19">
+        <v>1.36</v>
+      </c>
+      <c r="Q19">
+        <v>2.58</v>
+      </c>
+      <c r="R19">
+        <v>1.08</v>
+      </c>
+      <c r="S19">
+        <v>3.1</v>
+      </c>
+      <c r="T19">
+        <v>1.12</v>
+      </c>
+      <c r="U19">
+        <v>1.56</v>
+      </c>
+      <c r="V19">
+        <v>1.43</v>
+      </c>
+      <c r="W19">
+        <v>1.49</v>
+      </c>
+      <c r="X19">
+        <v>1000</v>
+      </c>
+      <c r="Y19">
+        <v>1000</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>1000</v>
+      </c>
+      <c r="AC19">
+        <v>1000</v>
+      </c>
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>1000</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>1.03</v>
+      </c>
+      <c r="AQ19">
+        <v>1.03</v>
+      </c>
+      <c r="AR19">
+        <v>1.03</v>
+      </c>
+      <c r="AS19">
+        <v>1.03</v>
+      </c>
+      <c r="AT19">
+        <v>1.03</v>
+      </c>
+      <c r="AU19">
+        <v>1.03</v>
+      </c>
+      <c r="AV19">
+        <v>1.03</v>
+      </c>
+      <c r="AW19">
+        <v>1.03</v>
+      </c>
+      <c r="AX19">
+        <v>1.03</v>
+      </c>
+      <c r="AY19">
+        <v>1.03</v>
+      </c>
+      <c r="AZ19">
+        <v>1.03</v>
+      </c>
+      <c r="BA19">
+        <v>1.03</v>
+      </c>
+      <c r="BB19">
+        <v>1.03</v>
+      </c>
+      <c r="BC19">
+        <v>1.03</v>
+      </c>
+      <c r="BD19">
+        <v>1.03</v>
+      </c>
+      <c r="BE19">
+        <v>1.03</v>
+      </c>
+      <c r="BF19">
+        <v>1.01</v>
+      </c>
+      <c r="BG19">
+        <v>1.01</v>
+      </c>
+      <c r="BH19">
+        <v>2.96</v>
+      </c>
+      <c r="BI19">
+        <v>2.02</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.53</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.53</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>2.02</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.53</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.53</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>2.16</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.53</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.53</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>1.53</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F20">
+        <v>1.57</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>4.1</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20">
+        <v>3.35</v>
+      </c>
+      <c r="K20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
         <v>1.04</v>
       </c>
-      <c r="N18">
-        <v>3.05</v>
-      </c>
-      <c r="O18">
+      <c r="N20">
+        <v>3</v>
+      </c>
+      <c r="O20">
         <v>1.29</v>
       </c>
-      <c r="P18">
+      <c r="P20">
         <v>1.8</v>
       </c>
-      <c r="Q18">
+      <c r="Q20">
         <v>1.74</v>
       </c>
-      <c r="R18">
-        <v>1.34</v>
-      </c>
-      <c r="S18">
+      <c r="R20">
+        <v>1.27</v>
+      </c>
+      <c r="S20">
         <v>2.5</v>
       </c>
-      <c r="T18">
-        <v>1.84</v>
-      </c>
-      <c r="U18">
-        <v>1.9</v>
-      </c>
-      <c r="V18">
-        <v>1.18</v>
-      </c>
-      <c r="W18">
-        <v>2.1</v>
-      </c>
-      <c r="X18">
-        <v>1000</v>
-      </c>
-      <c r="Y18">
-        <v>1000</v>
-      </c>
-      <c r="Z18">
-        <v>1000</v>
-      </c>
-      <c r="AA18">
-        <v>1000</v>
-      </c>
-      <c r="AB18">
-        <v>1000</v>
-      </c>
-      <c r="AC18">
-        <v>1000</v>
-      </c>
-      <c r="AD18">
-        <v>1000</v>
-      </c>
-      <c r="AE18">
-        <v>1000</v>
-      </c>
-      <c r="AF18">
-        <v>1000</v>
-      </c>
-      <c r="AG18">
-        <v>1000</v>
-      </c>
-      <c r="AH18">
-        <v>1000</v>
-      </c>
-      <c r="AI18">
-        <v>1000</v>
-      </c>
-      <c r="AJ18">
-        <v>1000</v>
-      </c>
-      <c r="AK18">
-        <v>1000</v>
-      </c>
-      <c r="AL18">
-        <v>1000</v>
-      </c>
-      <c r="AM18">
-        <v>1000</v>
-      </c>
-      <c r="AN18">
-        <v>1000</v>
-      </c>
-      <c r="AO18">
-        <v>1000</v>
-      </c>
-      <c r="AP18">
-        <v>1.03</v>
-      </c>
-      <c r="AQ18">
-        <v>1.03</v>
-      </c>
-      <c r="AR18">
-        <v>1.03</v>
-      </c>
-      <c r="AS18">
-        <v>1.03</v>
-      </c>
-      <c r="AT18">
-        <v>1.01</v>
-      </c>
-      <c r="AU18">
-        <v>1.01</v>
-      </c>
-      <c r="AV18">
-        <v>1.03</v>
-      </c>
-      <c r="AW18">
-        <v>1.03</v>
-      </c>
-      <c r="AX18">
-        <v>1.01</v>
-      </c>
-      <c r="AY18">
-        <v>1.01</v>
-      </c>
-      <c r="AZ18">
-        <v>1.03</v>
-      </c>
-      <c r="BA18">
-        <v>1.03</v>
-      </c>
-      <c r="BB18">
-        <v>1.01</v>
-      </c>
-      <c r="BC18">
-        <v>1.03</v>
-      </c>
-      <c r="BD18">
-        <v>1.03</v>
-      </c>
-      <c r="BE18">
-        <v>1.03</v>
-      </c>
-      <c r="BF18">
-        <v>1.01</v>
-      </c>
-      <c r="BG18">
-        <v>1.01</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.01</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>1.01</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>1.01</v>
-      </c>
-      <c r="BN18">
-        <v>1000</v>
-      </c>
-      <c r="BO18">
-        <v>1.01</v>
-      </c>
-      <c r="BP18">
-        <v>1000</v>
-      </c>
-      <c r="BQ18">
-        <v>1.01</v>
-      </c>
-      <c r="BR18">
-        <v>1000</v>
-      </c>
-      <c r="BS18">
-        <v>1.01</v>
-      </c>
-      <c r="BT18">
-        <v>1000</v>
-      </c>
-      <c r="BU18">
-        <v>1.01</v>
-      </c>
-      <c r="BV18">
-        <v>1000</v>
-      </c>
-      <c r="BW18">
-        <v>1.01</v>
-      </c>
-      <c r="BX18">
-        <v>1000</v>
-      </c>
-      <c r="BY18">
-        <v>1.01</v>
-      </c>
-      <c r="BZ18">
-        <v>1000</v>
-      </c>
-      <c r="CA18">
-        <v>1.01</v>
-      </c>
-      <c r="CB18" t="s">
-        <v>134</v>
+      <c r="T20">
+        <v>1.11</v>
+      </c>
+      <c r="U20">
+        <v>1.11</v>
+      </c>
+      <c r="V20">
+        <v>1.25</v>
+      </c>
+      <c r="W20">
+        <v>2</v>
+      </c>
+      <c r="X20">
+        <v>1000</v>
+      </c>
+      <c r="Y20">
+        <v>1000</v>
+      </c>
+      <c r="Z20">
+        <v>1000</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>1000</v>
+      </c>
+      <c r="AC20">
+        <v>1000</v>
+      </c>
+      <c r="AD20">
+        <v>1000</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>1000</v>
+      </c>
+      <c r="AH20">
+        <v>1000</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>1000</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>1.03</v>
+      </c>
+      <c r="AQ20">
+        <v>1.03</v>
+      </c>
+      <c r="AR20">
+        <v>1.03</v>
+      </c>
+      <c r="AS20">
+        <v>1.03</v>
+      </c>
+      <c r="AT20">
+        <v>1.01</v>
+      </c>
+      <c r="AU20">
+        <v>1.01</v>
+      </c>
+      <c r="AV20">
+        <v>1.03</v>
+      </c>
+      <c r="AW20">
+        <v>1.03</v>
+      </c>
+      <c r="AX20">
+        <v>1.01</v>
+      </c>
+      <c r="AY20">
+        <v>1.01</v>
+      </c>
+      <c r="AZ20">
+        <v>1.03</v>
+      </c>
+      <c r="BA20">
+        <v>1.03</v>
+      </c>
+      <c r="BB20">
+        <v>1.01</v>
+      </c>
+      <c r="BC20">
+        <v>1.03</v>
+      </c>
+      <c r="BD20">
+        <v>1.03</v>
+      </c>
+      <c r="BE20">
+        <v>1.03</v>
+      </c>
+      <c r="BF20">
+        <v>1.01</v>
+      </c>
+      <c r="BG20">
+        <v>1.01</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.01</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.01</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.01</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.01</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.01</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.01</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.01</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="156">
   <si>
     <t>League</t>
   </si>
@@ -274,12 +274,12 @@
     <t>Moroccan Botola Pro 1</t>
   </si>
   <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
     <t>Ecuadorian Serie B</t>
   </si>
   <si>
-    <t>Algerian Ligue 1</t>
-  </si>
-  <si>
     <t>Romanian Liga I</t>
   </si>
   <si>
@@ -289,6 +289,12 @@
     <t>Irish Premier Division</t>
   </si>
   <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
     <t>2026-10-08</t>
   </si>
   <si>
@@ -322,6 +328,15 @@
     <t>20:30:00</t>
   </si>
   <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
+    <t>23:05:00</t>
+  </si>
+  <si>
     <t>Cruzeiro MG</t>
   </si>
   <si>
@@ -343,18 +358,18 @@
     <t>Union de Touarga</t>
   </si>
   <si>
+    <t>MB Rouissat</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>Independiente Juniors</t>
+  </si>
+  <si>
     <t>Al-Wakra</t>
   </si>
   <si>
-    <t>Independiente Juniors</t>
-  </si>
-  <si>
-    <t>MB Rouissat</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
@@ -379,6 +394,21 @@
     <t>Atletico Grau</t>
   </si>
   <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Ceara SC Fortaleza</t>
+  </si>
+  <si>
+    <t>Nautico PE</t>
+  </si>
+  <si>
+    <t>Athletico-PR</t>
+  </si>
+  <si>
+    <t>Atletico Nacional Medellin</t>
+  </si>
+  <si>
     <t>Sao Paulo</t>
   </si>
   <si>
@@ -400,18 +430,18 @@
     <t>RSB Berkane</t>
   </si>
   <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>Olympique Akbou</t>
+  </si>
+  <si>
+    <t>Club Nueve de Octubre</t>
+  </si>
+  <si>
     <t>Al Gharafa</t>
   </si>
   <si>
-    <t>Club Nueve de Octubre</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>Olympique Akbou</t>
-  </si>
-  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
@@ -436,7 +466,22 @@
     <t>CD Los Chankas</t>
   </si>
   <si>
-    <t>2026-10-06 23:49:07</t>
+    <t>Flamengo</t>
+  </si>
+  <si>
+    <t>Criciuma</t>
+  </si>
+  <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
+    <t>Atletico MG</t>
+  </si>
+  <si>
+    <t>Tolima</t>
+  </si>
+  <si>
+    <t>2026-10-07 02:01:18</t>
   </si>
 </sst>
 </file>
@@ -768,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1018,79 +1063,79 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="F2">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="G2">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J2">
+        <v>3.65</v>
+      </c>
+      <c r="K2">
         <v>3.7</v>
-      </c>
-      <c r="K2">
-        <v>3.9</v>
       </c>
       <c r="L2">
         <v>1.44</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
+        <v>3.75</v>
+      </c>
+      <c r="O2">
+        <v>1.35</v>
+      </c>
+      <c r="P2">
+        <v>1.91</v>
+      </c>
+      <c r="Q2">
+        <v>2.04</v>
+      </c>
+      <c r="R2">
+        <v>1.34</v>
+      </c>
+      <c r="S2">
         <v>3.7</v>
       </c>
-      <c r="O2">
-        <v>1.34</v>
-      </c>
-      <c r="P2">
-        <v>1.92</v>
-      </c>
-      <c r="Q2">
-        <v>2.02</v>
-      </c>
-      <c r="R2">
-        <v>1.35</v>
-      </c>
-      <c r="S2">
-        <v>3.65</v>
-      </c>
       <c r="T2">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U2">
         <v>2.1</v>
       </c>
       <c r="V2">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W2">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="X2">
+        <v>14</v>
+      </c>
+      <c r="Y2">
         <v>15</v>
       </c>
-      <c r="Y2">
-        <v>16</v>
-      </c>
       <c r="Z2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1105,34 +1150,34 @@
         <v>17.5</v>
       </c>
       <c r="AE2">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1141,13 +1186,13 @@
         <v>13</v>
       </c>
       <c r="AQ2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS2">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AT2">
         <v>8</v>
@@ -1156,40 +1201,40 @@
         <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AX2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
         <v>17</v>
       </c>
       <c r="BA2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BB2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC2">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BD2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE2">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="BF2">
         <v>12.5</v>
       </c>
       <c r="BG2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH2">
         <v>3.3</v>
@@ -1207,7 +1252,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN2">
         <v>4.5</v>
@@ -1225,25 +1270,25 @@
         <v>30</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BV2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW2">
         <v>11.5</v>
       </c>
       <c r="BX2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
         <v>27</v>
@@ -1252,7 +1297,7 @@
         <v>10</v>
       </c>
       <c r="CB2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1260,34 +1305,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F3">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="G3">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="H3">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="I3">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="J3">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1296,34 +1341,34 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.07</v>
+        <v>4.2</v>
       </c>
       <c r="O3">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P3">
-        <v>1.07</v>
+        <v>1.8</v>
       </c>
       <c r="Q3">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R3">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="S3">
-        <v>1.19</v>
+        <v>2.36</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1380,52 +1425,52 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3">
         <v>1.01</v>
@@ -1437,64 +1482,64 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1502,22 +1547,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="F4">
         <v>1.62</v>
       </c>
       <c r="G4">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H4">
         <v>5.7</v>
@@ -1544,31 +1589,31 @@
         <v>1.23</v>
       </c>
       <c r="P4">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q4">
         <v>1.72</v>
       </c>
       <c r="R4">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S4">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T4">
         <v>1.73</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V4">
         <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y4">
         <v>32</v>
@@ -1586,13 +1631,13 @@
         <v>12</v>
       </c>
       <c r="AD4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG4">
         <v>12</v>
@@ -1604,10 +1649,10 @@
         <v>100</v>
       </c>
       <c r="AJ4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK4">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AL4">
         <v>46</v>
@@ -1619,22 +1664,22 @@
         <v>9.4</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP4">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4">
         <v>14</v>
       </c>
       <c r="AR4">
-        <v>3.05</v>
+        <v>10.5</v>
       </c>
       <c r="AS4">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AT4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU4">
         <v>7.8</v>
@@ -1643,7 +1688,7 @@
         <v>14</v>
       </c>
       <c r="AW4">
-        <v>3.1</v>
+        <v>15</v>
       </c>
       <c r="AX4">
         <v>8.6</v>
@@ -1652,10 +1697,10 @@
         <v>7.8</v>
       </c>
       <c r="AZ4">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA4">
-        <v>3.1</v>
+        <v>15.5</v>
       </c>
       <c r="BB4">
         <v>13.5</v>
@@ -1664,16 +1709,16 @@
         <v>13.5</v>
       </c>
       <c r="BD4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE4">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="BF4">
         <v>6</v>
       </c>
       <c r="BG4">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BH4">
         <v>5</v>
@@ -1685,13 +1730,13 @@
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>2.18</v>
+        <v>6.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="BN4">
         <v>5.9</v>
@@ -1703,40 +1748,40 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="CB4" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1744,31 +1789,31 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G5">
         <v>990</v>
       </c>
       <c r="H5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I5">
         <v>990</v>
       </c>
       <c r="J5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1804,10 +1849,10 @@
         <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1921,64 +1966,64 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1986,16 +2031,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F6">
         <v>1.1</v>
@@ -2220,7 +2265,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2228,31 +2273,31 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F7">
         <v>1.65</v>
       </c>
       <c r="G7">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H7">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I7">
         <v>6.4</v>
       </c>
       <c r="J7">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K7">
         <v>4.3</v>
@@ -2261,13 +2306,13 @@
         <v>1.36</v>
       </c>
       <c r="M7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P7">
         <v>1.94</v>
@@ -2276,7 +2321,7 @@
         <v>1.96</v>
       </c>
       <c r="R7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
         <v>3.5</v>
@@ -2285,19 +2330,19 @@
         <v>1.96</v>
       </c>
       <c r="U7">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V7">
         <v>1.18</v>
       </c>
       <c r="W7">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z7">
         <v>60</v>
@@ -2306,7 +2351,7 @@
         <v>210</v>
       </c>
       <c r="AB7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7">
         <v>9.199999999999999</v>
@@ -2336,7 +2381,7 @@
         <v>18.5</v>
       </c>
       <c r="AL7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM7">
         <v>160</v>
@@ -2354,10 +2399,10 @@
         <v>16.5</v>
       </c>
       <c r="AR7">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AS7">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT7">
         <v>7.4</v>
@@ -2369,7 +2414,7 @@
         <v>20</v>
       </c>
       <c r="AW7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX7">
         <v>8.6</v>
@@ -2381,7 +2426,7 @@
         <v>19.5</v>
       </c>
       <c r="BA7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB7">
         <v>14</v>
@@ -2390,16 +2435,16 @@
         <v>16</v>
       </c>
       <c r="BD7">
-        <v>9.4</v>
+        <v>19</v>
       </c>
       <c r="BE7">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF7">
         <v>9</v>
       </c>
       <c r="BG7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2411,58 +2456,58 @@
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="CB7" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2470,22 +2515,22 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F8">
         <v>3.1</v>
       </c>
       <c r="G8">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H8">
         <v>2.16</v>
@@ -2521,7 +2566,7 @@
         <v>1.14</v>
       </c>
       <c r="S8">
-        <v>3.2</v>
+        <v>1.05</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2533,7 +2578,7 @@
         <v>1.52</v>
       </c>
       <c r="W8">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2647,138 +2692,138 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F9">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="H9">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="J9">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="K9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M9">
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.07</v>
+        <v>2.18</v>
       </c>
       <c r="O9">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="P9">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="Q9">
-        <v>1.16</v>
+        <v>2.42</v>
       </c>
       <c r="R9">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="S9">
-        <v>1.16</v>
+        <v>4</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y9">
         <v>1000</v>
@@ -2832,52 +2877,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2889,64 +2934,64 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2954,70 +2999,70 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F10">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="G10">
-        <v>990</v>
+        <v>2.08</v>
       </c>
       <c r="H10">
+        <v>4.8</v>
+      </c>
+      <c r="I10">
+        <v>6.2</v>
+      </c>
+      <c r="J10">
+        <v>3.1</v>
+      </c>
+      <c r="K10">
+        <v>3.45</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
         <v>1.12</v>
       </c>
-      <c r="I10">
-        <v>990</v>
-      </c>
-      <c r="J10">
-        <v>1.12</v>
-      </c>
-      <c r="K10">
-        <v>3.1</v>
-      </c>
-      <c r="L10">
-        <v>1.01</v>
-      </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
       <c r="N10">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="O10">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="P10">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="Q10">
-        <v>1.62</v>
+        <v>2.36</v>
       </c>
       <c r="R10">
         <v>1.08</v>
       </c>
       <c r="S10">
-        <v>1.62</v>
+        <v>5</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V10">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3035,7 +3080,7 @@
         <v>1000</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD10">
         <v>1000</v>
@@ -3044,7 +3089,7 @@
         <v>1000</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG10">
         <v>1000</v>
@@ -3062,7 +3107,7 @@
         <v>1000</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM10">
         <v>1000</v>
@@ -3104,16 +3149,16 @@
         <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BA10">
         <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BD10">
         <v>1.03</v>
@@ -3122,7 +3167,7 @@
         <v>1.03</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG10">
         <v>1.01</v>
@@ -3131,64 +3176,64 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="CB10" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3196,58 +3241,58 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F11">
-        <v>3.2</v>
+        <v>2.32</v>
       </c>
       <c r="G11">
-        <v>4.8</v>
+        <v>2.68</v>
       </c>
       <c r="H11">
-        <v>2.14</v>
+        <v>3.35</v>
       </c>
       <c r="I11">
-        <v>2.7</v>
+        <v>870</v>
       </c>
       <c r="J11">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>3.05</v>
       </c>
       <c r="L11">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O11">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="P11">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="Q11">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="R11">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="S11">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3256,13 +3301,13 @@
         <v>1.11</v>
       </c>
       <c r="V11">
+        <v>1.32</v>
+      </c>
+      <c r="W11">
         <v>1.6</v>
       </c>
-      <c r="W11">
-        <v>1.31</v>
-      </c>
       <c r="X11">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
         <v>1000</v>
@@ -3373,135 +3418,135 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="F12">
-        <v>1.89</v>
+        <v>1.1</v>
       </c>
       <c r="G12">
-        <v>2.08</v>
+        <v>600</v>
       </c>
       <c r="H12">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="I12">
-        <v>6.2</v>
+        <v>870</v>
       </c>
       <c r="J12">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="K12">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>2.42</v>
+        <v>1.1</v>
       </c>
       <c r="O12">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="P12">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="Q12">
-        <v>2.46</v>
+        <v>1.16</v>
       </c>
       <c r="R12">
         <v>1.08</v>
       </c>
       <c r="S12">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="T12">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="W12">
-        <v>1.94</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3519,7 +3564,7 @@
         <v>1000</v>
       </c>
       <c r="AC12">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
         <v>1000</v>
@@ -3528,7 +3573,7 @@
         <v>1000</v>
       </c>
       <c r="AF12">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
         <v>1000</v>
@@ -3546,7 +3591,7 @@
         <v>1000</v>
       </c>
       <c r="AL12">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
         <v>1000</v>
@@ -3606,7 +3651,7 @@
         <v>1.03</v>
       </c>
       <c r="BF12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
         <v>1.01</v>
@@ -3615,64 +3660,64 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3680,19 +3725,19 @@
         <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E13" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="F13">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G13">
         <v>2.66</v>
@@ -3725,7 +3770,7 @@
         <v>2.04</v>
       </c>
       <c r="Q13">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R13">
         <v>1.41</v>
@@ -3785,7 +3830,7 @@
         <v>36</v>
       </c>
       <c r="AK13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL13">
         <v>40</v>
@@ -3797,7 +3842,7 @@
         <v>22</v>
       </c>
       <c r="AO13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP13">
         <v>14</v>
@@ -3809,7 +3854,7 @@
         <v>18.5</v>
       </c>
       <c r="AS13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT13">
         <v>10</v>
@@ -3833,7 +3878,7 @@
         <v>14</v>
       </c>
       <c r="BA13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BB13">
         <v>27</v>
@@ -3845,7 +3890,7 @@
         <v>30</v>
       </c>
       <c r="BE13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF13">
         <v>16</v>
@@ -3914,7 +3959,7 @@
         <v>3</v>
       </c>
       <c r="CB13" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3922,16 +3967,16 @@
         <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E14" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F14">
         <v>2.3</v>
@@ -4099,7 +4144,7 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
@@ -4156,7 +4201,7 @@
         <v>1.45</v>
       </c>
       <c r="CB14" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4164,16 +4209,16 @@
         <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E15" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F15">
         <v>1.46</v>
@@ -4341,64 +4386,64 @@
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4406,16 +4451,16 @@
         <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E16" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F16">
         <v>3.3</v>
@@ -4424,16 +4469,16 @@
         <v>3.9</v>
       </c>
       <c r="H16">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I16">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="J16">
         <v>3.4</v>
       </c>
       <c r="K16">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4448,7 +4493,7 @@
         <v>1.29</v>
       </c>
       <c r="P16">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q16">
         <v>1.85</v>
@@ -4472,7 +4517,7 @@
         <v>1.34</v>
       </c>
       <c r="X16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y16">
         <v>12</v>
@@ -4484,7 +4529,7 @@
         <v>34</v>
       </c>
       <c r="AB16">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC16">
         <v>9.6</v>
@@ -4496,10 +4541,10 @@
         <v>27</v>
       </c>
       <c r="AF16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH16">
         <v>20</v>
@@ -4511,16 +4556,16 @@
         <v>75</v>
       </c>
       <c r="AK16">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL16">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM16">
         <v>100</v>
       </c>
       <c r="AN16">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO16">
         <v>19.5</v>
@@ -4532,10 +4577,10 @@
         <v>8</v>
       </c>
       <c r="AR16">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AT16">
         <v>10.5</v>
@@ -4547,13 +4592,13 @@
         <v>8.6</v>
       </c>
       <c r="AW16">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
         <v>13</v>
@@ -4577,87 +4622,87 @@
         <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
         <v>1000</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F17">
         <v>1.97</v>
@@ -4666,10 +4711,10 @@
         <v>2.22</v>
       </c>
       <c r="H17">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="J17">
         <v>2.68</v>
@@ -4708,7 +4753,7 @@
         <v>1.11</v>
       </c>
       <c r="V17">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W17">
         <v>1.81</v>
@@ -4882,7 +4927,7 @@
         <v>1.85</v>
       </c>
       <c r="CB17" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4890,19 +4935,19 @@
         <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E18" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F18">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G18">
         <v>1.44</v>
@@ -5124,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5132,16 +5177,16 @@
         <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="F19">
         <v>2.68</v>
@@ -5366,7 +5411,7 @@
         <v>1.53</v>
       </c>
       <c r="CB19" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5374,16 +5419,16 @@
         <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E20" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="F20">
         <v>1.57</v>
@@ -5551,64 +5596,1274 @@
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>140</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21">
+        <v>4.3</v>
+      </c>
+      <c r="G21">
+        <v>4.7</v>
+      </c>
+      <c r="H21">
+        <v>1.87</v>
+      </c>
+      <c r="I21">
+        <v>1.96</v>
+      </c>
+      <c r="J21">
+        <v>3.8</v>
+      </c>
+      <c r="K21">
+        <v>4.2</v>
+      </c>
+      <c r="L21">
+        <v>1.35</v>
+      </c>
+      <c r="M21">
+        <v>1.05</v>
+      </c>
+      <c r="N21">
+        <v>4.2</v>
+      </c>
+      <c r="O21">
+        <v>1.27</v>
+      </c>
+      <c r="P21">
+        <v>2.12</v>
+      </c>
+      <c r="Q21">
+        <v>1.8</v>
+      </c>
+      <c r="R21">
+        <v>1.45</v>
+      </c>
+      <c r="S21">
+        <v>2.96</v>
+      </c>
+      <c r="T21">
+        <v>1.72</v>
+      </c>
+      <c r="U21">
+        <v>2.22</v>
+      </c>
+      <c r="V21">
+        <v>2.04</v>
+      </c>
+      <c r="W21">
+        <v>1.27</v>
+      </c>
+      <c r="X21">
+        <v>22</v>
+      </c>
+      <c r="Y21">
+        <v>10.5</v>
+      </c>
+      <c r="Z21">
+        <v>13</v>
+      </c>
+      <c r="AA21">
+        <v>22</v>
+      </c>
+      <c r="AB21">
+        <v>18</v>
+      </c>
+      <c r="AC21">
+        <v>9</v>
+      </c>
+      <c r="AD21">
+        <v>10.5</v>
+      </c>
+      <c r="AE21">
+        <v>19.5</v>
+      </c>
+      <c r="AF21">
+        <v>36</v>
+      </c>
+      <c r="AG21">
+        <v>18</v>
+      </c>
+      <c r="AH21">
+        <v>18</v>
+      </c>
+      <c r="AI21">
+        <v>32</v>
+      </c>
+      <c r="AJ21">
+        <v>120</v>
+      </c>
+      <c r="AK21">
+        <v>55</v>
+      </c>
+      <c r="AL21">
+        <v>65</v>
+      </c>
+      <c r="AM21">
+        <v>100</v>
+      </c>
+      <c r="AN21">
+        <v>60</v>
+      </c>
+      <c r="AO21">
+        <v>11</v>
+      </c>
+      <c r="AP21">
+        <v>15.5</v>
+      </c>
+      <c r="AQ21">
+        <v>9</v>
+      </c>
+      <c r="AR21">
+        <v>11</v>
+      </c>
+      <c r="AS21">
+        <v>18.5</v>
+      </c>
+      <c r="AT21">
+        <v>15.5</v>
+      </c>
+      <c r="AU21">
+        <v>8</v>
+      </c>
+      <c r="AV21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW21">
+        <v>16.5</v>
+      </c>
+      <c r="AX21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY21">
+        <v>15.5</v>
+      </c>
+      <c r="AZ21">
+        <v>15.5</v>
+      </c>
+      <c r="BA21">
+        <v>8</v>
+      </c>
+      <c r="BB21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC21">
+        <v>9</v>
+      </c>
+      <c r="BD21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG21">
+        <v>9.6</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
+        <v>1.58</v>
+      </c>
+      <c r="BJ21">
+        <v>1000</v>
+      </c>
+      <c r="BK21">
+        <v>2.2</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>2.62</v>
+      </c>
+      <c r="BN21">
+        <v>1000</v>
+      </c>
+      <c r="BO21">
+        <v>2.08</v>
+      </c>
+      <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
+        <v>2.62</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>2.62</v>
+      </c>
+      <c r="BT21">
+        <v>1000</v>
+      </c>
+      <c r="BU21">
+        <v>1.76</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>2.62</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>2.62</v>
+      </c>
+      <c r="BZ21">
+        <v>1000</v>
+      </c>
+      <c r="CA21">
+        <v>2.62</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F22">
+        <v>2.42</v>
+      </c>
+      <c r="G22">
+        <v>2.66</v>
+      </c>
+      <c r="H22">
+        <v>3.2</v>
+      </c>
+      <c r="I22">
+        <v>3.6</v>
+      </c>
+      <c r="J22">
+        <v>3.15</v>
+      </c>
+      <c r="K22">
+        <v>3.35</v>
+      </c>
+      <c r="L22">
+        <v>1.47</v>
+      </c>
+      <c r="M22">
+        <v>1.11</v>
+      </c>
+      <c r="N22">
+        <v>2.62</v>
+      </c>
+      <c r="O22">
+        <v>1.49</v>
+      </c>
+      <c r="P22">
+        <v>1.64</v>
+      </c>
+      <c r="Q22">
+        <v>2.42</v>
+      </c>
+      <c r="R22">
+        <v>1.2</v>
+      </c>
+      <c r="S22">
+        <v>4.5</v>
+      </c>
+      <c r="T22">
+        <v>1.93</v>
+      </c>
+      <c r="U22">
+        <v>1.78</v>
+      </c>
+      <c r="V22">
+        <v>1.4</v>
+      </c>
+      <c r="W22">
+        <v>1.61</v>
+      </c>
+      <c r="X22">
+        <v>970</v>
+      </c>
+      <c r="Y22">
+        <v>12.5</v>
+      </c>
+      <c r="Z22">
+        <v>30</v>
+      </c>
+      <c r="AA22">
+        <v>95</v>
+      </c>
+      <c r="AB22">
+        <v>10</v>
+      </c>
+      <c r="AC22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD22">
+        <v>20</v>
+      </c>
+      <c r="AE22">
+        <v>70</v>
+      </c>
+      <c r="AF22">
+        <v>21</v>
+      </c>
+      <c r="AG22">
+        <v>15</v>
+      </c>
+      <c r="AH22">
+        <v>29</v>
+      </c>
+      <c r="AI22">
+        <v>95</v>
+      </c>
+      <c r="AJ22">
+        <v>50</v>
+      </c>
+      <c r="AK22">
+        <v>46</v>
+      </c>
+      <c r="AL22">
+        <v>70</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>46</v>
+      </c>
+      <c r="AO22">
+        <v>85</v>
+      </c>
+      <c r="AP22">
+        <v>2.98</v>
+      </c>
+      <c r="AQ22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR22">
+        <v>15</v>
+      </c>
+      <c r="AS22">
+        <v>3.5</v>
+      </c>
+      <c r="AT22">
+        <v>7</v>
+      </c>
+      <c r="AU22">
+        <v>6</v>
+      </c>
+      <c r="AV22">
+        <v>11</v>
+      </c>
+      <c r="AW22">
+        <v>3.45</v>
+      </c>
+      <c r="AX22">
+        <v>11</v>
+      </c>
+      <c r="AY22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ22">
+        <v>3.25</v>
+      </c>
+      <c r="BA22">
+        <v>3.5</v>
+      </c>
+      <c r="BB22">
+        <v>3.4</v>
+      </c>
+      <c r="BC22">
+        <v>3.35</v>
+      </c>
+      <c r="BD22">
+        <v>3.45</v>
+      </c>
+      <c r="BE22">
+        <v>3.65</v>
+      </c>
+      <c r="BF22">
+        <v>22</v>
+      </c>
+      <c r="BG22">
+        <v>3.5</v>
+      </c>
+      <c r="BH22">
+        <v>3.4</v>
+      </c>
+      <c r="BI22">
+        <v>2.32</v>
+      </c>
+      <c r="BJ22">
+        <v>1000</v>
+      </c>
+      <c r="BK22">
+        <v>1.43</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.43</v>
+      </c>
+      <c r="BN22">
+        <v>1000</v>
+      </c>
+      <c r="BO22">
+        <v>1.5</v>
+      </c>
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
+        <v>1.43</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>1.43</v>
+      </c>
+      <c r="BT22">
+        <v>1000</v>
+      </c>
+      <c r="BU22">
+        <v>1.43</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>1.43</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>1.43</v>
+      </c>
+      <c r="BZ22">
+        <v>1000</v>
+      </c>
+      <c r="CA22">
+        <v>1.43</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" t="s">
+        <v>152</v>
+      </c>
+      <c r="F23">
+        <v>3.4</v>
+      </c>
+      <c r="G23">
+        <v>3.6</v>
+      </c>
+      <c r="H23">
+        <v>2.26</v>
+      </c>
+      <c r="I23">
+        <v>2.38</v>
+      </c>
+      <c r="J23">
+        <v>3.45</v>
+      </c>
+      <c r="K23">
+        <v>3.6</v>
+      </c>
+      <c r="L23">
+        <v>1.37</v>
+      </c>
+      <c r="M23">
+        <v>1.07</v>
+      </c>
+      <c r="N23">
+        <v>3.7</v>
+      </c>
+      <c r="O23">
+        <v>1.32</v>
+      </c>
+      <c r="P23">
+        <v>1.91</v>
+      </c>
+      <c r="Q23">
+        <v>1.96</v>
+      </c>
+      <c r="R23">
+        <v>1.36</v>
+      </c>
+      <c r="S23">
+        <v>3.4</v>
+      </c>
+      <c r="T23">
+        <v>1.72</v>
+      </c>
+      <c r="U23">
+        <v>2.12</v>
+      </c>
+      <c r="V23">
+        <v>1.72</v>
+      </c>
+      <c r="W23">
+        <v>1.38</v>
+      </c>
+      <c r="X23">
+        <v>1000</v>
+      </c>
+      <c r="Y23">
+        <v>970</v>
+      </c>
+      <c r="Z23">
+        <v>970</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>970</v>
+      </c>
+      <c r="AC23">
+        <v>970</v>
+      </c>
+      <c r="AD23">
+        <v>970</v>
+      </c>
+      <c r="AE23">
+        <v>27</v>
+      </c>
+      <c r="AF23">
+        <v>30</v>
+      </c>
+      <c r="AG23">
+        <v>15.5</v>
+      </c>
+      <c r="AH23">
+        <v>21</v>
+      </c>
+      <c r="AI23">
+        <v>1000</v>
+      </c>
+      <c r="AJ23">
+        <v>1000</v>
+      </c>
+      <c r="AK23">
+        <v>1000</v>
+      </c>
+      <c r="AL23">
+        <v>1000</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>46</v>
+      </c>
+      <c r="AO23">
+        <v>1000</v>
+      </c>
+      <c r="AP23">
+        <v>2.24</v>
+      </c>
+      <c r="AQ23">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR23">
+        <v>1.97</v>
+      </c>
+      <c r="AS23">
+        <v>21</v>
+      </c>
+      <c r="AT23">
+        <v>11</v>
+      </c>
+      <c r="AU23">
+        <v>1.84</v>
+      </c>
+      <c r="AV23">
+        <v>2</v>
+      </c>
+      <c r="AW23">
+        <v>17.5</v>
+      </c>
+      <c r="AX23">
+        <v>16.5</v>
+      </c>
+      <c r="AY23">
+        <v>1.96</v>
+      </c>
+      <c r="AZ23">
+        <v>2.02</v>
+      </c>
+      <c r="BA23">
+        <v>1.96</v>
+      </c>
+      <c r="BB23">
+        <v>2.26</v>
+      </c>
+      <c r="BC23">
+        <v>1.96</v>
+      </c>
+      <c r="BD23">
+        <v>2.26</v>
+      </c>
+      <c r="BE23">
+        <v>1.96</v>
+      </c>
+      <c r="BF23">
+        <v>1.88</v>
+      </c>
+      <c r="BG23">
+        <v>16</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>1.04</v>
+      </c>
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
+        <v>1.58</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.58</v>
+      </c>
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
+        <v>1.58</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
+        <v>1.58</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.58</v>
+      </c>
+      <c r="BT23">
+        <v>1000</v>
+      </c>
+      <c r="BU23">
+        <v>1.12</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>1.58</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.58</v>
+      </c>
+      <c r="BZ23">
+        <v>1000</v>
+      </c>
+      <c r="CA23">
+        <v>1.58</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" t="s">
+        <v>153</v>
+      </c>
+      <c r="F24">
+        <v>2.16</v>
+      </c>
+      <c r="G24">
+        <v>2.24</v>
+      </c>
+      <c r="H24">
+        <v>3.8</v>
+      </c>
+      <c r="I24">
+        <v>4.1</v>
+      </c>
+      <c r="J24">
+        <v>3.45</v>
+      </c>
+      <c r="K24">
+        <v>3.5</v>
+      </c>
+      <c r="L24">
+        <v>1.44</v>
+      </c>
+      <c r="M24">
+        <v>1.08</v>
+      </c>
+      <c r="N24">
+        <v>3.5</v>
+      </c>
+      <c r="O24">
+        <v>1.34</v>
+      </c>
+      <c r="P24">
+        <v>1.84</v>
+      </c>
+      <c r="Q24">
+        <v>2.06</v>
+      </c>
+      <c r="R24">
+        <v>1.29</v>
+      </c>
+      <c r="S24">
+        <v>3.7</v>
+      </c>
+      <c r="T24">
+        <v>1.86</v>
+      </c>
+      <c r="U24">
+        <v>2.06</v>
+      </c>
+      <c r="V24">
+        <v>1.32</v>
+      </c>
+      <c r="W24">
+        <v>1.8</v>
+      </c>
+      <c r="X24">
+        <v>22</v>
+      </c>
+      <c r="Y24">
+        <v>16</v>
+      </c>
+      <c r="Z24">
+        <v>38</v>
+      </c>
+      <c r="AA24">
+        <v>100</v>
+      </c>
+      <c r="AB24">
+        <v>10</v>
+      </c>
+      <c r="AC24">
+        <v>8.6</v>
+      </c>
+      <c r="AD24">
+        <v>19</v>
+      </c>
+      <c r="AE24">
+        <v>65</v>
+      </c>
+      <c r="AF24">
+        <v>15.5</v>
+      </c>
+      <c r="AG24">
+        <v>12.5</v>
+      </c>
+      <c r="AH24">
+        <v>21</v>
+      </c>
+      <c r="AI24">
+        <v>90</v>
+      </c>
+      <c r="AJ24">
+        <v>38</v>
+      </c>
+      <c r="AK24">
+        <v>32</v>
+      </c>
+      <c r="AL24">
+        <v>48</v>
+      </c>
+      <c r="AM24">
+        <v>1000</v>
+      </c>
+      <c r="AN24">
+        <v>25</v>
+      </c>
+      <c r="AO24">
+        <v>80</v>
+      </c>
+      <c r="AP24">
+        <v>10</v>
+      </c>
+      <c r="AQ24">
+        <v>10.5</v>
+      </c>
+      <c r="AR24">
+        <v>19</v>
+      </c>
+      <c r="AS24">
+        <v>4.3</v>
+      </c>
+      <c r="AT24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU24">
+        <v>6.8</v>
+      </c>
+      <c r="AV24">
+        <v>12.5</v>
+      </c>
+      <c r="AW24">
+        <v>4.2</v>
+      </c>
+      <c r="AX24">
+        <v>10</v>
+      </c>
+      <c r="AY24">
+        <v>9.6</v>
+      </c>
+      <c r="AZ24">
+        <v>3.7</v>
+      </c>
+      <c r="BA24">
+        <v>4.2</v>
+      </c>
+      <c r="BB24">
+        <v>4</v>
+      </c>
+      <c r="BC24">
+        <v>19</v>
+      </c>
+      <c r="BD24">
+        <v>4.1</v>
+      </c>
+      <c r="BE24">
+        <v>4.5</v>
+      </c>
+      <c r="BF24">
+        <v>14</v>
+      </c>
+      <c r="BG24">
+        <v>4.2</v>
+      </c>
+      <c r="BH24">
+        <v>3.8</v>
+      </c>
+      <c r="BI24">
+        <v>2.66</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>2.46</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>2.48</v>
+      </c>
+      <c r="BN24">
+        <v>6.2</v>
+      </c>
+      <c r="BO24">
+        <v>3.65</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>2.9</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>2.48</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>5</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>2.48</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>2.48</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
+        <v>2.48</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" t="s">
+        <v>154</v>
+      </c>
+      <c r="F25">
+        <v>1.64</v>
+      </c>
+      <c r="G25">
+        <v>1.79</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="I25">
+        <v>6.2</v>
+      </c>
+      <c r="J25">
+        <v>3.9</v>
+      </c>
+      <c r="K25">
+        <v>4.4</v>
+      </c>
+      <c r="L25">
+        <v>1.01</v>
+      </c>
+      <c r="M25">
+        <v>1.06</v>
+      </c>
+      <c r="N25">
+        <v>4</v>
+      </c>
+      <c r="O25">
+        <v>1.28</v>
+      </c>
+      <c r="P25">
+        <v>1.96</v>
+      </c>
+      <c r="Q25">
+        <v>1.8</v>
+      </c>
+      <c r="R25">
+        <v>1.4</v>
+      </c>
+      <c r="S25">
+        <v>3.1</v>
+      </c>
+      <c r="T25">
+        <v>1.85</v>
+      </c>
+      <c r="U25">
+        <v>2.06</v>
+      </c>
+      <c r="V25">
+        <v>1.19</v>
+      </c>
+      <c r="W25">
+        <v>2.26</v>
+      </c>
+      <c r="X25">
+        <v>23</v>
+      </c>
+      <c r="Y25">
+        <v>950</v>
+      </c>
+      <c r="Z25">
+        <v>65</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>11</v>
+      </c>
+      <c r="AC25">
+        <v>10</v>
+      </c>
+      <c r="AD25">
+        <v>950</v>
+      </c>
+      <c r="AE25">
+        <v>100</v>
+      </c>
+      <c r="AF25">
+        <v>15</v>
+      </c>
+      <c r="AG25">
+        <v>13.5</v>
+      </c>
+      <c r="AH25">
+        <v>28</v>
+      </c>
+      <c r="AI25">
+        <v>100</v>
+      </c>
+      <c r="AJ25">
+        <v>23</v>
+      </c>
+      <c r="AK25">
+        <v>24</v>
+      </c>
+      <c r="AL25">
+        <v>48</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>10.5</v>
+      </c>
+      <c r="AO25">
+        <v>100</v>
+      </c>
+      <c r="AP25">
+        <v>3.4</v>
+      </c>
+      <c r="AQ25">
+        <v>16</v>
+      </c>
+      <c r="AR25">
+        <v>3.8</v>
+      </c>
+      <c r="AS25">
+        <v>4</v>
+      </c>
+      <c r="AT25">
+        <v>7.6</v>
+      </c>
+      <c r="AU25">
+        <v>7.8</v>
+      </c>
+      <c r="AV25">
+        <v>14</v>
+      </c>
+      <c r="AW25">
+        <v>3.9</v>
+      </c>
+      <c r="AX25">
+        <v>8.4</v>
+      </c>
+      <c r="AY25">
+        <v>8.4</v>
+      </c>
+      <c r="AZ25">
+        <v>16.5</v>
+      </c>
+      <c r="BA25">
+        <v>3.9</v>
+      </c>
+      <c r="BB25">
+        <v>11</v>
+      </c>
+      <c r="BC25">
+        <v>14.5</v>
+      </c>
+      <c r="BD25">
+        <v>3.75</v>
+      </c>
+      <c r="BE25">
+        <v>4</v>
+      </c>
+      <c r="BF25">
+        <v>7.6</v>
+      </c>
+      <c r="BG25">
+        <v>3.9</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>1.04</v>
+      </c>
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
+        <v>1.04</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>1.04</v>
+      </c>
+      <c r="BN25">
+        <v>1000</v>
+      </c>
+      <c r="BO25">
+        <v>1.04</v>
+      </c>
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
+        <v>1.04</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>1.04</v>
+      </c>
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
+        <v>1.04</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.04</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>1.04</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>1.04</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
@@ -481,7 +481,7 @@
     <t>Tolima</t>
   </si>
   <si>
-    <t>2026-10-07 02:01:18</t>
+    <t>2026-10-07 04:13:12</t>
   </si>
 </sst>
 </file>
@@ -1075,13 +1075,13 @@
         <v>131</v>
       </c>
       <c r="F2">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I2">
         <v>4.5</v>
@@ -1105,55 +1105,55 @@
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q2">
         <v>2.04</v>
       </c>
       <c r="R2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S2">
         <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U2">
         <v>2.1</v>
       </c>
       <c r="V2">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W2">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y2">
         <v>15</v>
       </c>
       <c r="Z2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB2">
         <v>9</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE2">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
@@ -1171,7 +1171,7 @@
         <v>22</v>
       </c>
       <c r="AL2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM2">
         <v>1000</v>
@@ -1180,25 +1180,25 @@
         <v>15</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP2">
         <v>13</v>
       </c>
       <c r="AQ2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS2">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AT2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV2">
         <v>15.5</v>
@@ -1210,34 +1210,34 @@
         <v>11</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB2">
         <v>20</v>
       </c>
       <c r="BC2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE2">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="BF2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI2">
         <v>3.05</v>
@@ -1252,7 +1252,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN2">
         <v>4.5</v>
@@ -1270,10 +1270,10 @@
         <v>30</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU2">
         <v>6.8</v>
@@ -1282,19 +1282,19 @@
         <v>40</v>
       </c>
       <c r="BW2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BX2">
         <v>50</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2">
         <v>27</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB2" t="s">
         <v>155</v>
@@ -1317,13 +1317,13 @@
         <v>132</v>
       </c>
       <c r="F3">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="G3">
         <v>4.9</v>
       </c>
       <c r="H3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I3">
         <v>2.76</v>
@@ -1332,7 +1332,7 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1341,7 +1341,7 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O3">
         <v>1.2</v>
@@ -1425,52 +1425,52 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
         <v>1.01</v>
@@ -1562,7 +1562,7 @@
         <v>1.62</v>
       </c>
       <c r="G4">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H4">
         <v>5.7</v>
@@ -1577,184 +1577,184 @@
         <v>4.6</v>
       </c>
       <c r="L4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M4">
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="O4">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R4">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S4">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="T4">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="U4">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V4">
         <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X4">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="Y4">
+        <v>23</v>
+      </c>
+      <c r="Z4">
+        <v>60</v>
+      </c>
+      <c r="AA4">
+        <v>180</v>
+      </c>
+      <c r="AB4">
+        <v>10</v>
+      </c>
+      <c r="AC4">
+        <v>10</v>
+      </c>
+      <c r="AD4">
+        <v>23</v>
+      </c>
+      <c r="AE4">
+        <v>90</v>
+      </c>
+      <c r="AF4">
+        <v>10.5</v>
+      </c>
+      <c r="AG4">
+        <v>10.5</v>
+      </c>
+      <c r="AH4">
+        <v>20</v>
+      </c>
+      <c r="AI4">
+        <v>85</v>
+      </c>
+      <c r="AJ4">
+        <v>16.5</v>
+      </c>
+      <c r="AK4">
+        <v>16.5</v>
+      </c>
+      <c r="AL4">
         <v>32</v>
       </c>
-      <c r="Z4">
-        <v>70</v>
-      </c>
-      <c r="AA4">
-        <v>1000</v>
-      </c>
-      <c r="AB4">
-        <v>13</v>
-      </c>
-      <c r="AC4">
-        <v>12</v>
-      </c>
-      <c r="AD4">
-        <v>29</v>
-      </c>
-      <c r="AE4">
+      <c r="AM4">
+        <v>120</v>
+      </c>
+      <c r="AN4">
+        <v>8</v>
+      </c>
+      <c r="AO4">
         <v>95</v>
       </c>
-      <c r="AF4">
-        <v>12.5</v>
-      </c>
-      <c r="AG4">
-        <v>12</v>
-      </c>
-      <c r="AH4">
-        <v>28</v>
-      </c>
-      <c r="AI4">
-        <v>100</v>
-      </c>
-      <c r="AJ4">
+      <c r="AP4">
+        <v>17</v>
+      </c>
+      <c r="AQ4">
         <v>19.5</v>
       </c>
-      <c r="AK4">
+      <c r="AR4">
+        <v>24</v>
+      </c>
+      <c r="AS4">
+        <v>11.5</v>
+      </c>
+      <c r="AT4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU4">
+        <v>9</v>
+      </c>
+      <c r="AV4">
         <v>19.5</v>
       </c>
-      <c r="AL4">
-        <v>46</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
+      <c r="AW4">
+        <v>10.5</v>
+      </c>
+      <c r="AX4">
         <v>9.4</v>
       </c>
-      <c r="AO4">
-        <v>100</v>
-      </c>
-      <c r="AP4">
-        <v>13.5</v>
-      </c>
-      <c r="AQ4">
+      <c r="AY4">
+        <v>9</v>
+      </c>
+      <c r="AZ4">
+        <v>17.5</v>
+      </c>
+      <c r="BA4">
+        <v>10.5</v>
+      </c>
+      <c r="BB4">
         <v>14</v>
       </c>
-      <c r="AR4">
+      <c r="BC4">
+        <v>14</v>
+      </c>
+      <c r="BD4">
+        <v>15</v>
+      </c>
+      <c r="BE4">
+        <v>11</v>
+      </c>
+      <c r="BF4">
+        <v>7</v>
+      </c>
+      <c r="BG4">
         <v>10.5</v>
       </c>
-      <c r="AS4">
-        <v>3.75</v>
-      </c>
-      <c r="AT4">
-        <v>8</v>
-      </c>
-      <c r="AU4">
-        <v>7.8</v>
-      </c>
-      <c r="AV4">
-        <v>14</v>
-      </c>
-      <c r="AW4">
-        <v>15</v>
-      </c>
-      <c r="AX4">
-        <v>8.6</v>
-      </c>
-      <c r="AY4">
-        <v>7.8</v>
-      </c>
-      <c r="AZ4">
-        <v>14.5</v>
-      </c>
-      <c r="BA4">
-        <v>15.5</v>
-      </c>
-      <c r="BB4">
-        <v>13.5</v>
-      </c>
-      <c r="BC4">
-        <v>13.5</v>
-      </c>
-      <c r="BD4">
-        <v>19</v>
-      </c>
-      <c r="BE4">
-        <v>3.75</v>
-      </c>
-      <c r="BF4">
-        <v>6</v>
-      </c>
-      <c r="BG4">
-        <v>3.6</v>
-      </c>
       <c r="BH4">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6.2</v>
+        <v>2.28</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BN4">
         <v>5.9</v>
       </c>
       <c r="BO4">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BT4">
         <v>1000</v>
@@ -1766,19 +1766,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CB4" t="s">
         <v>155</v>
@@ -1813,7 +1813,7 @@
         <v>990</v>
       </c>
       <c r="J5">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1849,10 +1849,10 @@
         <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1909,52 +1909,52 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
         <v>1.01</v>
@@ -2046,16 +2046,16 @@
         <v>1.1</v>
       </c>
       <c r="G6">
-        <v>600</v>
+        <v>1.8</v>
       </c>
       <c r="H6">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>870</v>
       </c>
       <c r="J6">
-        <v>1.12</v>
+        <v>2.24</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2073,7 +2073,7 @@
         <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q6">
         <v>1.02</v>
@@ -2291,13 +2291,13 @@
         <v>1.71</v>
       </c>
       <c r="H7">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I7">
         <v>6.4</v>
       </c>
       <c r="J7">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
         <v>4.3</v>
@@ -2309,10 +2309,10 @@
         <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P7">
         <v>1.94</v>
@@ -2321,7 +2321,7 @@
         <v>1.96</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S7">
         <v>3.5</v>
@@ -2330,7 +2330,7 @@
         <v>1.96</v>
       </c>
       <c r="U7">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V7">
         <v>1.18</v>
@@ -2399,7 +2399,7 @@
         <v>16.5</v>
       </c>
       <c r="AR7">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="AS7">
         <v>12.5</v>
@@ -2447,64 +2447,64 @@
         <v>12</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI7">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.77</v>
+        <v>3.45</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="CB7" t="s">
         <v>155</v>
@@ -2542,7 +2542,7 @@
         <v>2.68</v>
       </c>
       <c r="K8">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L8">
         <v>1.49</v>
@@ -2551,10 +2551,10 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2.68</v>
+        <v>2.36</v>
       </c>
       <c r="O8">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="P8">
         <v>1.48</v>
@@ -2566,7 +2566,7 @@
         <v>1.14</v>
       </c>
       <c r="S8">
-        <v>1.05</v>
+        <v>3.25</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2581,112 +2581,112 @@
         <v>1.27</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2775,7 +2775,7 @@
         <v>4.8</v>
       </c>
       <c r="H9">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="I9">
         <v>2.7</v>
@@ -2784,7 +2784,7 @@
         <v>2.42</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L9">
         <v>1.49</v>
@@ -2805,10 +2805,10 @@
         <v>2.42</v>
       </c>
       <c r="R9">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="S9">
-        <v>4</v>
+        <v>2.84</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2823,7 +2823,7 @@
         <v>1.31</v>
       </c>
       <c r="X9">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
         <v>1000</v>
@@ -2877,52 +2877,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -3011,7 +3011,7 @@
         <v>139</v>
       </c>
       <c r="F10">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="G10">
         <v>2.08</v>
@@ -3035,25 +3035,25 @@
         <v>1.12</v>
       </c>
       <c r="N10">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="O10">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P10">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q10">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="R10">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S10">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="T10">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U10">
         <v>1.7</v>
@@ -3062,175 +3062,175 @@
         <v>1.2</v>
       </c>
       <c r="W10">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC10">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL10">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB10">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
         <v>155</v>
@@ -3253,40 +3253,40 @@
         <v>140</v>
       </c>
       <c r="F11">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G11">
         <v>2.68</v>
       </c>
       <c r="H11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I11">
-        <v>870</v>
+        <v>4.9</v>
       </c>
       <c r="J11">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="K11">
         <v>3.05</v>
       </c>
       <c r="L11">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="M11">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N11">
         <v>2.2</v>
       </c>
       <c r="O11">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P11">
         <v>1.37</v>
       </c>
       <c r="Q11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R11">
         <v>1.11</v>
@@ -3361,52 +3361,52 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -3495,22 +3495,22 @@
         <v>141</v>
       </c>
       <c r="F12">
-        <v>1.1</v>
+        <v>2.24</v>
       </c>
       <c r="G12">
-        <v>600</v>
+        <v>2.6</v>
       </c>
       <c r="H12">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="I12">
-        <v>870</v>
+        <v>3.25</v>
       </c>
       <c r="J12">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="K12">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3519,34 +3519,34 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="O12">
         <v>1.16</v>
       </c>
       <c r="P12">
-        <v>1.08</v>
+        <v>2.28</v>
       </c>
       <c r="Q12">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="R12">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="S12">
-        <v>1.16</v>
+        <v>2.22</v>
       </c>
       <c r="T12">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.65</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3603,52 +3603,52 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
         <v>1.01</v>
@@ -3737,7 +3737,7 @@
         <v>142</v>
       </c>
       <c r="F13">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G13">
         <v>2.66</v>
@@ -3746,7 +3746,7 @@
         <v>2.88</v>
       </c>
       <c r="I13">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J13">
         <v>3.45</v>
@@ -3755,19 +3755,19 @@
         <v>3.65</v>
       </c>
       <c r="L13">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="M13">
         <v>1.06</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O13">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P13">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q13">
         <v>1.81</v>
@@ -3776,7 +3776,7 @@
         <v>1.41</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T13">
         <v>1.67</v>
@@ -3785,7 +3785,7 @@
         <v>2.24</v>
       </c>
       <c r="V13">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W13">
         <v>1.6</v>
@@ -3806,7 +3806,7 @@
         <v>12.5</v>
       </c>
       <c r="AC13">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD13">
         <v>13.5</v>
@@ -3815,7 +3815,7 @@
         <v>34</v>
       </c>
       <c r="AF13">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AG13">
         <v>12</v>
@@ -3842,7 +3842,7 @@
         <v>22</v>
       </c>
       <c r="AO13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP13">
         <v>14</v>
@@ -3854,10 +3854,10 @@
         <v>18.5</v>
       </c>
       <c r="AS13">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AT13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU13">
         <v>7.2</v>
@@ -3866,10 +3866,10 @@
         <v>11.5</v>
       </c>
       <c r="AW13">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AX13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY13">
         <v>10</v>
@@ -3878,7 +3878,7 @@
         <v>14</v>
       </c>
       <c r="BA13">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="BB13">
         <v>27</v>
@@ -3890,7 +3890,7 @@
         <v>30</v>
       </c>
       <c r="BE13">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF13">
         <v>16</v>
@@ -4087,16 +4087,16 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
         <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
         <v>1.01</v>
@@ -4105,10 +4105,10 @@
         <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
         <v>1.01</v>
@@ -4117,22 +4117,22 @@
         <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
         <v>1.01</v>
@@ -4162,7 +4162,7 @@
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="BP14">
         <v>1000</v>
@@ -4224,55 +4224,55 @@
         <v>1.46</v>
       </c>
       <c r="G15">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H15">
         <v>8</v>
       </c>
       <c r="I15">
-        <v>990</v>
+        <v>11.5</v>
       </c>
       <c r="J15">
-        <v>3.95</v>
+        <v>1.12</v>
       </c>
       <c r="K15">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="O15">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Q15">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R15">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S15">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="T15">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U15">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="V15">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W15">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="X15">
         <v>13</v>
@@ -4305,7 +4305,7 @@
         <v>11</v>
       </c>
       <c r="AH15">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI15">
         <v>180</v>
@@ -4392,13 +4392,13 @@
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BN15">
         <v>1000</v>
@@ -4410,37 +4410,37 @@
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="CB15" t="s">
         <v>155</v>
@@ -4466,13 +4466,13 @@
         <v>3.3</v>
       </c>
       <c r="G16">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H16">
         <v>2.14</v>
       </c>
       <c r="I16">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="J16">
         <v>3.4</v>
@@ -4490,7 +4490,7 @@
         <v>3.75</v>
       </c>
       <c r="O16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P16">
         <v>1.94</v>
@@ -4514,7 +4514,7 @@
         <v>1.72</v>
       </c>
       <c r="W16">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X16">
         <v>17.5</v>
@@ -4577,7 +4577,7 @@
         <v>8</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS16">
         <v>18</v>
@@ -4592,37 +4592,37 @@
         <v>8.6</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ16">
         <v>13</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4705,22 +4705,22 @@
         <v>146</v>
       </c>
       <c r="F17">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G17">
         <v>2.22</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I17">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J17">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="K17">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4729,31 +4729,31 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="O17">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="P17">
         <v>1.37</v>
       </c>
       <c r="Q17">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="R17">
         <v>1.08</v>
       </c>
       <c r="S17">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="T17">
         <v>1.11</v>
       </c>
       <c r="U17">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="V17">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="W17">
         <v>1.81</v>
@@ -4813,52 +4813,52 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
         <v>1.01</v>
@@ -4870,7 +4870,7 @@
         <v>2.94</v>
       </c>
       <c r="BI17">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
@@ -4882,7 +4882,7 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="BN17">
         <v>1000</v>
@@ -4900,7 +4900,7 @@
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="BT17">
         <v>1000</v>
@@ -4912,19 +4912,19 @@
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="CB17" t="s">
         <v>155</v>
@@ -4947,10 +4947,10 @@
         <v>147</v>
       </c>
       <c r="F18">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G18">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="H18">
         <v>8</v>
@@ -4962,7 +4962,7 @@
         <v>4.9</v>
       </c>
       <c r="K18">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4977,10 +4977,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.07</v>
+        <v>2.16</v>
       </c>
       <c r="Q18">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5198,10 +5198,10 @@
         <v>2.9</v>
       </c>
       <c r="I19">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="J19">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="K19">
         <v>3.55</v>
@@ -5210,7 +5210,7 @@
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N19">
         <v>2.16</v>
@@ -5222,7 +5222,7 @@
         <v>1.36</v>
       </c>
       <c r="Q19">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="R19">
         <v>1.08</v>
@@ -5231,13 +5231,13 @@
         <v>3.1</v>
       </c>
       <c r="T19">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="W19">
         <v>1.49</v>
@@ -5297,52 +5297,52 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
         <v>1.01</v>
@@ -5372,7 +5372,7 @@
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="BP19">
         <v>1000</v>
@@ -5390,7 +5390,7 @@
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="BV19">
         <v>1000</v>
@@ -5431,166 +5431,166 @@
         <v>149</v>
       </c>
       <c r="F20">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="H20">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="I20">
         <v>5</v>
       </c>
       <c r="J20">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="K20">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="O20">
         <v>1.29</v>
       </c>
       <c r="P20">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Q20">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="R20">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="S20">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="T20">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="U20">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V20">
         <v>1.25</v>
       </c>
       <c r="W20">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP20">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ20">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AR20">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS20">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV20">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AW20">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ20">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA20">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BC20">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BD20">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BE20">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5688,7 +5688,7 @@
         <v>3.8</v>
       </c>
       <c r="K21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L21">
         <v>1.35</v>
@@ -5697,13 +5697,13 @@
         <v>1.05</v>
       </c>
       <c r="N21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O21">
         <v>1.27</v>
       </c>
       <c r="P21">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q21">
         <v>1.8</v>
@@ -5715,7 +5715,7 @@
         <v>2.96</v>
       </c>
       <c r="T21">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U21">
         <v>2.22</v>
@@ -5784,7 +5784,7 @@
         <v>15.5</v>
       </c>
       <c r="AQ21">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR21">
         <v>11</v>
@@ -5915,16 +5915,16 @@
         <v>151</v>
       </c>
       <c r="F22">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G22">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H22">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I22">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J22">
         <v>3.15</v>
@@ -5933,13 +5933,13 @@
         <v>3.35</v>
       </c>
       <c r="L22">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M22">
         <v>1.11</v>
       </c>
       <c r="N22">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="O22">
         <v>1.49</v>
@@ -5951,190 +5951,190 @@
         <v>2.42</v>
       </c>
       <c r="R22">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S22">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T22">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="U22">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="V22">
         <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X22">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y22">
+        <v>11</v>
+      </c>
+      <c r="Z22">
+        <v>27</v>
+      </c>
+      <c r="AA22">
+        <v>80</v>
+      </c>
+      <c r="AB22">
+        <v>8.4</v>
+      </c>
+      <c r="AC22">
+        <v>7.4</v>
+      </c>
+      <c r="AD22">
+        <v>15.5</v>
+      </c>
+      <c r="AE22">
+        <v>60</v>
+      </c>
+      <c r="AF22">
+        <v>16.5</v>
+      </c>
+      <c r="AG22">
         <v>12.5</v>
       </c>
-      <c r="Z22">
+      <c r="AH22">
+        <v>22</v>
+      </c>
+      <c r="AI22">
+        <v>80</v>
+      </c>
+      <c r="AJ22">
+        <v>40</v>
+      </c>
+      <c r="AK22">
+        <v>36</v>
+      </c>
+      <c r="AL22">
+        <v>65</v>
+      </c>
+      <c r="AM22">
+        <v>180</v>
+      </c>
+      <c r="AN22">
+        <v>36</v>
+      </c>
+      <c r="AO22">
+        <v>70</v>
+      </c>
+      <c r="AP22">
+        <v>8.6</v>
+      </c>
+      <c r="AQ22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR22">
+        <v>20</v>
+      </c>
+      <c r="AS22">
+        <v>7.8</v>
+      </c>
+      <c r="AT22">
+        <v>7.4</v>
+      </c>
+      <c r="AU22">
+        <v>6.6</v>
+      </c>
+      <c r="AV22">
+        <v>13</v>
+      </c>
+      <c r="AW22">
         <v>30</v>
       </c>
-      <c r="AA22">
-        <v>95</v>
-      </c>
-      <c r="AB22">
-        <v>10</v>
-      </c>
-      <c r="AC22">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD22">
-        <v>20</v>
-      </c>
-      <c r="AE22">
-        <v>70</v>
-      </c>
-      <c r="AF22">
-        <v>21</v>
-      </c>
-      <c r="AG22">
-        <v>15</v>
-      </c>
-      <c r="AH22">
-        <v>29</v>
-      </c>
-      <c r="AI22">
-        <v>95</v>
-      </c>
-      <c r="AJ22">
-        <v>50</v>
-      </c>
-      <c r="AK22">
-        <v>46</v>
-      </c>
-      <c r="AL22">
-        <v>70</v>
-      </c>
-      <c r="AM22">
-        <v>1000</v>
-      </c>
-      <c r="AN22">
-        <v>46</v>
-      </c>
-      <c r="AO22">
-        <v>85</v>
-      </c>
-      <c r="AP22">
-        <v>2.98</v>
-      </c>
-      <c r="AQ22">
+      <c r="AX22">
+        <v>13</v>
+      </c>
+      <c r="AY22">
+        <v>10.5</v>
+      </c>
+      <c r="AZ22">
+        <v>18.5</v>
+      </c>
+      <c r="BA22">
+        <v>7.8</v>
+      </c>
+      <c r="BB22">
+        <v>27</v>
+      </c>
+      <c r="BC22">
+        <v>7</v>
+      </c>
+      <c r="BD22">
+        <v>7.8</v>
+      </c>
+      <c r="BE22">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AR22">
-        <v>15</v>
-      </c>
-      <c r="AS22">
-        <v>3.5</v>
-      </c>
-      <c r="AT22">
-        <v>7</v>
-      </c>
-      <c r="AU22">
-        <v>6</v>
-      </c>
-      <c r="AV22">
-        <v>11</v>
-      </c>
-      <c r="AW22">
-        <v>3.45</v>
-      </c>
-      <c r="AX22">
-        <v>11</v>
-      </c>
-      <c r="AY22">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ22">
-        <v>3.25</v>
-      </c>
-      <c r="BA22">
-        <v>3.5</v>
-      </c>
-      <c r="BB22">
-        <v>3.4</v>
-      </c>
-      <c r="BC22">
-        <v>3.35</v>
-      </c>
-      <c r="BD22">
-        <v>3.45</v>
-      </c>
-      <c r="BE22">
-        <v>3.65</v>
       </c>
       <c r="BF22">
         <v>22</v>
       </c>
       <c r="BG22">
-        <v>3.5</v>
+        <v>38</v>
       </c>
       <c r="BH22">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
         <v>155</v>
@@ -6163,7 +6163,7 @@
         <v>3.6</v>
       </c>
       <c r="H23">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I23">
         <v>2.38</v>
@@ -6187,22 +6187,22 @@
         <v>1.32</v>
       </c>
       <c r="P23">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q23">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R23">
         <v>1.36</v>
       </c>
       <c r="S23">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T23">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="U23">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V23">
         <v>1.72</v>
@@ -6211,118 +6211,118 @@
         <v>1.38</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y23">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z23">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB23">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC23">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AD23">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AE23">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF23">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AG23">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH23">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN23">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP23">
-        <v>2.24</v>
+        <v>12</v>
       </c>
       <c r="AQ23">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR23">
-        <v>1.97</v>
+        <v>13</v>
       </c>
       <c r="AS23">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="AT23">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU23">
-        <v>1.84</v>
+        <v>7</v>
       </c>
       <c r="AV23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AW23">
         <v>17.5</v>
       </c>
       <c r="AX23">
+        <v>21</v>
+      </c>
+      <c r="AY23">
+        <v>13</v>
+      </c>
+      <c r="AZ23">
+        <v>15</v>
+      </c>
+      <c r="BA23">
+        <v>6.8</v>
+      </c>
+      <c r="BB23">
+        <v>7</v>
+      </c>
+      <c r="BC23">
+        <v>6.8</v>
+      </c>
+      <c r="BD23">
+        <v>32</v>
+      </c>
+      <c r="BE23">
+        <v>6.8</v>
+      </c>
+      <c r="BF23">
+        <v>32</v>
+      </c>
+      <c r="BG23">
         <v>16.5</v>
       </c>
-      <c r="AY23">
-        <v>1.96</v>
-      </c>
-      <c r="AZ23">
-        <v>2.02</v>
-      </c>
-      <c r="BA23">
-        <v>1.96</v>
-      </c>
-      <c r="BB23">
-        <v>2.26</v>
-      </c>
-      <c r="BC23">
-        <v>1.96</v>
-      </c>
-      <c r="BD23">
-        <v>2.26</v>
-      </c>
-      <c r="BE23">
-        <v>1.96</v>
-      </c>
-      <c r="BF23">
-        <v>1.88</v>
-      </c>
-      <c r="BG23">
-        <v>16</v>
-      </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
@@ -6358,7 +6358,7 @@
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="BV23">
         <v>1000</v>
@@ -6402,7 +6402,7 @@
         <v>2.16</v>
       </c>
       <c r="G24">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H24">
         <v>3.8</v>
@@ -6423,25 +6423,25 @@
         <v>1.08</v>
       </c>
       <c r="N24">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O24">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P24">
         <v>1.84</v>
       </c>
       <c r="Q24">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R24">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S24">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T24">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U24">
         <v>2.06</v>
@@ -6450,13 +6450,13 @@
         <v>1.32</v>
       </c>
       <c r="W24">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X24">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="Y24">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z24">
         <v>38</v>
@@ -6465,58 +6465,58 @@
         <v>100</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC24">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD24">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AE24">
         <v>65</v>
       </c>
       <c r="AF24">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG24">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI24">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ24">
         <v>38</v>
       </c>
       <c r="AK24">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL24">
         <v>48</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO24">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ24">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR24">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS24">
-        <v>4.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT24">
         <v>8.199999999999999</v>
@@ -6525,43 +6525,43 @@
         <v>6.8</v>
       </c>
       <c r="AV24">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW24">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX24">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AY24">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24">
-        <v>3.7</v>
+        <v>16</v>
       </c>
       <c r="BA24">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BB24">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="BC24">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD24">
-        <v>4.1</v>
+        <v>30</v>
       </c>
       <c r="BE24">
-        <v>4.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF24">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BG24">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH24">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
         <v>2.66</v>
@@ -6570,7 +6570,7 @@
         <v>1000</v>
       </c>
       <c r="BK24">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="BL24">
         <v>1000</v>
@@ -6579,16 +6579,16 @@
         <v>2.48</v>
       </c>
       <c r="BN24">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>3.65</v>
+        <v>1.9</v>
       </c>
       <c r="BP24">
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="BR24">
         <v>1000</v>
@@ -6600,7 +6600,7 @@
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>5</v>
+        <v>2.16</v>
       </c>
       <c r="BV24">
         <v>1000</v>
@@ -6641,43 +6641,43 @@
         <v>154</v>
       </c>
       <c r="F25">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="G25">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="H25">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I25">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K25">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L25">
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N25">
         <v>4</v>
       </c>
       <c r="O25">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P25">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="Q25">
         <v>1.8</v>
       </c>
       <c r="R25">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S25">
         <v>3.1</v>
@@ -6686,121 +6686,121 @@
         <v>1.85</v>
       </c>
       <c r="U25">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V25">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W25">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="X25">
+        <v>17</v>
+      </c>
+      <c r="Y25">
         <v>23</v>
       </c>
-      <c r="Y25">
-        <v>950</v>
-      </c>
       <c r="Z25">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC25">
+        <v>9.4</v>
+      </c>
+      <c r="AD25">
+        <v>25</v>
+      </c>
+      <c r="AE25">
+        <v>85</v>
+      </c>
+      <c r="AF25">
         <v>11</v>
       </c>
-      <c r="AC25">
+      <c r="AG25">
         <v>10</v>
       </c>
-      <c r="AD25">
-        <v>950</v>
-      </c>
-      <c r="AE25">
-        <v>100</v>
-      </c>
-      <c r="AF25">
-        <v>15</v>
-      </c>
-      <c r="AG25">
-        <v>13.5</v>
-      </c>
       <c r="AH25">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AI25">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ25">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AK25">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AL25">
         <v>48</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN25">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO25">
         <v>100</v>
       </c>
       <c r="AP25">
-        <v>3.4</v>
+        <v>14.5</v>
       </c>
       <c r="AQ25">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AR25">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS25">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AT25">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU25">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV25">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AW25">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="AX25">
+        <v>9.4</v>
+      </c>
+      <c r="AY25">
+        <v>9</v>
+      </c>
+      <c r="AZ25">
+        <v>17.5</v>
+      </c>
+      <c r="BA25">
+        <v>9.6</v>
+      </c>
+      <c r="BB25">
+        <v>15</v>
+      </c>
+      <c r="BC25">
+        <v>15.5</v>
+      </c>
+      <c r="BD25">
         <v>8.4</v>
       </c>
-      <c r="AY25">
-        <v>8.4</v>
-      </c>
-      <c r="AZ25">
-        <v>16.5</v>
-      </c>
-      <c r="BA25">
-        <v>3.9</v>
-      </c>
-      <c r="BB25">
-        <v>11</v>
-      </c>
-      <c r="BC25">
-        <v>14.5</v>
-      </c>
-      <c r="BD25">
-        <v>3.75</v>
-      </c>
       <c r="BE25">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BF25">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG25">
-        <v>3.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH25">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="140">
   <si>
     <t>League</t>
   </si>
@@ -259,18 +259,12 @@
     <t>Brazilian Serie A</t>
   </si>
   <si>
-    <t>Qatari Stars League</t>
-  </si>
-  <si>
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
     <t>Jordanian Premier League</t>
   </si>
   <si>
-    <t>Romanian Liga II</t>
-  </si>
-  <si>
     <t>Moroccan Botola Pro 1</t>
   </si>
   <si>
@@ -280,9 +274,6 @@
     <t>Ecuadorian Serie B</t>
   </si>
   <si>
-    <t>Romanian Liga I</t>
-  </si>
-  <si>
     <t>Peruvian Primera Division</t>
   </si>
   <si>
@@ -301,9 +292,6 @@
     <t>00:30:00</t>
   </si>
   <si>
-    <t>14:45:00</t>
-  </si>
-  <si>
     <t>15:00:00</t>
   </si>
   <si>
@@ -313,9 +301,6 @@
     <t>17:00:00</t>
   </si>
   <si>
-    <t>17:30:00</t>
-  </si>
-  <si>
     <t>18:00:00</t>
   </si>
   <si>
@@ -325,9 +310,6 @@
     <t>20:00:00</t>
   </si>
   <si>
-    <t>20:30:00</t>
-  </si>
-  <si>
     <t>22:30:00</t>
   </si>
   <si>
@@ -340,18 +322,12 @@
     <t>Cruzeiro MG</t>
   </si>
   <si>
-    <t>Al Shamal</t>
-  </si>
-  <si>
     <t>HJK Helsinki</t>
   </si>
   <si>
     <t>Shabab Al Ordon</t>
   </si>
   <si>
-    <t>Politehnica Timisoara</t>
-  </si>
-  <si>
     <t>KuPS</t>
   </si>
   <si>
@@ -367,21 +343,15 @@
     <t>Independiente Juniors</t>
   </si>
   <si>
-    <t>Al-Wakra</t>
-  </si>
-  <si>
-    <t>CFR Cluj</t>
+    <t>Cesar Vallejo Moquegua</t>
+  </si>
+  <si>
+    <t>FAR Rabat</t>
   </si>
   <si>
     <t>Club R Zemamra</t>
   </si>
   <si>
-    <t>FAR Rabat</t>
-  </si>
-  <si>
-    <t>Cesar Vallejo Moquegua</t>
-  </si>
-  <si>
     <t>MC Oran</t>
   </si>
   <si>
@@ -391,9 +361,6 @@
     <t>MAS Maghrib A Fes</t>
   </si>
   <si>
-    <t>Atletico Grau</t>
-  </si>
-  <si>
     <t>Santos</t>
   </si>
   <si>
@@ -412,18 +379,12 @@
     <t>Sao Paulo</t>
   </si>
   <si>
-    <t>Al-Duhail SC</t>
-  </si>
-  <si>
     <t>VPS</t>
   </si>
   <si>
     <t>Al Buqaa</t>
   </si>
   <si>
-    <t>CSA Steaua Bucuresti</t>
-  </si>
-  <si>
     <t>AC Oulu</t>
   </si>
   <si>
@@ -439,21 +400,15 @@
     <t>Club Nueve de Octubre</t>
   </si>
   <si>
-    <t>Al Gharafa</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
+    <t>Cienciano</t>
+  </si>
+  <si>
+    <t>Widad Temara</t>
   </si>
   <si>
     <t>HUSA Agadir</t>
   </si>
   <si>
-    <t>Widad Temara</t>
-  </si>
-  <si>
-    <t>Cienciano</t>
-  </si>
-  <si>
     <t>ES Setif</t>
   </si>
   <si>
@@ -463,9 +418,6 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
-    <t>CD Los Chankas</t>
-  </si>
-  <si>
     <t>Flamengo</t>
   </si>
   <si>
@@ -481,7 +433,7 @@
     <t>Tolima</t>
   </si>
   <si>
-    <t>2026-10-07 04:13:12</t>
+    <t>2026-10-07 06:26:08</t>
   </si>
 </sst>
 </file>
@@ -813,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1063,16 +1015,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -1084,13 +1036,13 @@
         <v>4.2</v>
       </c>
       <c r="I2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -1102,13 +1054,13 @@
         <v>3.75</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
         <v>1.92</v>
       </c>
       <c r="Q2">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R2">
         <v>1.35</v>
@@ -1117,7 +1069,7 @@
         <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U2">
         <v>2.1</v>
@@ -1153,7 +1105,7 @@
         <v>60</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
@@ -1171,31 +1123,31 @@
         <v>22</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO2">
         <v>65</v>
       </c>
       <c r="AP2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2">
         <v>14</v>
       </c>
       <c r="AR2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS2">
         <v>85</v>
       </c>
       <c r="AT2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU2">
         <v>7.4</v>
@@ -1204,7 +1156,7 @@
         <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX2">
         <v>11</v>
@@ -1219,7 +1171,7 @@
         <v>55</v>
       </c>
       <c r="BB2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC2">
         <v>19.5</v>
@@ -1228,7 +1180,7 @@
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF2">
         <v>13.5</v>
@@ -1252,13 +1204,13 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BN2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
         <v>14.5</v>
@@ -1270,34 +1222,34 @@
         <v>30</v>
       </c>
       <c r="BS2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT2">
         <v>7.6</v>
       </c>
       <c r="BU2">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BX2">
         <v>50</v>
       </c>
       <c r="BY2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ2">
         <v>27</v>
       </c>
       <c r="CA2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1305,241 +1257,241 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="F3">
-        <v>3.1</v>
+        <v>1.63</v>
       </c>
       <c r="G3">
-        <v>4.9</v>
+        <v>1.68</v>
       </c>
       <c r="H3">
-        <v>2.08</v>
+        <v>5.7</v>
       </c>
       <c r="I3">
-        <v>2.76</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="K3">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3">
         <v>4.5</v>
       </c>
       <c r="O3">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="P3">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="Q3">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="R3">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="S3">
-        <v>2.36</v>
+        <v>2.86</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="V3">
-        <v>1.56</v>
+        <v>1.19</v>
       </c>
       <c r="W3">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="CB3" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1547,1146 +1499,1146 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="F4">
-        <v>1.62</v>
+        <v>1.12</v>
       </c>
       <c r="G4">
-        <v>1.68</v>
+        <v>990</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>1.12</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>990</v>
       </c>
       <c r="J4">
-        <v>4.3</v>
+        <v>1.18</v>
       </c>
       <c r="K4">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L4">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>1.28</v>
+      </c>
+      <c r="O4">
+        <v>1.01</v>
+      </c>
+      <c r="P4">
+        <v>1.27</v>
+      </c>
+      <c r="Q4">
+        <v>1.35</v>
+      </c>
+      <c r="R4">
+        <v>1.18</v>
+      </c>
+      <c r="S4">
         <v>1.05</v>
       </c>
-      <c r="N4">
-        <v>4.6</v>
-      </c>
-      <c r="O4">
-        <v>1.25</v>
-      </c>
-      <c r="P4">
-        <v>2.24</v>
-      </c>
-      <c r="Q4">
-        <v>1.73</v>
-      </c>
-      <c r="R4">
-        <v>1.49</v>
-      </c>
-      <c r="S4">
-        <v>2.8</v>
-      </c>
       <c r="T4">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="U4">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="W4">
-        <v>2.46</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
         <v>93</v>
       </c>
-      <c r="C5" t="s">
-        <v>96</v>
-      </c>
       <c r="D5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5">
+        <v>1.65</v>
+      </c>
+      <c r="G5">
+        <v>1.71</v>
+      </c>
+      <c r="H5">
+        <v>5.9</v>
+      </c>
+      <c r="I5">
+        <v>6.6</v>
+      </c>
+      <c r="J5">
+        <v>3.9</v>
+      </c>
+      <c r="K5">
+        <v>4.3</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.07</v>
+      </c>
+      <c r="N5">
+        <v>3.7</v>
+      </c>
+      <c r="O5">
+        <v>1.32</v>
+      </c>
+      <c r="P5">
+        <v>1.92</v>
+      </c>
+      <c r="Q5">
+        <v>1.94</v>
+      </c>
+      <c r="R5">
+        <v>1.35</v>
+      </c>
+      <c r="S5">
+        <v>3.4</v>
+      </c>
+      <c r="T5">
+        <v>1.95</v>
+      </c>
+      <c r="U5">
+        <v>1.91</v>
+      </c>
+      <c r="V5">
+        <v>1.18</v>
+      </c>
+      <c r="W5">
+        <v>2.4</v>
+      </c>
+      <c r="X5">
+        <v>15</v>
+      </c>
+      <c r="Y5">
+        <v>19.5</v>
+      </c>
+      <c r="Z5">
+        <v>80</v>
+      </c>
+      <c r="AA5">
+        <v>210</v>
+      </c>
+      <c r="AB5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD5">
+        <v>24</v>
+      </c>
+      <c r="AE5">
         <v>110</v>
       </c>
-      <c r="E5" t="s">
-        <v>134</v>
-      </c>
-      <c r="F5">
-        <v>1.12</v>
-      </c>
-      <c r="G5">
-        <v>990</v>
-      </c>
-      <c r="H5">
-        <v>1.12</v>
-      </c>
-      <c r="I5">
-        <v>990</v>
-      </c>
-      <c r="J5">
-        <v>1.16</v>
-      </c>
-      <c r="K5">
-        <v>950</v>
-      </c>
-      <c r="L5">
-        <v>1.01</v>
-      </c>
-      <c r="M5">
-        <v>1.01</v>
-      </c>
-      <c r="N5">
-        <v>1.13</v>
-      </c>
-      <c r="O5">
-        <v>1.33</v>
-      </c>
-      <c r="P5">
-        <v>1.13</v>
-      </c>
-      <c r="Q5">
-        <v>1.35</v>
-      </c>
-      <c r="R5">
-        <v>1.08</v>
-      </c>
-      <c r="S5">
-        <v>2.96</v>
-      </c>
-      <c r="T5">
-        <v>1.11</v>
-      </c>
-      <c r="U5">
-        <v>1.11</v>
-      </c>
-      <c r="V5">
-        <v>1.07</v>
-      </c>
-      <c r="W5">
-        <v>1.08</v>
-      </c>
-      <c r="X5">
-        <v>1000</v>
-      </c>
-      <c r="Y5">
-        <v>1000</v>
-      </c>
-      <c r="Z5">
-        <v>1000</v>
-      </c>
-      <c r="AA5">
-        <v>1000</v>
-      </c>
-      <c r="AB5">
-        <v>1000</v>
-      </c>
-      <c r="AC5">
-        <v>1000</v>
-      </c>
-      <c r="AD5">
-        <v>1000</v>
-      </c>
-      <c r="AE5">
-        <v>1000</v>
-      </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="CB5" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
         <v>93</v>
       </c>
-      <c r="C6" t="s">
-        <v>96</v>
-      </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>2.26</v>
       </c>
       <c r="I6">
-        <v>870</v>
+        <v>2.6</v>
       </c>
       <c r="J6">
-        <v>2.24</v>
+        <v>2.96</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="P6">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="Q6">
-        <v>1.02</v>
+        <v>2.3</v>
       </c>
       <c r="R6">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH6">
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="G7">
-        <v>1.71</v>
+        <v>4.4</v>
       </c>
       <c r="H7">
-        <v>5.9</v>
+        <v>1.99</v>
       </c>
       <c r="I7">
-        <v>6.4</v>
+        <v>2.66</v>
       </c>
       <c r="J7">
-        <v>3.9</v>
+        <v>2.94</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="L7">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.75</v>
+        <v>2.18</v>
       </c>
       <c r="O7">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="P7">
-        <v>1.94</v>
+        <v>1.39</v>
       </c>
       <c r="Q7">
-        <v>1.96</v>
+        <v>2.42</v>
       </c>
       <c r="R7">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="S7">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="T7">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="W7">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="X7">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F8">
+        <v>1.88</v>
+      </c>
+      <c r="G8">
+        <v>2.04</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>6.2</v>
+      </c>
+      <c r="J8">
         <v>3.1</v>
       </c>
-      <c r="G8">
-        <v>4.7</v>
-      </c>
-      <c r="H8">
-        <v>2.16</v>
-      </c>
-      <c r="I8">
-        <v>2.92</v>
-      </c>
-      <c r="J8">
-        <v>2.68</v>
-      </c>
       <c r="K8">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="L8">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N8">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="O8">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="P8">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Q8">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="R8">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V8">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="W8">
-        <v>1.27</v>
+        <v>1.97</v>
       </c>
       <c r="X8">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y8">
-        <v>8.6</v>
+        <v>15.5</v>
       </c>
       <c r="Z8">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="AA8">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="AB8">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="AC8">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD8">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="AE8">
+        <v>130</v>
+      </c>
+      <c r="AF8">
+        <v>11</v>
+      </c>
+      <c r="AG8">
+        <v>13.5</v>
+      </c>
+      <c r="AH8">
+        <v>32</v>
+      </c>
+      <c r="AI8">
+        <v>150</v>
+      </c>
+      <c r="AJ8">
+        <v>29</v>
+      </c>
+      <c r="AK8">
         <v>34</v>
       </c>
-      <c r="AF8">
-        <v>26</v>
-      </c>
-      <c r="AG8">
-        <v>16.5</v>
-      </c>
-      <c r="AH8">
-        <v>22</v>
-      </c>
-      <c r="AI8">
-        <v>60</v>
-      </c>
-      <c r="AJ8">
-        <v>100</v>
-      </c>
-      <c r="AK8">
-        <v>60</v>
-      </c>
       <c r="AL8">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AM8">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="AN8">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="AO8">
-        <v>34</v>
+        <v>220</v>
       </c>
       <c r="AP8">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ8">
-        <v>4.1</v>
+        <v>9.6</v>
       </c>
       <c r="AR8">
+        <v>4.8</v>
+      </c>
+      <c r="AS8">
         <v>5.2</v>
       </c>
-      <c r="AS8">
-        <v>6.6</v>
-      </c>
       <c r="AT8">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU8">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV8">
+        <v>16</v>
+      </c>
+      <c r="AW8">
+        <v>5.1</v>
+      </c>
+      <c r="AX8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ8">
+        <v>19</v>
+      </c>
+      <c r="BA8">
+        <v>5.1</v>
+      </c>
+      <c r="BB8">
+        <v>17.5</v>
+      </c>
+      <c r="BC8">
+        <v>20</v>
+      </c>
+      <c r="BD8">
         <v>4.9</v>
       </c>
-      <c r="AW8">
-        <v>6.4</v>
-      </c>
-      <c r="AX8">
-        <v>6</v>
-      </c>
-      <c r="AY8">
-        <v>5.4</v>
-      </c>
-      <c r="AZ8">
-        <v>5.9</v>
-      </c>
-      <c r="BA8">
-        <v>7</v>
-      </c>
-      <c r="BB8">
-        <v>7.2</v>
-      </c>
-      <c r="BC8">
-        <v>7</v>
-      </c>
-      <c r="BD8">
-        <v>7.2</v>
-      </c>
       <c r="BE8">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF8">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="BG8">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2749,66 +2701,66 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F9">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="G9">
-        <v>4.8</v>
+        <v>2.68</v>
       </c>
       <c r="H9">
-        <v>1.99</v>
+        <v>3.4</v>
       </c>
       <c r="I9">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="J9">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
       <c r="K9">
-        <v>5.4</v>
+        <v>3.05</v>
       </c>
       <c r="L9">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N9">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="O9">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="P9">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q9">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="R9">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="S9">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2817,11 +2769,11 @@
         <v>1.11</v>
       </c>
       <c r="V9">
+        <v>1.32</v>
+      </c>
+      <c r="W9">
         <v>1.6</v>
       </c>
-      <c r="W9">
-        <v>1.31</v>
-      </c>
       <c r="X9">
         <v>1000</v>
       </c>
@@ -2991,7 +2943,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2999,420 +2951,420 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>1.36</v>
+      </c>
+      <c r="S10">
+        <v>3.15</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
         <v>139</v>
-      </c>
-      <c r="F10">
-        <v>1.89</v>
-      </c>
-      <c r="G10">
-        <v>2.08</v>
-      </c>
-      <c r="H10">
-        <v>4.8</v>
-      </c>
-      <c r="I10">
-        <v>6.2</v>
-      </c>
-      <c r="J10">
-        <v>3.1</v>
-      </c>
-      <c r="K10">
-        <v>3.45</v>
-      </c>
-      <c r="L10">
-        <v>1.01</v>
-      </c>
-      <c r="M10">
-        <v>1.12</v>
-      </c>
-      <c r="N10">
-        <v>2.52</v>
-      </c>
-      <c r="O10">
-        <v>1.55</v>
-      </c>
-      <c r="P10">
-        <v>1.52</v>
-      </c>
-      <c r="Q10">
-        <v>2.58</v>
-      </c>
-      <c r="R10">
-        <v>1.18</v>
-      </c>
-      <c r="S10">
-        <v>5.4</v>
-      </c>
-      <c r="T10">
-        <v>2.22</v>
-      </c>
-      <c r="U10">
-        <v>1.7</v>
-      </c>
-      <c r="V10">
-        <v>1.2</v>
-      </c>
-      <c r="W10">
-        <v>1.93</v>
-      </c>
-      <c r="X10">
-        <v>10.5</v>
-      </c>
-      <c r="Y10">
-        <v>15.5</v>
-      </c>
-      <c r="Z10">
-        <v>48</v>
-      </c>
-      <c r="AA10">
-        <v>200</v>
-      </c>
-      <c r="AB10">
-        <v>7.6</v>
-      </c>
-      <c r="AC10">
-        <v>8</v>
-      </c>
-      <c r="AD10">
-        <v>27</v>
-      </c>
-      <c r="AE10">
-        <v>130</v>
-      </c>
-      <c r="AF10">
-        <v>11</v>
-      </c>
-      <c r="AG10">
-        <v>13.5</v>
-      </c>
-      <c r="AH10">
-        <v>32</v>
-      </c>
-      <c r="AI10">
-        <v>150</v>
-      </c>
-      <c r="AJ10">
-        <v>30</v>
-      </c>
-      <c r="AK10">
-        <v>34</v>
-      </c>
-      <c r="AL10">
-        <v>65</v>
-      </c>
-      <c r="AM10">
-        <v>280</v>
-      </c>
-      <c r="AN10">
-        <v>30</v>
-      </c>
-      <c r="AO10">
-        <v>220</v>
-      </c>
-      <c r="AP10">
-        <v>6.4</v>
-      </c>
-      <c r="AQ10">
-        <v>9.6</v>
-      </c>
-      <c r="AR10">
-        <v>4.7</v>
-      </c>
-      <c r="AS10">
-        <v>5.1</v>
-      </c>
-      <c r="AT10">
-        <v>5.5</v>
-      </c>
-      <c r="AU10">
-        <v>5.8</v>
-      </c>
-      <c r="AV10">
-        <v>16</v>
-      </c>
-      <c r="AW10">
-        <v>5</v>
-      </c>
-      <c r="AX10">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ10">
-        <v>19</v>
-      </c>
-      <c r="BA10">
-        <v>5</v>
-      </c>
-      <c r="BB10">
-        <v>17.5</v>
-      </c>
-      <c r="BC10">
-        <v>20</v>
-      </c>
-      <c r="BD10">
-        <v>4.8</v>
-      </c>
-      <c r="BE10">
-        <v>5.1</v>
-      </c>
-      <c r="BF10">
-        <v>17.5</v>
-      </c>
-      <c r="BG10">
-        <v>5.1</v>
-      </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
-        <v>1.04</v>
-      </c>
-      <c r="BJ10">
-        <v>1000</v>
-      </c>
-      <c r="BK10">
-        <v>1.04</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>1.04</v>
-      </c>
-      <c r="BN10">
-        <v>1000</v>
-      </c>
-      <c r="BO10">
-        <v>1.04</v>
-      </c>
-      <c r="BP10">
-        <v>1000</v>
-      </c>
-      <c r="BQ10">
-        <v>1.04</v>
-      </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
-        <v>1.04</v>
-      </c>
-      <c r="BT10">
-        <v>1000</v>
-      </c>
-      <c r="BU10">
-        <v>1.04</v>
-      </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
-      <c r="BW10">
-        <v>1.04</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>1.04</v>
-      </c>
-      <c r="BZ10">
-        <v>1000</v>
-      </c>
-      <c r="CA10">
-        <v>1.04</v>
-      </c>
-      <c r="CB10" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F11">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="G11">
-        <v>2.68</v>
+        <v>1.6</v>
       </c>
       <c r="H11">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="J11">
-        <v>2.72</v>
+        <v>1.12</v>
       </c>
       <c r="K11">
-        <v>3.05</v>
+        <v>5.2</v>
       </c>
       <c r="L11">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M11">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="O11">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="P11">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="Q11">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="R11">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="S11">
         <v>3.25</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="V11">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="W11">
-        <v>1.6</v>
+        <v>2.68</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3424,13 +3376,13 @@
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BN11">
         <v>1000</v>
@@ -3442,111 +3394,111 @@
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="CB11" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="F12">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="G12">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="H12">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="I12">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="J12">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N12">
-        <v>4.5</v>
+        <v>2.58</v>
       </c>
       <c r="O12">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="P12">
-        <v>2.28</v>
+        <v>1.58</v>
       </c>
       <c r="Q12">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="R12">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="S12">
-        <v>2.22</v>
+        <v>2.72</v>
       </c>
       <c r="T12">
-        <v>1.54</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="W12">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3666,7 +3618,7 @@
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="BL12">
         <v>1000</v>
@@ -3684,1734 +3636,1734 @@
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="CB12" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F13">
+        <v>2.04</v>
+      </c>
+      <c r="G13">
+        <v>2.22</v>
+      </c>
+      <c r="H13">
+        <v>4.3</v>
+      </c>
+      <c r="I13">
+        <v>6.6</v>
+      </c>
+      <c r="J13">
+        <v>2.66</v>
+      </c>
+      <c r="K13">
+        <v>3.25</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>2.3</v>
+      </c>
+      <c r="O13">
+        <v>1.59</v>
+      </c>
+      <c r="P13">
+        <v>1.37</v>
+      </c>
+      <c r="Q13">
         <v>2.56</v>
       </c>
-      <c r="G13">
-        <v>2.66</v>
-      </c>
-      <c r="H13">
-        <v>2.88</v>
-      </c>
-      <c r="I13">
-        <v>3.05</v>
-      </c>
-      <c r="J13">
-        <v>3.45</v>
-      </c>
-      <c r="K13">
-        <v>3.65</v>
-      </c>
-      <c r="L13">
-        <v>1.36</v>
-      </c>
-      <c r="M13">
-        <v>1.06</v>
-      </c>
-      <c r="N13">
-        <v>4.1</v>
-      </c>
-      <c r="O13">
-        <v>1.28</v>
-      </c>
-      <c r="P13">
+      <c r="R13">
+        <v>1.12</v>
+      </c>
+      <c r="S13">
+        <v>2.56</v>
+      </c>
+      <c r="T13">
+        <v>1.11</v>
+      </c>
+      <c r="U13">
+        <v>1.11</v>
+      </c>
+      <c r="V13">
+        <v>1.2</v>
+      </c>
+      <c r="W13">
+        <v>1.81</v>
+      </c>
+      <c r="X13">
+        <v>1000</v>
+      </c>
+      <c r="Y13">
+        <v>1000</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>1000</v>
+      </c>
+      <c r="AC13">
+        <v>1000</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>1000</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13">
+        <v>1.01</v>
+      </c>
+      <c r="AR13">
+        <v>1.01</v>
+      </c>
+      <c r="AS13">
+        <v>1.01</v>
+      </c>
+      <c r="AT13">
+        <v>1.01</v>
+      </c>
+      <c r="AU13">
+        <v>1.01</v>
+      </c>
+      <c r="AV13">
+        <v>1.01</v>
+      </c>
+      <c r="AW13">
+        <v>1.01</v>
+      </c>
+      <c r="AX13">
+        <v>1.01</v>
+      </c>
+      <c r="AY13">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13">
+        <v>1.01</v>
+      </c>
+      <c r="BA13">
+        <v>1.01</v>
+      </c>
+      <c r="BB13">
+        <v>1.01</v>
+      </c>
+      <c r="BC13">
+        <v>1.01</v>
+      </c>
+      <c r="BD13">
+        <v>1.01</v>
+      </c>
+      <c r="BE13">
+        <v>1.01</v>
+      </c>
+      <c r="BF13">
+        <v>1.01</v>
+      </c>
+      <c r="BG13">
+        <v>1.01</v>
+      </c>
+      <c r="BH13">
+        <v>2.94</v>
+      </c>
+      <c r="BI13">
         <v>2.06</v>
       </c>
-      <c r="Q13">
-        <v>1.81</v>
-      </c>
-      <c r="R13">
-        <v>1.41</v>
-      </c>
-      <c r="S13">
-        <v>3.05</v>
-      </c>
-      <c r="T13">
-        <v>1.67</v>
-      </c>
-      <c r="U13">
-        <v>2.24</v>
-      </c>
-      <c r="V13">
-        <v>1.49</v>
-      </c>
-      <c r="W13">
-        <v>1.6</v>
-      </c>
-      <c r="X13">
-        <v>21</v>
-      </c>
-      <c r="Y13">
-        <v>14</v>
-      </c>
-      <c r="Z13">
-        <v>22</v>
-      </c>
-      <c r="AA13">
-        <v>60</v>
-      </c>
-      <c r="AB13">
-        <v>12.5</v>
-      </c>
-      <c r="AC13">
-        <v>8.6</v>
-      </c>
-      <c r="AD13">
-        <v>13.5</v>
-      </c>
-      <c r="AE13">
-        <v>34</v>
-      </c>
-      <c r="AF13">
-        <v>18.5</v>
-      </c>
-      <c r="AG13">
-        <v>12</v>
-      </c>
-      <c r="AH13">
-        <v>17</v>
-      </c>
-      <c r="AI13">
-        <v>42</v>
-      </c>
-      <c r="AJ13">
-        <v>36</v>
-      </c>
-      <c r="AK13">
-        <v>27</v>
-      </c>
-      <c r="AL13">
-        <v>40</v>
-      </c>
-      <c r="AM13">
-        <v>100</v>
-      </c>
-      <c r="AN13">
-        <v>22</v>
-      </c>
-      <c r="AO13">
-        <v>26</v>
-      </c>
-      <c r="AP13">
-        <v>14</v>
-      </c>
-      <c r="AQ13">
-        <v>11.5</v>
-      </c>
-      <c r="AR13">
-        <v>18.5</v>
-      </c>
-      <c r="AS13">
-        <v>20</v>
-      </c>
-      <c r="AT13">
-        <v>10.5</v>
-      </c>
-      <c r="AU13">
-        <v>7.2</v>
-      </c>
-      <c r="AV13">
-        <v>11.5</v>
-      </c>
-      <c r="AW13">
-        <v>14.5</v>
-      </c>
-      <c r="AX13">
-        <v>15</v>
-      </c>
-      <c r="AY13">
-        <v>10</v>
-      </c>
-      <c r="AZ13">
-        <v>14</v>
-      </c>
-      <c r="BA13">
-        <v>18</v>
-      </c>
-      <c r="BB13">
-        <v>27</v>
-      </c>
-      <c r="BC13">
-        <v>21</v>
-      </c>
-      <c r="BD13">
-        <v>30</v>
-      </c>
-      <c r="BE13">
-        <v>8.4</v>
-      </c>
-      <c r="BF13">
-        <v>16</v>
-      </c>
-      <c r="BG13">
-        <v>18</v>
-      </c>
-      <c r="BH13">
-        <v>4.2</v>
-      </c>
-      <c r="BI13">
-        <v>2.84</v>
-      </c>
       <c r="BJ13">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>2.64</v>
+        <v>1.53</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="BN13">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="BP13">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>2.94</v>
+        <v>1.53</v>
       </c>
       <c r="BR13">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>3.05</v>
+        <v>1.53</v>
       </c>
       <c r="BT13">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>4.1</v>
+        <v>1.53</v>
       </c>
       <c r="BV13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="BX13">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>3.1</v>
+        <v>1.53</v>
       </c>
       <c r="BZ13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="CB13" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="F14">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="G14">
-        <v>4.5</v>
+        <v>1.49</v>
       </c>
       <c r="H14">
-        <v>2.74</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>2.88</v>
+        <v>4.7</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L14">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="Q14">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="R14">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI14">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK14">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM14">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO14">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ14">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS14">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU14">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW14">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY14">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="F15">
+        <v>2.66</v>
+      </c>
+      <c r="G15">
+        <v>3.15</v>
+      </c>
+      <c r="H15">
+        <v>2.88</v>
+      </c>
+      <c r="I15">
+        <v>3.3</v>
+      </c>
+      <c r="J15">
+        <v>2.64</v>
+      </c>
+      <c r="K15">
+        <v>3.6</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>2.16</v>
+      </c>
+      <c r="O15">
+        <v>1.48</v>
+      </c>
+      <c r="P15">
+        <v>1.5</v>
+      </c>
+      <c r="Q15">
+        <v>2.54</v>
+      </c>
+      <c r="R15">
+        <v>1.18</v>
+      </c>
+      <c r="S15">
+        <v>3.1</v>
+      </c>
+      <c r="T15">
+        <v>1.12</v>
+      </c>
+      <c r="U15">
+        <v>1.11</v>
+      </c>
+      <c r="V15">
+        <v>1.43</v>
+      </c>
+      <c r="W15">
         <v>1.46</v>
       </c>
-      <c r="G15">
-        <v>1.6</v>
-      </c>
-      <c r="H15">
-        <v>8</v>
-      </c>
-      <c r="I15">
-        <v>11.5</v>
-      </c>
-      <c r="J15">
-        <v>1.12</v>
-      </c>
-      <c r="K15">
-        <v>5.2</v>
-      </c>
-      <c r="L15">
-        <v>1.01</v>
-      </c>
-      <c r="M15">
-        <v>1.04</v>
-      </c>
-      <c r="N15">
-        <v>3.1</v>
-      </c>
-      <c r="O15">
-        <v>1.34</v>
-      </c>
-      <c r="P15">
-        <v>1.61</v>
-      </c>
-      <c r="Q15">
-        <v>1.91</v>
-      </c>
-      <c r="R15">
-        <v>1.23</v>
-      </c>
-      <c r="S15">
-        <v>3.25</v>
-      </c>
-      <c r="T15">
-        <v>1.89</v>
-      </c>
-      <c r="U15">
-        <v>1.5</v>
-      </c>
-      <c r="V15">
-        <v>1.1</v>
-      </c>
-      <c r="W15">
-        <v>2.68</v>
-      </c>
       <c r="X15">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI15">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="CB15" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E16" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="F16">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="G16">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="H16">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="I16">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="J16">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K16">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M16">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N16">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O16">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="P16">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="Q16">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="R16">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S16">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T16">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="U16">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="V16">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="W16">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="X16">
+        <v>22</v>
+      </c>
+      <c r="Y16">
+        <v>10.5</v>
+      </c>
+      <c r="Z16">
+        <v>13</v>
+      </c>
+      <c r="AA16">
+        <v>22</v>
+      </c>
+      <c r="AB16">
+        <v>18</v>
+      </c>
+      <c r="AC16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD16">
+        <v>10.5</v>
+      </c>
+      <c r="AE16">
+        <v>19</v>
+      </c>
+      <c r="AF16">
+        <v>36</v>
+      </c>
+      <c r="AG16">
+        <v>18</v>
+      </c>
+      <c r="AH16">
         <v>17.5</v>
       </c>
-      <c r="Y16">
-        <v>12</v>
-      </c>
-      <c r="Z16">
-        <v>17</v>
-      </c>
-      <c r="AA16">
-        <v>34</v>
-      </c>
-      <c r="AB16">
-        <v>16</v>
-      </c>
-      <c r="AC16">
-        <v>9.6</v>
-      </c>
-      <c r="AD16">
-        <v>13</v>
-      </c>
-      <c r="AE16">
-        <v>27</v>
-      </c>
-      <c r="AF16">
-        <v>29</v>
-      </c>
-      <c r="AG16">
-        <v>17</v>
-      </c>
-      <c r="AH16">
-        <v>20</v>
-      </c>
       <c r="AI16">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AJ16">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AK16">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL16">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM16">
         <v>100</v>
       </c>
       <c r="AN16">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AO16">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="AP16">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16">
+        <v>9</v>
+      </c>
+      <c r="AR16">
+        <v>11</v>
+      </c>
+      <c r="AS16">
+        <v>18.5</v>
+      </c>
+      <c r="AT16">
+        <v>15.5</v>
+      </c>
+      <c r="AU16">
         <v>8</v>
       </c>
-      <c r="AR16">
-        <v>4.1</v>
-      </c>
-      <c r="AS16">
-        <v>18</v>
-      </c>
-      <c r="AT16">
-        <v>10.5</v>
-      </c>
-      <c r="AU16">
-        <v>6.4</v>
-      </c>
       <c r="AV16">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW16">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX16">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY16">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="AZ16">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA16">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BB16">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC16">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD16">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BE16">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="BF16">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="BG16">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BN16">
         <v>1000</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BT16">
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="CB16" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="F17">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="G17">
-        <v>2.22</v>
+        <v>2.64</v>
       </c>
       <c r="H17">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="I17">
-        <v>6.4</v>
+        <v>3.55</v>
       </c>
       <c r="J17">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="K17">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N17">
-        <v>2.28</v>
+        <v>2.9</v>
       </c>
       <c r="O17">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="P17">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="Q17">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="R17">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="S17">
-        <v>2.56</v>
+        <v>4.7</v>
       </c>
       <c r="T17">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U17">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="V17">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="W17">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BH17">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" t="s">
         <v>90</v>
       </c>
-      <c r="B18" t="s">
-        <v>93</v>
-      </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F18">
-        <v>1.43</v>
+        <v>3.4</v>
       </c>
       <c r="G18">
-        <v>1.47</v>
+        <v>3.6</v>
       </c>
       <c r="H18">
+        <v>2.28</v>
+      </c>
+      <c r="I18">
+        <v>2.38</v>
+      </c>
+      <c r="J18">
+        <v>3.45</v>
+      </c>
+      <c r="K18">
+        <v>3.6</v>
+      </c>
+      <c r="L18">
+        <v>1.37</v>
+      </c>
+      <c r="M18">
+        <v>1.07</v>
+      </c>
+      <c r="N18">
+        <v>3.85</v>
+      </c>
+      <c r="O18">
+        <v>1.33</v>
+      </c>
+      <c r="P18">
+        <v>1.91</v>
+      </c>
+      <c r="Q18">
+        <v>1.96</v>
+      </c>
+      <c r="R18">
+        <v>1.36</v>
+      </c>
+      <c r="S18">
+        <v>3.45</v>
+      </c>
+      <c r="T18">
+        <v>1.76</v>
+      </c>
+      <c r="U18">
+        <v>2.14</v>
+      </c>
+      <c r="V18">
+        <v>1.71</v>
+      </c>
+      <c r="W18">
+        <v>1.37</v>
+      </c>
+      <c r="X18">
+        <v>17</v>
+      </c>
+      <c r="Y18">
+        <v>10.5</v>
+      </c>
+      <c r="Z18">
+        <v>15.5</v>
+      </c>
+      <c r="AA18">
+        <v>38</v>
+      </c>
+      <c r="AB18">
+        <v>16.5</v>
+      </c>
+      <c r="AC18">
         <v>8</v>
       </c>
-      <c r="I18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J18">
-        <v>4.9</v>
-      </c>
-      <c r="K18">
-        <v>5.2</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>2.16</v>
-      </c>
-      <c r="Q18">
-        <v>1.76</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <v>0</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
       <c r="AD18">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="CB18" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="F19">
-        <v>2.68</v>
+        <v>2.16</v>
       </c>
       <c r="G19">
-        <v>3.05</v>
+        <v>2.22</v>
       </c>
       <c r="H19">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="I19">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J19">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="K19">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="N19">
+        <v>3.45</v>
+      </c>
+      <c r="O19">
+        <v>1.37</v>
+      </c>
+      <c r="P19">
+        <v>1.84</v>
+      </c>
+      <c r="Q19">
+        <v>2.08</v>
+      </c>
+      <c r="R19">
+        <v>1.31</v>
+      </c>
+      <c r="S19">
+        <v>3.7</v>
+      </c>
+      <c r="T19">
+        <v>1.83</v>
+      </c>
+      <c r="U19">
+        <v>2.04</v>
+      </c>
+      <c r="V19">
+        <v>1.32</v>
+      </c>
+      <c r="W19">
+        <v>1.8</v>
+      </c>
+      <c r="X19">
+        <v>15.5</v>
+      </c>
+      <c r="Y19">
+        <v>14</v>
+      </c>
+      <c r="Z19">
+        <v>38</v>
+      </c>
+      <c r="AA19">
+        <v>100</v>
+      </c>
+      <c r="AB19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC19">
+        <v>7.8</v>
+      </c>
+      <c r="AD19">
+        <v>16.5</v>
+      </c>
+      <c r="AE19">
+        <v>65</v>
+      </c>
+      <c r="AF19">
+        <v>15.5</v>
+      </c>
+      <c r="AG19">
+        <v>11.5</v>
+      </c>
+      <c r="AH19">
+        <v>970</v>
+      </c>
+      <c r="AI19">
+        <v>75</v>
+      </c>
+      <c r="AJ19">
+        <v>38</v>
+      </c>
+      <c r="AK19">
+        <v>32</v>
+      </c>
+      <c r="AL19">
+        <v>48</v>
+      </c>
+      <c r="AM19">
+        <v>130</v>
+      </c>
+      <c r="AN19">
+        <v>25</v>
+      </c>
+      <c r="AO19">
+        <v>70</v>
+      </c>
+      <c r="AP19">
+        <v>11</v>
+      </c>
+      <c r="AQ19">
+        <v>12</v>
+      </c>
+      <c r="AR19">
+        <v>21</v>
+      </c>
+      <c r="AS19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT19">
+        <v>8</v>
+      </c>
+      <c r="AU19">
+        <v>6.8</v>
+      </c>
+      <c r="AV19">
+        <v>14</v>
+      </c>
+      <c r="AW19">
+        <v>8.4</v>
+      </c>
+      <c r="AX19">
+        <v>11.5</v>
+      </c>
+      <c r="AY19">
+        <v>9.6</v>
+      </c>
+      <c r="AZ19">
+        <v>15</v>
+      </c>
+      <c r="BA19">
+        <v>8.6</v>
+      </c>
+      <c r="BB19">
+        <v>21</v>
+      </c>
+      <c r="BC19">
+        <v>21</v>
+      </c>
+      <c r="BD19">
+        <v>30</v>
+      </c>
+      <c r="BE19">
+        <v>9</v>
+      </c>
+      <c r="BF19">
+        <v>16</v>
+      </c>
+      <c r="BG19">
+        <v>8.4</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.55</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.12</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.2</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.9</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.2</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.2</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
         <v>2.16</v>
       </c>
-      <c r="O19">
-        <v>1.48</v>
-      </c>
-      <c r="P19">
-        <v>1.36</v>
-      </c>
-      <c r="Q19">
-        <v>2.54</v>
-      </c>
-      <c r="R19">
-        <v>1.08</v>
-      </c>
-      <c r="S19">
-        <v>3.1</v>
-      </c>
-      <c r="T19">
-        <v>1.11</v>
-      </c>
-      <c r="U19">
-        <v>1.11</v>
-      </c>
-      <c r="V19">
-        <v>1.31</v>
-      </c>
-      <c r="W19">
-        <v>1.49</v>
-      </c>
-      <c r="X19">
-        <v>1000</v>
-      </c>
-      <c r="Y19">
-        <v>1000</v>
-      </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>1000</v>
-      </c>
-      <c r="AC19">
-        <v>1000</v>
-      </c>
-      <c r="AD19">
-        <v>1000</v>
-      </c>
-      <c r="AE19">
-        <v>1000</v>
-      </c>
-      <c r="AF19">
-        <v>1000</v>
-      </c>
-      <c r="AG19">
-        <v>1000</v>
-      </c>
-      <c r="AH19">
-        <v>1000</v>
-      </c>
-      <c r="AI19">
-        <v>1000</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
-      <c r="AK19">
-        <v>1000</v>
-      </c>
-      <c r="AL19">
-        <v>1000</v>
-      </c>
-      <c r="AM19">
-        <v>1000</v>
-      </c>
-      <c r="AN19">
-        <v>1000</v>
-      </c>
-      <c r="AO19">
-        <v>1000</v>
-      </c>
-      <c r="AP19">
-        <v>1.01</v>
-      </c>
-      <c r="AQ19">
-        <v>1.01</v>
-      </c>
-      <c r="AR19">
-        <v>1.01</v>
-      </c>
-      <c r="AS19">
-        <v>1.01</v>
-      </c>
-      <c r="AT19">
-        <v>1.01</v>
-      </c>
-      <c r="AU19">
-        <v>1.01</v>
-      </c>
-      <c r="AV19">
-        <v>1.01</v>
-      </c>
-      <c r="AW19">
-        <v>1.01</v>
-      </c>
-      <c r="AX19">
-        <v>1.01</v>
-      </c>
-      <c r="AY19">
-        <v>1.01</v>
-      </c>
-      <c r="AZ19">
-        <v>1.01</v>
-      </c>
-      <c r="BA19">
-        <v>1.01</v>
-      </c>
-      <c r="BB19">
-        <v>1.01</v>
-      </c>
-      <c r="BC19">
-        <v>1.01</v>
-      </c>
-      <c r="BD19">
-        <v>1.01</v>
-      </c>
-      <c r="BE19">
-        <v>1.01</v>
-      </c>
-      <c r="BF19">
-        <v>1.01</v>
-      </c>
-      <c r="BG19">
-        <v>1.01</v>
-      </c>
-      <c r="BH19">
-        <v>2.96</v>
-      </c>
-      <c r="BI19">
-        <v>2.02</v>
-      </c>
-      <c r="BJ19">
-        <v>1000</v>
-      </c>
-      <c r="BK19">
-        <v>1.53</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>1.53</v>
-      </c>
-      <c r="BN19">
-        <v>1000</v>
-      </c>
-      <c r="BO19">
-        <v>1.52</v>
-      </c>
-      <c r="BP19">
-        <v>1000</v>
-      </c>
-      <c r="BQ19">
-        <v>1.53</v>
-      </c>
-      <c r="BR19">
-        <v>1000</v>
-      </c>
-      <c r="BS19">
-        <v>1.53</v>
-      </c>
-      <c r="BT19">
-        <v>1000</v>
-      </c>
-      <c r="BU19">
-        <v>1.66</v>
-      </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="CB19" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5419,178 +5371,178 @@
         <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="F20">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="G20">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="H20">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>3.95</v>
       </c>
       <c r="K20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N20">
-        <v>3.7</v>
+        <v>2.86</v>
       </c>
       <c r="O20">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P20">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q20">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="R20">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S20">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="T20">
         <v>1.85</v>
       </c>
       <c r="U20">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="V20">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W20">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="X20">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y20">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z20">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA20">
         <v>160</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC20">
         <v>9.4</v>
       </c>
       <c r="AD20">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE20">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF20">
         <v>11</v>
       </c>
       <c r="AG20">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH20">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI20">
         <v>85</v>
       </c>
       <c r="AJ20">
+        <v>17.5</v>
+      </c>
+      <c r="AK20">
+        <v>18</v>
+      </c>
+      <c r="AL20">
+        <v>48</v>
+      </c>
+      <c r="AM20">
+        <v>130</v>
+      </c>
+      <c r="AN20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO20">
+        <v>100</v>
+      </c>
+      <c r="AP20">
+        <v>14.5</v>
+      </c>
+      <c r="AQ20">
+        <v>17.5</v>
+      </c>
+      <c r="AR20">
+        <v>9</v>
+      </c>
+      <c r="AS20">
+        <v>10</v>
+      </c>
+      <c r="AT20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV20">
         <v>19</v>
       </c>
-      <c r="AK20">
-        <v>19.5</v>
-      </c>
-      <c r="AL20">
-        <v>38</v>
-      </c>
-      <c r="AM20">
-        <v>140</v>
-      </c>
-      <c r="AN20">
-        <v>11.5</v>
-      </c>
-      <c r="AO20">
-        <v>110</v>
-      </c>
-      <c r="AP20">
-        <v>11.5</v>
-      </c>
-      <c r="AQ20">
-        <v>13.5</v>
-      </c>
-      <c r="AR20">
-        <v>7</v>
-      </c>
-      <c r="AS20">
-        <v>7.8</v>
-      </c>
-      <c r="AT20">
-        <v>6.6</v>
-      </c>
-      <c r="AU20">
-        <v>7</v>
-      </c>
-      <c r="AV20">
+      <c r="AW20">
+        <v>9.6</v>
+      </c>
+      <c r="AX20">
+        <v>9.4</v>
+      </c>
+      <c r="AY20">
+        <v>9</v>
+      </c>
+      <c r="AZ20">
+        <v>17.5</v>
+      </c>
+      <c r="BA20">
+        <v>9.6</v>
+      </c>
+      <c r="BB20">
+        <v>15</v>
+      </c>
+      <c r="BC20">
         <v>15.5</v>
       </c>
-      <c r="AW20">
-        <v>7.6</v>
-      </c>
-      <c r="AX20">
+      <c r="BD20">
         <v>8.199999999999999</v>
       </c>
-      <c r="AY20">
-        <v>7.8</v>
-      </c>
-      <c r="AZ20">
-        <v>15.5</v>
-      </c>
-      <c r="BA20">
-        <v>7.6</v>
-      </c>
-      <c r="BB20">
-        <v>13.5</v>
-      </c>
-      <c r="BC20">
-        <v>14</v>
-      </c>
-      <c r="BD20">
-        <v>6.8</v>
-      </c>
       <c r="BE20">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BF20">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG20">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5653,1217 +5605,7 @@
         <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="21" spans="1:80">
-      <c r="A21" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" t="s">
-        <v>126</v>
-      </c>
-      <c r="E21" t="s">
-        <v>150</v>
-      </c>
-      <c r="F21">
-        <v>4.3</v>
-      </c>
-      <c r="G21">
-        <v>4.7</v>
-      </c>
-      <c r="H21">
-        <v>1.87</v>
-      </c>
-      <c r="I21">
-        <v>1.96</v>
-      </c>
-      <c r="J21">
-        <v>3.8</v>
-      </c>
-      <c r="K21">
-        <v>4.1</v>
-      </c>
-      <c r="L21">
-        <v>1.35</v>
-      </c>
-      <c r="M21">
-        <v>1.05</v>
-      </c>
-      <c r="N21">
-        <v>4.3</v>
-      </c>
-      <c r="O21">
-        <v>1.27</v>
-      </c>
-      <c r="P21">
-        <v>2.14</v>
-      </c>
-      <c r="Q21">
-        <v>1.8</v>
-      </c>
-      <c r="R21">
-        <v>1.45</v>
-      </c>
-      <c r="S21">
-        <v>2.96</v>
-      </c>
-      <c r="T21">
-        <v>1.73</v>
-      </c>
-      <c r="U21">
-        <v>2.22</v>
-      </c>
-      <c r="V21">
-        <v>2.04</v>
-      </c>
-      <c r="W21">
-        <v>1.27</v>
-      </c>
-      <c r="X21">
-        <v>22</v>
-      </c>
-      <c r="Y21">
-        <v>10.5</v>
-      </c>
-      <c r="Z21">
-        <v>13</v>
-      </c>
-      <c r="AA21">
-        <v>22</v>
-      </c>
-      <c r="AB21">
-        <v>18</v>
-      </c>
-      <c r="AC21">
-        <v>9</v>
-      </c>
-      <c r="AD21">
-        <v>10.5</v>
-      </c>
-      <c r="AE21">
-        <v>19.5</v>
-      </c>
-      <c r="AF21">
-        <v>36</v>
-      </c>
-      <c r="AG21">
-        <v>18</v>
-      </c>
-      <c r="AH21">
-        <v>18</v>
-      </c>
-      <c r="AI21">
-        <v>32</v>
-      </c>
-      <c r="AJ21">
-        <v>120</v>
-      </c>
-      <c r="AK21">
-        <v>55</v>
-      </c>
-      <c r="AL21">
-        <v>65</v>
-      </c>
-      <c r="AM21">
-        <v>100</v>
-      </c>
-      <c r="AN21">
-        <v>60</v>
-      </c>
-      <c r="AO21">
-        <v>11</v>
-      </c>
-      <c r="AP21">
-        <v>15.5</v>
-      </c>
-      <c r="AQ21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR21">
-        <v>11</v>
-      </c>
-      <c r="AS21">
-        <v>18.5</v>
-      </c>
-      <c r="AT21">
-        <v>15.5</v>
-      </c>
-      <c r="AU21">
-        <v>8</v>
-      </c>
-      <c r="AV21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW21">
-        <v>16.5</v>
-      </c>
-      <c r="AX21">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY21">
-        <v>15.5</v>
-      </c>
-      <c r="AZ21">
-        <v>15.5</v>
-      </c>
-      <c r="BA21">
-        <v>8</v>
-      </c>
-      <c r="BB21">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC21">
-        <v>9</v>
-      </c>
-      <c r="BD21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE21">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG21">
-        <v>9.6</v>
-      </c>
-      <c r="BH21">
-        <v>1000</v>
-      </c>
-      <c r="BI21">
-        <v>1.58</v>
-      </c>
-      <c r="BJ21">
-        <v>1000</v>
-      </c>
-      <c r="BK21">
-        <v>2.2</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>2.62</v>
-      </c>
-      <c r="BN21">
-        <v>1000</v>
-      </c>
-      <c r="BO21">
-        <v>2.08</v>
-      </c>
-      <c r="BP21">
-        <v>1000</v>
-      </c>
-      <c r="BQ21">
-        <v>2.62</v>
-      </c>
-      <c r="BR21">
-        <v>1000</v>
-      </c>
-      <c r="BS21">
-        <v>2.62</v>
-      </c>
-      <c r="BT21">
-        <v>1000</v>
-      </c>
-      <c r="BU21">
-        <v>1.76</v>
-      </c>
-      <c r="BV21">
-        <v>1000</v>
-      </c>
-      <c r="BW21">
-        <v>2.62</v>
-      </c>
-      <c r="BX21">
-        <v>1000</v>
-      </c>
-      <c r="BY21">
-        <v>2.62</v>
-      </c>
-      <c r="BZ21">
-        <v>1000</v>
-      </c>
-      <c r="CA21">
-        <v>2.62</v>
-      </c>
-      <c r="CB21" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="22" spans="1:80">
-      <c r="A22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E22" t="s">
-        <v>151</v>
-      </c>
-      <c r="F22">
-        <v>2.46</v>
-      </c>
-      <c r="G22">
-        <v>2.62</v>
-      </c>
-      <c r="H22">
-        <v>3.25</v>
-      </c>
-      <c r="I22">
-        <v>3.5</v>
-      </c>
-      <c r="J22">
-        <v>3.15</v>
-      </c>
-      <c r="K22">
-        <v>3.35</v>
-      </c>
-      <c r="L22">
-        <v>1.48</v>
-      </c>
-      <c r="M22">
-        <v>1.11</v>
-      </c>
-      <c r="N22">
-        <v>2.76</v>
-      </c>
-      <c r="O22">
-        <v>1.49</v>
-      </c>
-      <c r="P22">
-        <v>1.64</v>
-      </c>
-      <c r="Q22">
-        <v>2.42</v>
-      </c>
-      <c r="R22">
-        <v>1.23</v>
-      </c>
-      <c r="S22">
-        <v>4.7</v>
-      </c>
-      <c r="T22">
-        <v>2.02</v>
-      </c>
-      <c r="U22">
-        <v>1.9</v>
-      </c>
-      <c r="V22">
-        <v>1.4</v>
-      </c>
-      <c r="W22">
-        <v>1.62</v>
-      </c>
-      <c r="X22">
-        <v>11.5</v>
-      </c>
-      <c r="Y22">
-        <v>11</v>
-      </c>
-      <c r="Z22">
-        <v>27</v>
-      </c>
-      <c r="AA22">
-        <v>80</v>
-      </c>
-      <c r="AB22">
-        <v>8.4</v>
-      </c>
-      <c r="AC22">
-        <v>7.4</v>
-      </c>
-      <c r="AD22">
-        <v>15.5</v>
-      </c>
-      <c r="AE22">
-        <v>60</v>
-      </c>
-      <c r="AF22">
-        <v>16.5</v>
-      </c>
-      <c r="AG22">
-        <v>12.5</v>
-      </c>
-      <c r="AH22">
-        <v>22</v>
-      </c>
-      <c r="AI22">
-        <v>80</v>
-      </c>
-      <c r="AJ22">
-        <v>40</v>
-      </c>
-      <c r="AK22">
-        <v>36</v>
-      </c>
-      <c r="AL22">
-        <v>65</v>
-      </c>
-      <c r="AM22">
-        <v>180</v>
-      </c>
-      <c r="AN22">
-        <v>36</v>
-      </c>
-      <c r="AO22">
-        <v>70</v>
-      </c>
-      <c r="AP22">
-        <v>8.6</v>
-      </c>
-      <c r="AQ22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR22">
-        <v>20</v>
-      </c>
-      <c r="AS22">
-        <v>7.8</v>
-      </c>
-      <c r="AT22">
-        <v>7.4</v>
-      </c>
-      <c r="AU22">
-        <v>6.6</v>
-      </c>
-      <c r="AV22">
-        <v>13</v>
-      </c>
-      <c r="AW22">
-        <v>30</v>
-      </c>
-      <c r="AX22">
-        <v>13</v>
-      </c>
-      <c r="AY22">
-        <v>10.5</v>
-      </c>
-      <c r="AZ22">
-        <v>18.5</v>
-      </c>
-      <c r="BA22">
-        <v>7.8</v>
-      </c>
-      <c r="BB22">
-        <v>27</v>
-      </c>
-      <c r="BC22">
-        <v>7</v>
-      </c>
-      <c r="BD22">
-        <v>7.8</v>
-      </c>
-      <c r="BE22">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF22">
-        <v>22</v>
-      </c>
-      <c r="BG22">
-        <v>38</v>
-      </c>
-      <c r="BH22">
-        <v>1000</v>
-      </c>
-      <c r="BI22">
-        <v>1.04</v>
-      </c>
-      <c r="BJ22">
-        <v>1000</v>
-      </c>
-      <c r="BK22">
-        <v>1.04</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>1.04</v>
-      </c>
-      <c r="BN22">
-        <v>1000</v>
-      </c>
-      <c r="BO22">
-        <v>1.04</v>
-      </c>
-      <c r="BP22">
-        <v>1000</v>
-      </c>
-      <c r="BQ22">
-        <v>1.04</v>
-      </c>
-      <c r="BR22">
-        <v>1000</v>
-      </c>
-      <c r="BS22">
-        <v>1.04</v>
-      </c>
-      <c r="BT22">
-        <v>1000</v>
-      </c>
-      <c r="BU22">
-        <v>1.04</v>
-      </c>
-      <c r="BV22">
-        <v>1000</v>
-      </c>
-      <c r="BW22">
-        <v>1.04</v>
-      </c>
-      <c r="BX22">
-        <v>1000</v>
-      </c>
-      <c r="BY22">
-        <v>1.04</v>
-      </c>
-      <c r="BZ22">
-        <v>1000</v>
-      </c>
-      <c r="CA22">
-        <v>1.04</v>
-      </c>
-      <c r="CB22" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="23" spans="1:80">
-      <c r="A23" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" t="s">
-        <v>104</v>
-      </c>
-      <c r="D23" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" t="s">
-        <v>152</v>
-      </c>
-      <c r="F23">
-        <v>3.4</v>
-      </c>
-      <c r="G23">
-        <v>3.6</v>
-      </c>
-      <c r="H23">
-        <v>2.28</v>
-      </c>
-      <c r="I23">
-        <v>2.38</v>
-      </c>
-      <c r="J23">
-        <v>3.45</v>
-      </c>
-      <c r="K23">
-        <v>3.6</v>
-      </c>
-      <c r="L23">
-        <v>1.37</v>
-      </c>
-      <c r="M23">
-        <v>1.07</v>
-      </c>
-      <c r="N23">
-        <v>3.7</v>
-      </c>
-      <c r="O23">
-        <v>1.32</v>
-      </c>
-      <c r="P23">
-        <v>1.92</v>
-      </c>
-      <c r="Q23">
-        <v>1.98</v>
-      </c>
-      <c r="R23">
-        <v>1.36</v>
-      </c>
-      <c r="S23">
-        <v>3.5</v>
-      </c>
-      <c r="T23">
-        <v>1.77</v>
-      </c>
-      <c r="U23">
-        <v>2.16</v>
-      </c>
-      <c r="V23">
-        <v>1.72</v>
-      </c>
-      <c r="W23">
-        <v>1.38</v>
-      </c>
-      <c r="X23">
-        <v>17</v>
-      </c>
-      <c r="Y23">
-        <v>10.5</v>
-      </c>
-      <c r="Z23">
-        <v>15.5</v>
-      </c>
-      <c r="AA23">
-        <v>38</v>
-      </c>
-      <c r="AB23">
-        <v>16.5</v>
-      </c>
-      <c r="AC23">
-        <v>8</v>
-      </c>
-      <c r="AD23">
-        <v>11.5</v>
-      </c>
-      <c r="AE23">
-        <v>26</v>
-      </c>
-      <c r="AF23">
-        <v>25</v>
-      </c>
-      <c r="AG23">
-        <v>15</v>
-      </c>
-      <c r="AH23">
-        <v>17</v>
-      </c>
-      <c r="AI23">
-        <v>48</v>
-      </c>
-      <c r="AJ23">
-        <v>65</v>
-      </c>
-      <c r="AK23">
-        <v>50</v>
-      </c>
-      <c r="AL23">
-        <v>65</v>
-      </c>
-      <c r="AM23">
-        <v>110</v>
-      </c>
-      <c r="AN23">
-        <v>50</v>
-      </c>
-      <c r="AO23">
-        <v>24</v>
-      </c>
-      <c r="AP23">
-        <v>12</v>
-      </c>
-      <c r="AQ23">
-        <v>9</v>
-      </c>
-      <c r="AR23">
-        <v>13</v>
-      </c>
-      <c r="AS23">
-        <v>6.6</v>
-      </c>
-      <c r="AT23">
-        <v>11.5</v>
-      </c>
-      <c r="AU23">
-        <v>7</v>
-      </c>
-      <c r="AV23">
-        <v>10</v>
-      </c>
-      <c r="AW23">
-        <v>17.5</v>
-      </c>
-      <c r="AX23">
-        <v>21</v>
-      </c>
-      <c r="AY23">
-        <v>13</v>
-      </c>
-      <c r="AZ23">
-        <v>15</v>
-      </c>
-      <c r="BA23">
-        <v>6.8</v>
-      </c>
-      <c r="BB23">
-        <v>7</v>
-      </c>
-      <c r="BC23">
-        <v>6.8</v>
-      </c>
-      <c r="BD23">
-        <v>32</v>
-      </c>
-      <c r="BE23">
-        <v>6.8</v>
-      </c>
-      <c r="BF23">
-        <v>32</v>
-      </c>
-      <c r="BG23">
-        <v>16.5</v>
-      </c>
-      <c r="BH23">
-        <v>1000</v>
-      </c>
-      <c r="BI23">
-        <v>1.17</v>
-      </c>
-      <c r="BJ23">
-        <v>1000</v>
-      </c>
-      <c r="BK23">
-        <v>1.58</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>1.58</v>
-      </c>
-      <c r="BN23">
-        <v>1000</v>
-      </c>
-      <c r="BO23">
-        <v>1.58</v>
-      </c>
-      <c r="BP23">
-        <v>1000</v>
-      </c>
-      <c r="BQ23">
-        <v>1.58</v>
-      </c>
-      <c r="BR23">
-        <v>1000</v>
-      </c>
-      <c r="BS23">
-        <v>1.58</v>
-      </c>
-      <c r="BT23">
-        <v>1000</v>
-      </c>
-      <c r="BU23">
-        <v>1.32</v>
-      </c>
-      <c r="BV23">
-        <v>1000</v>
-      </c>
-      <c r="BW23">
-        <v>1.58</v>
-      </c>
-      <c r="BX23">
-        <v>1000</v>
-      </c>
-      <c r="BY23">
-        <v>1.58</v>
-      </c>
-      <c r="BZ23">
-        <v>1000</v>
-      </c>
-      <c r="CA23">
-        <v>1.58</v>
-      </c>
-      <c r="CB23" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="24" spans="1:80">
-      <c r="A24" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" t="s">
-        <v>129</v>
-      </c>
-      <c r="E24" t="s">
-        <v>153</v>
-      </c>
-      <c r="F24">
-        <v>2.16</v>
-      </c>
-      <c r="G24">
-        <v>2.22</v>
-      </c>
-      <c r="H24">
-        <v>3.8</v>
-      </c>
-      <c r="I24">
-        <v>4.1</v>
-      </c>
-      <c r="J24">
-        <v>3.45</v>
-      </c>
-      <c r="K24">
-        <v>3.5</v>
-      </c>
-      <c r="L24">
-        <v>1.44</v>
-      </c>
-      <c r="M24">
-        <v>1.08</v>
-      </c>
-      <c r="N24">
-        <v>3.45</v>
-      </c>
-      <c r="O24">
-        <v>1.36</v>
-      </c>
-      <c r="P24">
-        <v>1.84</v>
-      </c>
-      <c r="Q24">
-        <v>2.08</v>
-      </c>
-      <c r="R24">
-        <v>1.32</v>
-      </c>
-      <c r="S24">
-        <v>3.75</v>
-      </c>
-      <c r="T24">
-        <v>1.84</v>
-      </c>
-      <c r="U24">
-        <v>2.06</v>
-      </c>
-      <c r="V24">
-        <v>1.32</v>
-      </c>
-      <c r="W24">
-        <v>1.81</v>
-      </c>
-      <c r="X24">
-        <v>15.5</v>
-      </c>
-      <c r="Y24">
-        <v>14</v>
-      </c>
-      <c r="Z24">
-        <v>38</v>
-      </c>
-      <c r="AA24">
-        <v>100</v>
-      </c>
-      <c r="AB24">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC24">
-        <v>7.6</v>
-      </c>
-      <c r="AD24">
-        <v>16.5</v>
-      </c>
-      <c r="AE24">
-        <v>65</v>
-      </c>
-      <c r="AF24">
-        <v>15</v>
-      </c>
-      <c r="AG24">
-        <v>11.5</v>
-      </c>
-      <c r="AH24">
-        <v>20</v>
-      </c>
-      <c r="AI24">
-        <v>75</v>
-      </c>
-      <c r="AJ24">
-        <v>38</v>
-      </c>
-      <c r="AK24">
-        <v>30</v>
-      </c>
-      <c r="AL24">
-        <v>48</v>
-      </c>
-      <c r="AM24">
-        <v>130</v>
-      </c>
-      <c r="AN24">
-        <v>24</v>
-      </c>
-      <c r="AO24">
-        <v>70</v>
-      </c>
-      <c r="AP24">
-        <v>11</v>
-      </c>
-      <c r="AQ24">
-        <v>12</v>
-      </c>
-      <c r="AR24">
-        <v>21</v>
-      </c>
-      <c r="AS24">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT24">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU24">
-        <v>6.8</v>
-      </c>
-      <c r="AV24">
-        <v>14</v>
-      </c>
-      <c r="AW24">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX24">
-        <v>11.5</v>
-      </c>
-      <c r="AY24">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ24">
-        <v>16</v>
-      </c>
-      <c r="BA24">
-        <v>9</v>
-      </c>
-      <c r="BB24">
-        <v>21</v>
-      </c>
-      <c r="BC24">
-        <v>21</v>
-      </c>
-      <c r="BD24">
-        <v>30</v>
-      </c>
-      <c r="BE24">
-        <v>9.4</v>
-      </c>
-      <c r="BF24">
-        <v>16</v>
-      </c>
-      <c r="BG24">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH24">
-        <v>1000</v>
-      </c>
-      <c r="BI24">
-        <v>2.66</v>
-      </c>
-      <c r="BJ24">
-        <v>1000</v>
-      </c>
-      <c r="BK24">
-        <v>2.16</v>
-      </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>2.48</v>
-      </c>
-      <c r="BN24">
-        <v>1000</v>
-      </c>
-      <c r="BO24">
-        <v>1.9</v>
-      </c>
-      <c r="BP24">
-        <v>1000</v>
-      </c>
-      <c r="BQ24">
-        <v>2.56</v>
-      </c>
-      <c r="BR24">
-        <v>1000</v>
-      </c>
-      <c r="BS24">
-        <v>2.48</v>
-      </c>
-      <c r="BT24">
-        <v>1000</v>
-      </c>
-      <c r="BU24">
-        <v>2.16</v>
-      </c>
-      <c r="BV24">
-        <v>1000</v>
-      </c>
-      <c r="BW24">
-        <v>2.48</v>
-      </c>
-      <c r="BX24">
-        <v>1000</v>
-      </c>
-      <c r="BY24">
-        <v>2.48</v>
-      </c>
-      <c r="BZ24">
-        <v>1000</v>
-      </c>
-      <c r="CA24">
-        <v>2.48</v>
-      </c>
-      <c r="CB24" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="25" spans="1:80">
-      <c r="A25" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" t="s">
-        <v>130</v>
-      </c>
-      <c r="E25" t="s">
-        <v>154</v>
-      </c>
-      <c r="F25">
-        <v>1.69</v>
-      </c>
-      <c r="G25">
-        <v>1.75</v>
-      </c>
-      <c r="H25">
-        <v>5.4</v>
-      </c>
-      <c r="I25">
-        <v>6</v>
-      </c>
-      <c r="J25">
-        <v>4</v>
-      </c>
-      <c r="K25">
-        <v>4.3</v>
-      </c>
-      <c r="L25">
-        <v>1.01</v>
-      </c>
-      <c r="M25">
-        <v>1.05</v>
-      </c>
-      <c r="N25">
-        <v>4</v>
-      </c>
-      <c r="O25">
-        <v>1.27</v>
-      </c>
-      <c r="P25">
-        <v>2.08</v>
-      </c>
-      <c r="Q25">
-        <v>1.8</v>
-      </c>
-      <c r="R25">
-        <v>1.42</v>
-      </c>
-      <c r="S25">
-        <v>3.1</v>
-      </c>
-      <c r="T25">
-        <v>1.85</v>
-      </c>
-      <c r="U25">
-        <v>2.08</v>
-      </c>
-      <c r="V25">
-        <v>1.2</v>
-      </c>
-      <c r="W25">
-        <v>2.32</v>
-      </c>
-      <c r="X25">
-        <v>17</v>
-      </c>
-      <c r="Y25">
-        <v>23</v>
-      </c>
-      <c r="Z25">
-        <v>55</v>
-      </c>
-      <c r="AA25">
-        <v>160</v>
-      </c>
-      <c r="AB25">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC25">
-        <v>9.4</v>
-      </c>
-      <c r="AD25">
-        <v>25</v>
-      </c>
-      <c r="AE25">
-        <v>85</v>
-      </c>
-      <c r="AF25">
-        <v>11</v>
-      </c>
-      <c r="AG25">
-        <v>10</v>
-      </c>
-      <c r="AH25">
-        <v>20</v>
-      </c>
-      <c r="AI25">
-        <v>85</v>
-      </c>
-      <c r="AJ25">
-        <v>17.5</v>
-      </c>
-      <c r="AK25">
-        <v>18</v>
-      </c>
-      <c r="AL25">
-        <v>48</v>
-      </c>
-      <c r="AM25">
-        <v>130</v>
-      </c>
-      <c r="AN25">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO25">
-        <v>100</v>
-      </c>
-      <c r="AP25">
-        <v>14.5</v>
-      </c>
-      <c r="AQ25">
-        <v>17.5</v>
-      </c>
-      <c r="AR25">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS25">
-        <v>10</v>
-      </c>
-      <c r="AT25">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU25">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV25">
-        <v>19</v>
-      </c>
-      <c r="AW25">
-        <v>9.6</v>
-      </c>
-      <c r="AX25">
-        <v>9.4</v>
-      </c>
-      <c r="AY25">
-        <v>9</v>
-      </c>
-      <c r="AZ25">
-        <v>17.5</v>
-      </c>
-      <c r="BA25">
-        <v>9.6</v>
-      </c>
-      <c r="BB25">
-        <v>15</v>
-      </c>
-      <c r="BC25">
-        <v>15.5</v>
-      </c>
-      <c r="BD25">
-        <v>8.4</v>
-      </c>
-      <c r="BE25">
-        <v>10</v>
-      </c>
-      <c r="BF25">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG25">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
-        <v>1.04</v>
-      </c>
-      <c r="BJ25">
-        <v>1000</v>
-      </c>
-      <c r="BK25">
-        <v>1.04</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>1.04</v>
-      </c>
-      <c r="BN25">
-        <v>1000</v>
-      </c>
-      <c r="BO25">
-        <v>1.04</v>
-      </c>
-      <c r="BP25">
-        <v>1000</v>
-      </c>
-      <c r="BQ25">
-        <v>1.04</v>
-      </c>
-      <c r="BR25">
-        <v>1000</v>
-      </c>
-      <c r="BS25">
-        <v>1.04</v>
-      </c>
-      <c r="BT25">
-        <v>1000</v>
-      </c>
-      <c r="BU25">
-        <v>1.04</v>
-      </c>
-      <c r="BV25">
-        <v>1000</v>
-      </c>
-      <c r="BW25">
-        <v>1.04</v>
-      </c>
-      <c r="BX25">
-        <v>1000</v>
-      </c>
-      <c r="BY25">
-        <v>1.04</v>
-      </c>
-      <c r="BZ25">
-        <v>1000</v>
-      </c>
-      <c r="CA25">
-        <v>1.04</v>
-      </c>
-      <c r="CB25" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
